--- a/セリフ編集/キャラタイプ別/標準×強気.xlsx
+++ b/セリフ編集/キャラタイプ別/標準×強気.xlsx
@@ -2030,7 +2030,7 @@
       </c>
       <c r="F50" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">引き分け? そんなの求めてません。</t>
+          <t xml:space="preserve">決着つかず? そんなの求めてません。</t>
         </is>
       </c>
     </row>

--- a/セリフ編集/キャラタイプ別/標準×強気.xlsx
+++ b/セリフ編集/キャラタイプ別/標準×強気.xlsx
@@ -411,7 +411,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H150"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -469,22 +469,22 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.bold.standard.hit[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.standard.bold[1]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/victory-lines.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D2" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.standard.hit[1]</t>
+          <t xml:space="preserve">atk.standard.bold[1]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr" s="2">
@@ -494,29 +494,29 @@
       </c>
       <c r="F2" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あんたたち相手に、ここで膝はつかない。</t>
+          <t xml:space="preserve">まだまだっ！</t>
         </is>
       </c>
     </row>
     <row r="3" ht="40" customHeight="1">
       <c r="A3" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.bold.standard.hit[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.standard.bold[2]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/victory-lines.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D3" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.standard.hit[2]</t>
+          <t xml:space="preserve">atk.standard.bold[2]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr" s="2">
@@ -526,29 +526,29 @@
       </c>
       <c r="F3" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここで倒れたら、切った判断が正しかったことになる。冗談じゃない。</t>
+          <t xml:space="preserve">ここからが本番よっ！</t>
         </is>
       </c>
     </row>
     <row r="4" ht="40" customHeight="1">
       <c r="A4" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.bold.standard.win[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.standard.bold[3]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/victory-lines.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D4" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.standard.win[1]</t>
+          <t xml:space="preserve">atk.standard.bold[3]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr" s="2">
@@ -558,29 +558,29 @@
       </c>
       <c r="F4" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">切られた側が、あそこの選手を沈めた。これが答えよ。</t>
+          <t xml:space="preserve">逃がさないわよ！</t>
         </is>
       </c>
     </row>
     <row r="5" ht="40" customHeight="1">
       <c r="A5" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.bold.standard.win[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.standard.bold[4]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/victory-lines.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D5" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.standard.win[2]</t>
+          <t xml:space="preserve">atk.standard.bold[4]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr" s="2">
@@ -590,1292 +590,4652 @@
       </c>
       <c r="F5" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの団体で消えるはずだった女が、ここに立ってる。見たでしょ。</t>
+          <t xml:space="preserve">受けてみなさい！</t>
         </is>
       </c>
     </row>
     <row r="6" ht="40" customHeight="1">
       <c r="A6" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_bold.lose[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.standard.bold[1]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D6" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_bold.lose[1]</t>
+          <t xml:space="preserve">bigmove.standard.bold[1]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けました。……悔しいです。</t>
+          <t xml:space="preserve">さあ…終わらせるわよっ！</t>
         </is>
       </c>
     </row>
     <row r="7" ht="40" customHeight="1">
       <c r="A7" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_bold.lose[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.standard.bold[2]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D7" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_bold.lose[2]</t>
+          <t xml:space="preserve">bigmove.standard.bold[2]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は届きませんでした。……次は勝ちます。</t>
+          <t xml:space="preserve">見せてあげる…わたしの全力！</t>
         </is>
       </c>
     </row>
     <row r="8" ht="40" customHeight="1">
       <c r="A8" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_bold.lose[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.standard.bold[3]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D8" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_bold.lose[3]</t>
+          <t xml:space="preserve">bigmove.standard.bold[3]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すみません、負けました。でも、やってよかったです。</t>
+          <t xml:space="preserve">思いっきりいくわよっ！！</t>
         </is>
       </c>
     </row>
     <row r="9" ht="40" customHeight="1">
       <c r="A9" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_bold.petition[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.standard.bold[1]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D9" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_bold.petition[1]</t>
+          <t xml:space="preserve">climax.standard.bold[1]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、あの人とやらせてください。勝てます。</t>
+          <t xml:space="preserve">（ここからが、あたしの時間！）</t>
         </is>
       </c>
     </row>
     <row r="10" ht="40" customHeight="1">
       <c r="A10" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_bold.petition[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.standard.bold[2]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-engine-main.js</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">CUTIN_LINES</t>
         </is>
       </c>
       <c r="D10" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_bold.petition[2]</t>
+          <t xml:space="preserve">climax.standard.bold[2]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人とやりたいんです。……今なら、いけると思ってます。</t>
+          <t xml:space="preserve">（さあ…決めにいく）</t>
         </is>
       </c>
     </row>
     <row r="11" ht="40" customHeight="1">
       <c r="A11" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_bold.petition[3]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.standard.bold[1]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-lines.js</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
         </is>
       </c>
       <c r="D11" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_bold.petition[3]</t>
+          <t xml:space="preserve">standard.bold[1]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">待ってても回ってこないので、言いに来ました。組んでください。</t>
+          <t xml:space="preserve">はっ…やるじゃん…でもまだだよ！</t>
         </is>
       </c>
     </row>
     <row r="12" ht="40" customHeight="1">
       <c r="A12" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_bold.sendoff[1]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.standard.bold[2]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-lines.js</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
         </is>
       </c>
       <c r="D12" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_bold.sendoff[1]</t>
+          <t xml:space="preserve">standard.bold[2]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます! 勝ってきますから。</t>
+          <t xml:space="preserve">この程度じゃ…倒れないよ！</t>
         </is>
       </c>
     </row>
     <row r="13" ht="40" customHeight="1">
       <c r="A13" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_bold.sendoff[2]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.standard.bold[3]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/battle-lines.js</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES</t>
         </is>
       </c>
       <c r="D13" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_bold.sendoff[2]</t>
+          <t xml:space="preserve">standard.bold[3]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます。……見ててください。</t>
+          <t xml:space="preserve">あはは…痛い痛い…でもね！</t>
         </is>
       </c>
     </row>
     <row r="14" ht="40" customHeight="1">
       <c r="A14" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_bold.sendoff[3]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.standard.bold.hit[1]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/victory-lines.js</t>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
         </is>
       </c>
       <c r="D14" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_bold.sendoff[3]</t>
+          <t xml:space="preserve">standard.bold.hit[1]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">話が早くて助かります。行ってきます。</t>
+          <t xml:space="preserve">あんたたち相手に、ここで膝はつかない。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="40" customHeight="1">
       <c r="A15" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_bold.win[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.standard.bold.hit[2]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/victory-lines.js</t>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
         </is>
       </c>
       <c r="D15" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_bold.win[1]</t>
+          <t xml:space="preserve">standard.bold.hit[2]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ちました! ……言った通りでしょう。</t>
+          <t xml:space="preserve">ここで倒れたら、切った判断が正しかったことになる。冗談じゃない。</t>
         </is>
       </c>
     </row>
     <row r="16" ht="40" customHeight="1">
       <c r="A16" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_bold.win[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.standard.bold.win[1]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/victory-lines.js</t>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
         </is>
       </c>
       <c r="D16" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_bold.win[2]</t>
+          <t xml:space="preserve">standard.bold.win[1]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ちました。社長、ありがとうございました。</t>
+          <t xml:space="preserve">切られた側が、あそこの選手を沈めた。これが答えよ。</t>
         </is>
       </c>
     </row>
     <row r="17" ht="40" customHeight="1">
       <c r="A17" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES.standard_bold.win[3]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.standard.bold.win[2]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/victory-lines.js</t>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_LINES</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES</t>
         </is>
       </c>
       <c r="D17" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_bold.win[3]</t>
+          <t xml:space="preserve">standard.bold.win[2]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">01 試合本編・勝利演出・ダメージセリフ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やりました。……次も、任せてください。</t>
+          <t xml:space="preserve">あの団体で消えるはずだった女が、ここに立ってる。見たでしょ。</t>
         </is>
       </c>
     </row>
     <row r="18" ht="40" customHeight="1">
       <c r="A18" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_bold._accept[1]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.standard.bold[1]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">BETRAYAL_LINES</t>
         </is>
       </c>
       <c r="D18" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_bold._accept[1]</t>
+          <t xml:space="preserve">standard.bold[1]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">望むところ。よく言ってくれました。</t>
+          <t xml:space="preserve">くっ…！</t>
         </is>
       </c>
     </row>
     <row r="19" ht="40" customHeight="1">
       <c r="A19" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_bold._accept[2]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.standard.bold[2]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">BETRAYAL_LINES</t>
         </is>
       </c>
       <c r="D19" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_bold._accept[2]</t>
+          <t xml:space="preserve">standard.bold[2]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">待ってましたよ、そういうの。受けます。</t>
+          <t xml:space="preserve">ちっ…間に合わない</t>
         </is>
       </c>
     </row>
     <row r="20" ht="40" customHeight="1">
       <c r="A20" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_bold._accept[3]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.standard.bold[3]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">BETRAYAL_LINES</t>
         </is>
       </c>
       <c r="D20" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_bold._accept[3]</t>
+          <t xml:space="preserve">standard.bold[3]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いいですね。全部まとめて受け止めます。</t>
+          <t xml:space="preserve">届かなかった…</t>
         </is>
       </c>
     </row>
     <row r="21" ht="40" customHeight="1">
       <c r="A21" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_bold.draw[1]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.standard.bold[1]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES</t>
         </is>
       </c>
       <c r="D21" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_bold.draw[1]</t>
+          <t xml:space="preserve">standard.bold[1]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決めきれなかった。……つまらない終わり方だ。</t>
+          <t xml:space="preserve">そうはさせるか！</t>
         </is>
       </c>
     </row>
     <row r="22" ht="40" customHeight="1">
       <c r="A22" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_bold.draw[2]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.standard.bold[2]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES</t>
         </is>
       </c>
       <c r="D22" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_bold.draw[2]</t>
+          <t xml:space="preserve">standard.bold[2]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決着つかず? そんなの求めてません。</t>
+          <t xml:space="preserve">まだまだ！</t>
         </is>
       </c>
     </row>
     <row r="23" ht="40" customHeight="1">
       <c r="A23" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_bold.draw[3]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.standard.bold[3]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES</t>
         </is>
       </c>
       <c r="D23" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_bold.draw[3]</t>
+          <t xml:space="preserve">standard.bold[3]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ足りない。もう一度、名前を呼んでください。</t>
+          <t xml:space="preserve">そうはいかない！</t>
         </is>
       </c>
     </row>
     <row r="24" ht="40" customHeight="1">
       <c r="A24" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_bold.lose[1]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.standard.bold[1]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES</t>
         </is>
       </c>
       <c r="D24" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_bold.lose[1]</t>
+          <t xml:space="preserve">standard.bold[1]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">持っていかれました。……大口叩いた分、痛い。</t>
+          <t xml:space="preserve">二人で決める！</t>
         </is>
       </c>
     </row>
     <row r="25" ht="40" customHeight="1">
       <c r="A25" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_bold.lose[2]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.standard.bold[2]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES</t>
         </is>
       </c>
       <c r="D25" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_bold.lose[2]</t>
+          <t xml:space="preserve">standard.bold[2]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あなたが上でした。認めます、今日は。</t>
+          <t xml:space="preserve">合わせろ、いくぞ！</t>
         </is>
       </c>
     </row>
     <row r="26" ht="40" customHeight="1">
       <c r="A26" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_bold.lose[3]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.standard.bold[3]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES</t>
         </is>
       </c>
       <c r="D26" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_bold.lose[3]</t>
+          <t xml:space="preserve">standard.bold[3]</t>
         </is>
       </c>
       <c r="E26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けました。次はこうはいきませんから。</t>
+          <t xml:space="preserve">逃がさない、そっち頼む！</t>
         </is>
       </c>
     </row>
     <row r="27" ht="40" customHeight="1">
       <c r="A27" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_bold.win[1]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.standard.bold[1]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">HOT_TAG_LINES</t>
         </is>
       </c>
       <c r="D27" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_bold.win[1]</t>
+          <t xml:space="preserve">standard.bold[1]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ほら、言った通りでしょう。</t>
+          <t xml:space="preserve">待ってました！</t>
         </is>
       </c>
     </row>
     <row r="28" ht="40" customHeight="1">
       <c r="A28" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_bold.win[2]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.standard.bold[2]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">HOT_TAG_LINES</t>
         </is>
       </c>
       <c r="D28" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_bold.win[2]</t>
+          <t xml:space="preserve">standard.bold[2]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">引く気なんて、最初からなかったので。</t>
+          <t xml:space="preserve">私の番だ！</t>
         </is>
       </c>
     </row>
     <row r="29" ht="40" customHeight="1">
       <c r="A29" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_bold.win[3]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.standard.bold[3]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+          <t xml:space="preserve">HOT_TAG_LINES</t>
         </is>
       </c>
       <c r="D29" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard_bold.win[3]</t>
+          <t xml:space="preserve">standard.bold[3]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ちました。……次、いつでもどうぞ。</t>
+          <t xml:space="preserve">ようやく回ってきたな！</t>
         </is>
       </c>
     </row>
     <row r="30" ht="40" customHeight="1">
       <c r="A30" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LEADER_LINES.bold.standard[1]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.standard.bold[1]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LEADER_LINES</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES</t>
         </is>
       </c>
       <c r="D30" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.standard[1]</t>
+          <t xml:space="preserve">standard.bold[1]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あいつらと一緒にやってく気はないね。団体の中に、もう一本の筋が必要だ。</t>
+          <t xml:space="preserve">くそっ…{partner}、悪い。私のミスだ。次は絶対だ。</t>
         </is>
       </c>
     </row>
     <row r="31" ht="40" customHeight="1">
       <c r="A31" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LEADER_LINES.bold.standard[2]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.standard.bold[2]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LEADER_LINES</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES</t>
         </is>
       </c>
       <c r="D31" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.standard[2]</t>
+          <t xml:space="preserve">standard.bold[2]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あっち側にいるのがあたしの道じゃない。ここに集まった連中と、別でやる。</t>
+          <t xml:space="preserve">負けたままでいられるか…{partner}、次は倍返しだ！</t>
         </is>
       </c>
     </row>
     <row r="32" ht="40" customHeight="1">
       <c r="A32" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F03_SURVIVOR_LINES.bold.standard[1]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.standard.bold[1]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F03_SURVIVOR_LINES</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES</t>
         </is>
       </c>
       <c r="D32" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.standard[1]</t>
+          <t xml:space="preserve">standard.bold[1]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……信じられない。あの人が、もういない。</t>
+          <t xml:space="preserve">やったな{partner}！ 二人揃えば、負ける気がしないよ！</t>
         </is>
       </c>
     </row>
     <row r="33" ht="40" customHeight="1">
       <c r="A33" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F03_SURVIVOR_LINES.bold.standard[2]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.standard.bold[2]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/tag-battle-lines.js</t>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F03_SURVIVOR_LINES</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES</t>
         </is>
       </c>
       <c r="D33" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.standard[2]</t>
+          <t xml:space="preserve">standard.bold[2]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">02 タッグマッチ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふざけんな……あたしら、どうすりゃいいんだよ。</t>
+          <t xml:space="preserve">見たか、これが{partner}と私のタッグの力だ！</t>
         </is>
       </c>
     </row>
     <row r="34" ht="40" customHeight="1">
       <c r="A34" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES.bold.standard[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_bold.lose[1]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D34" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.standard[1]</t>
+          <t xml:space="preserve">standard_bold.lose[1]</t>
         </is>
       </c>
       <c r="E34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……悪いね。でも、あっち側のほうが、今のあたしには合ってる気がする。</t>
+          <t xml:space="preserve">負けました。……悔しいです。</t>
         </is>
       </c>
     </row>
     <row r="35" ht="40" customHeight="1">
       <c r="A35" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES.bold.standard[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_bold.lose[2]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F04_TARGET_LINES</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D35" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.standard[2]</t>
+          <t xml:space="preserve">standard_bold.lose[2]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここにいる理由、もう見つからないんだ。</t>
+          <t xml:space="preserve">今日は届きませんでした。……次は勝ちます。</t>
         </is>
       </c>
     </row>
     <row r="36" ht="40" customHeight="1">
       <c r="A36" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F07_LEADER_LINES.bold.standard[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_bold.lose[3]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F07_LEADER_LINES</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D36" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.standard[1]</t>
+          <t xml:space="preserve">standard_bold.lose[3]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、うちの連中の扱い、いいかげん見直してもらいたい。</t>
+          <t xml:space="preserve">すみません、負けました。でも、やってよかったです。</t>
         </is>
       </c>
     </row>
     <row r="37" ht="40" customHeight="1">
       <c r="A37" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F07_LEADER_LINES.bold.standard[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_bold.petition[1]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F07_LEADER_LINES</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D37" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.standard[2]</t>
+          <t xml:space="preserve">standard_bold.petition[1]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あたしが言う以上、話は通しておけよ。</t>
+          <t xml:space="preserve">社長、あの人とやらせてください。勝てます。</t>
         </is>
       </c>
     </row>
     <row r="38" ht="40" customHeight="1">
       <c r="A38" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_ENDING_WIN_LINES.bold.standard.high[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_bold.petition[2]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_ENDING_WIN_LINES</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D38" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.standard.high[1]</t>
+          <t xml:space="preserve">standard_bold.petition[2]</t>
         </is>
       </c>
       <c r="E38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ち越した。今夜は、うちの組の夜だ</t>
+          <t xml:space="preserve">あの人とやりたいんです。……今なら、いけると思ってます。</t>
         </is>
       </c>
     </row>
     <row r="39" ht="40" customHeight="1">
       <c r="A39" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_ENDING_WIN_LINES.bold.standard.high[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_bold.petition[3]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_ENDING_WIN_LINES</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D39" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.standard.high[2]</t>
+          <t xml:space="preserve">standard_bold.petition[3]</t>
         </is>
       </c>
       <c r="E39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">見たか。これがうちの組の力だ</t>
+          <t xml:space="preserve">待ってても回ってこないので、言いに来ました。組んでください。</t>
         </is>
       </c>
     </row>
     <row r="40" ht="40" customHeight="1">
       <c r="A40" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_MATCH_POST_WIN_LINES.bold.standard.high[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_bold.sendoff[1]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_MATCH_POST_WIN_LINES</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D40" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.standard.high[1]</t>
+          <t xml:space="preserve">standard_bold.sendoff[1]</t>
         </is>
       </c>
       <c r="E40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">1勝。あと何回続くかな</t>
+          <t xml:space="preserve">ありがとうございます! 勝ってきますから。</t>
         </is>
       </c>
     </row>
     <row r="41" ht="40" customHeight="1">
       <c r="A41" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_MATCH_POST_WIN_LINES.bold.standard.mid[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_bold.sendoff[2]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_MATCH_POST_WIN_LINES</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D41" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.standard.mid[1]</t>
+          <t xml:space="preserve">standard_bold.sendoff[2]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ序章だぜ</t>
+          <t xml:space="preserve">ありがとうございます。……見ててください。</t>
         </is>
       </c>
     </row>
     <row r="42" ht="40" customHeight="1">
       <c r="A42" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A.bold.standard.high[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_bold.sendoff[3]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D42" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.standard.high[1]</t>
+          <t xml:space="preserve">standard_bold.sendoff[3]</t>
         </is>
       </c>
       <c r="E42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今夜、あんたの組ごと踏み潰す。覚悟しときな</t>
+          <t xml:space="preserve">話が早くて助かります。行ってきます。</t>
         </is>
       </c>
     </row>
     <row r="43" ht="40" customHeight="1">
       <c r="A43" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A.bold.standard.high[2]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_bold.win[1]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D43" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.standard.high[2]</t>
+          <t xml:space="preserve">standard_bold.win[1]</t>
         </is>
       </c>
       <c r="E43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選手全員、リングに上げな。一人残らず叩く</t>
+          <t xml:space="preserve">勝ちました! ……言った通りでしょう。</t>
         </is>
       </c>
     </row>
     <row r="44" ht="40" customHeight="1">
       <c r="A44" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A.bold.standard.mid[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_bold.win[2]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A</t>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
         </is>
       </c>
       <c r="D44" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold.standard.mid[1]</t>
+          <t xml:space="preserve">standard_bold.win[2]</t>
         </is>
       </c>
       <c r="E44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日が、あんたんとこの分水嶺だ</t>
+          <t xml:space="preserve">勝ちました。社長、ありがとうございました。</t>
         </is>
       </c>
     </row>
     <row r="45" ht="40" customHeight="1">
       <c r="A45" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B.bold.standard.high[1]</t>
+          <t xml:space="preserve">CHALLENGE_LINES.standard_bold.win[3]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+          <t xml:space="preserve">src/data.js</t>
         </is>
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">CHALLENGE_LINES</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_bold.win[3]</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">やりました。……次も、任せてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="40" customHeight="1">
+      <c r="A46" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_bold._accept[1]</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_bold._accept[1]</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">望むところ。よく言ってくれました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="40" customHeight="1">
+      <c r="A47" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_bold._accept[2]</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_bold._accept[2]</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">待ってましたよ、そういうの。受けます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="40" customHeight="1">
+      <c r="A48" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_bold._accept[3]</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_bold._accept[3]</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">いいですね。全部まとめて受け止めます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="40" customHeight="1">
+      <c r="A49" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_bold.draw[1]</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_bold.draw[1]</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">決めきれなかった。……つまらない終わり方だ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="40" customHeight="1">
+      <c r="A50" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_bold.draw[2]</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_bold.draw[2]</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">決着つかず? そんなの求めてません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="40" customHeight="1">
+      <c r="A51" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_bold.draw[3]</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_bold.draw[3]</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まだ足りない。もう一度、名前を呼んでください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="40" customHeight="1">
+      <c r="A52" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_bold.lose[1]</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_bold.lose[1]</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">持っていかれました。……大口叩いた分、痛い。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="40" customHeight="1">
+      <c r="A53" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_bold.lose[2]</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_bold.lose[2]</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あなたが上でした。認めます、今日は。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="40" customHeight="1">
+      <c r="A54" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_bold.lose[3]</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_bold.lose[3]</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">負けました。次はこうはいきませんから。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="40" customHeight="1">
+      <c r="A55" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_bold.win[1]</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_bold.win[1]</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ほら、言った通りでしょう。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="40" customHeight="1">
+      <c r="A56" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_bold.win[2]</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_bold.win[2]</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">引く気なんて、最初からなかったので。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="40" customHeight="1">
+      <c r="A57" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS.standard_bold.win[3]</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHALLENGE_REQUEST_OPPONENT_REACTIONS</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard_bold.win[3]</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">04 挑戦試合(直訴・遠征)</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝ちました。……次、いつでもどうぞ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="40" customHeight="1">
+      <c r="A58" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長、私たちのメンバーのこと、もう少しだけ大事にしてもらえませんか。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="40" customHeight="1">
+      <c r="A59" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長、次の興行のメイン、私たちに任せてもらえませんか。実力で示します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="40" customHeight="1">
+      <c r="A60" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長、私たちのメンバーの待遇、もう一度見直してもらえませんか。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="40" customHeight="1">
+      <c r="A61" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">社長、私の貢献、ちゃんと評価してもらえてますか。確認させてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="40" customHeight="1">
+      <c r="A62" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ありがとうございます。その言葉だけで、十分です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="40" customHeight="1">
+      <c r="A63" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…そうですか。失礼しました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="40" customHeight="1">
+      <c r="A64" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…そういう形ですか。心遣い、ありがたく受け取ります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="40" customHeight="1">
+      <c r="A65" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ありがとうございます。期待に応えます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="40" customHeight="1">
+      <c r="A66" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…そうですか。わかりました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="40" customHeight="1">
+      <c r="A67" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…そういうことですか。心遣いはありがたく。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="40" customHeight="1">
+      <c r="A68" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">助かります。みんなにも、ちゃんと伝えます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="40" customHeight="1">
+      <c r="A69" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…そうですか。次の機会に、また話します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="40" customHeight="1">
+      <c r="A70" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ご配慮、ありがとうございます。お金の話、しちゃってすみません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="40" customHeight="1">
+      <c r="A71" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ありがとうございます。励みになります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="40" customHeight="1">
+      <c r="A72" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…そうですか。失礼しました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="40" customHeight="1">
+      <c r="A73" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ご配慮ありがとうございます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="40" customHeight="1">
+      <c r="A74" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…そうですね、配慮が足りませんでした。次は声をかけます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="40" customHeight="1">
+      <c r="A75" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ありがとうございます。仲間内の付き合いも大事ですから。</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="40" customHeight="1">
+      <c r="A76" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…そうですね、注意します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="40" customHeight="1">
+      <c r="A77" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ありがとうございます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="40" customHeight="1">
+      <c r="A78" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…そうですか。営業に響くなら、線は引きます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="40" customHeight="1">
+      <c r="A79" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ありがとうございます。これも仕事のうちです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="40" customHeight="1">
+      <c r="A80" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ご迷惑おかけしました。明日から、ちゃんと出ます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="40" customHeight="1">
+      <c r="A81" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ありがとうございます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="40" customHeight="1">
+      <c r="A82" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…そっちですか。…私たちのメンバーをちゃんと見てくれて、感謝します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="40" customHeight="1">
+      <c r="A83" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…大丈夫だと思ってましたが、…少しだけ、休ませてもらいます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="40" customHeight="1">
+      <c r="A84" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…大丈夫です。問題ありません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="40" customHeight="1">
+      <c r="A85" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…そっちですか。…メンバーにフォローを入れてくださると、私も楽になります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="40" customHeight="1">
+      <c r="A86" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…そうですか。私からも、メンバーに話します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="40" customHeight="1">
+      <c r="A87" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ありがとうございます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="40" customHeight="1">
+      <c r="A88" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ご配慮、ありがとうございます。下の子にも声をかけてくださって。</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="40" customHeight="1">
+      <c r="A89" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…わかりました。気をつけます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="40" customHeight="1">
+      <c r="A90" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">（黙ったまま、視線をそらした）</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="40" customHeight="1">
+      <c r="A91" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ご配慮、ありがとうございます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="40" customHeight="1">
+      <c r="A92" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…わかりました。怪我させちゃ意味がないですもんね。少し、緩めます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="40" customHeight="1">
+      <c r="A93" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ありがとうございます。このままで大丈夫です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="40" customHeight="1">
+      <c r="A94" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">F07_LINES</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…そっちですか。下の子の負担を見てくださって、ありがとうございます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="40" customHeight="1">
+      <c r="A95" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F02_LINES.bold.attack.standard</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.attack.standard</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">もう、同じ場所には立てない</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="40" customHeight="1">
+      <c r="A96" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F02_LINES.bold.defend.standard</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bold.defend.standard</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">上等だ。受けて立つ</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="40" customHeight="1">
+      <c r="A97" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あの人のやり方、もう付き合いきれねえわ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="40" customHeight="1">
+      <c r="A98" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES.standard.bold[2]</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F05_DISSIDENT_LINES</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold[2]</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あたしらの声なんて、届いてないんだよ。上は。</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="40" customHeight="1">
+      <c r="A99" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あんた、意外と悪くないじゃん。ちょっと見直したわ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="40" customHeight="1">
+      <c r="A100" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES.standard.bold[2]</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F06_AMBIENT_LINES</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold[2]</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まあ、あの日のことは、忘れてやるよ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="40" customHeight="1">
+      <c r="A101" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_LEADER_LINES.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_LEADER_LINES</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">もう言葉はいらない。リングで片をつけるだけだ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="40" customHeight="1">
+      <c r="A102" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_LEADER_LINES.standard.bold[2]</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_LEADER_LINES</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold[2]</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あたしが勝つ。それだけの話。</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="40" customHeight="1">
+      <c r="A103" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.standard.bold.hp_high[1]</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold.hp_high[1]</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……次は、こうはいかねえ。覚えとけよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="40" customHeight="1">
+      <c r="A104" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.standard.bold.hp_high[2]</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold.hp_high[2]</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">今日のとこは、あたしの負けだ。だが、組は潰れねえ</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="40" customHeight="1">
+      <c r="A105" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.standard.bold.hp_low[1]</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold.hp_low[1]</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……っ……</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="40" customHeight="1">
+      <c r="A106" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.standard.bold.hp_low[2]</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold.hp_low[2]</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">（呻き声）</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="40" customHeight="1">
+      <c r="A107" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.standard.bold.hp_mid[1]</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold.hp_mid[1]</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……くそっ……まだ、終わりじゃ……</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="40" customHeight="1">
+      <c r="A108" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES.standard.bold.hp_mid[2]</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_LOSER_LINES</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold.hp_mid[2]</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……次、絶対に……</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="40" customHeight="1">
+      <c r="A109" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.standard.bold.high[1]</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold.high[1]</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">これがあんたの組の限界か？　次は誰だ</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="40" customHeight="1">
+      <c r="A110" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.standard.bold.high[2]</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold.high[2]</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">見たかよ。これが格の違いってやつだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="40" customHeight="1">
+      <c r="A111" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.standard.bold.high[3]</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold.high[3]</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">もう二度と、あたしらに楯突くんじゃねえぞ</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="40" customHeight="1">
+      <c r="A112" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.standard.bold.low[1]</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold.low[1]</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……勝った。それだけだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="40" customHeight="1">
+      <c r="A113" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.standard.bold.mid[1]</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold.mid[1]</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……今日は、あたしの勝ちだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="40" customHeight="1">
+      <c r="A114" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES.standard.bold.mid[2]</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_POST_MATCH_WINNER_LINES</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold.mid[2]</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">次の番、誰でも構わねえ。来な</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="40" customHeight="1">
+      <c r="A115" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.standard.bold.high[1]</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold.high[1]</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あんたんとこの組、今夜で終わりだ。覚悟しときな</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="40" customHeight="1">
+      <c r="A116" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.standard.bold.high[2]</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold.high[2]</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あたしの背中にいる連中のためにも、今日は退かない</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="40" customHeight="1">
+      <c r="A117" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.standard.bold.high[3]</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold.high[3]</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あんた一人潰せば、組ごと崩れる――遠慮しねえぞ</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="40" customHeight="1">
+      <c r="A118" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.standard.bold.low[1]</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold.low[1]</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……来なよ。最後まで付き合ってやる</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="40" customHeight="1">
+      <c r="A119" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.standard.bold.mid[1]</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold.mid[1]</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">今日は決着つけにきた。話はリングの上で</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="40" customHeight="1">
+      <c r="A120" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A.standard.bold.mid[2]</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_A</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold.mid[2]</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">これ以上、あんたんとこに好き勝手はさせない</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="40" customHeight="1">
+      <c r="A121" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.standard.bold.high[1]</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold.high[1]</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">上等だ。やってもらおうじゃねえか</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="40" customHeight="1">
+      <c r="A122" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.standard.bold.high[2]</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold.high[2]</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">受けて立つ。あたしんとこの組も、舐められっぱなしじゃ終われねえ</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="40" customHeight="1">
+      <c r="A123" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.standard.bold.high[3]</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold.high[3]</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">そっちが来るなら、こっちも全力で潰しにいく</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="40" customHeight="1">
+      <c r="A124" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.standard.bold.low[1]</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold.low[1]</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……分かった。受けるよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="40" customHeight="1">
+      <c r="A125" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.standard.bold.mid[1]</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold.mid[1]</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">いいだろう。来な</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="40" customHeight="1">
+      <c r="A126" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B.standard.bold.mid[2]</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F08_PRE_MATCH_LINES_B</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold.mid[2]</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あんたの覚悟、リングで見せてみろよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="40" customHeight="1">
+      <c r="A127" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_ENDING_LOSE_LINES.standard.bold.high[1]</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F09_ENDING_LOSE_LINES</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold.high[1]</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……負けた。受け止める。次は必ず取り返す</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="40" customHeight="1">
+      <c r="A128" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_ENDING_LOSE_LINES.standard.bold.high[2]</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F09_ENDING_LOSE_LINES</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold.high[2]</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">今夜のは、覚えとく。次に返すから</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="40" customHeight="1">
+      <c r="A129" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_ENDING_WIN_LINES.standard.bold.high[1]</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F09_ENDING_WIN_LINES</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold.high[1]</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝ち越した。今夜は、うちの組の夜だ</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="40" customHeight="1">
+      <c r="A130" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_ENDING_WIN_LINES.standard.bold.high[2]</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F09_ENDING_WIN_LINES</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold.high[2]</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">見たか。これがうちの組の力だ</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="40" customHeight="1">
+      <c r="A131" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_MATCH_POST_LOSE_LINES.standard.bold.high[1]</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F09_MATCH_POST_LOSE_LINES</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold.high[1]</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……ちっ。次の奴で取り返してくれ</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="40" customHeight="1">
+      <c r="A132" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_MATCH_POST_WIN_LINES.standard.bold.high[1]</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F09_MATCH_POST_WIN_LINES</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold.high[1]</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">1勝。あと何回続くかな</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="40" customHeight="1">
+      <c r="A133" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_MATCH_POST_WIN_LINES.standard.bold.mid[1]</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F09_MATCH_POST_WIN_LINES</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold.mid[1]</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まだ序章だぜ</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="40" customHeight="1">
+      <c r="A134" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_MATCH_PRE_LINES.standard.bold.high[1]</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F09_MATCH_PRE_LINES</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold.high[1]</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">順番が来たね</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="40" customHeight="1">
+      <c r="A135" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_MATCH_PRE_LINES.standard.bold.mid[1]</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F09_MATCH_PRE_LINES</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold.mid[1]</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">先に来な</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="40" customHeight="1">
+      <c r="A136" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A.standard.bold.high[1]</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold.high[1]</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">今夜、あんたの組ごと踏み潰す。覚悟しときな</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="40" customHeight="1">
+      <c r="A137" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A.standard.bold.high[2]</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold.high[2]</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">選手全員、リングに上げな。一人残らず叩く</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="40" customHeight="1">
+      <c r="A138" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A.standard.bold.mid[1]</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_A</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold.mid[1]</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">今日が、あんたんとこの分水嶺だ</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="40" customHeight="1">
+      <c r="A139" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FACTION_F09_OPENING_LINES_B.standard.bold.high[1]</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">FACTION_F09_OPENING_LINES_B</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">bold.standard.high[1]</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">07 派閥イベント</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr" s="3">
+      <c r="D139" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold.high[1]</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">上等だ。組ごと潰し合おうじゃねえか</t>
         </is>
       </c>
     </row>
+    <row r="140" ht="40" customHeight="1">
+      <c r="A140" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES.standard.bold.hp_high[1]</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold.hp_high[1]</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……次はねえぞ。覚えとけ</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="40" customHeight="1">
+      <c r="A141" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES.standard.bold.hp_high[2]</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold.hp_high[2]</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ふん、今日は譲ってやる。それだけだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="40" customHeight="1">
+      <c r="A142" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES.standard.bold.hp_low[1]</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold.hp_low[1]</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……強かった</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="40" customHeight="1">
+      <c r="A143" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES.standard.bold.hp_mid[1]</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_LOSER_LINES</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold.hp_mid[1]</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">……認めるしかねえな、今日は</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="40" customHeight="1">
+      <c r="A144" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_WINNER_LINES.standard.bold.high[1]</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_WINNER_LINES</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold.high[1]</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">これで、あたしが先頭に立つ。文句あるか</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="40" customHeight="1">
+      <c r="A145" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_WINNER_LINES.standard.bold.high[2]</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_POST_WINNER_LINES</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold.high[2]</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">後ろのみんな、ついて来な。ここからだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="40" customHeight="1">
+      <c r="A146" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES.standard.bold.high[1]</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold.high[1]</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">今夜、あんたの座は降ろさせてもらう</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="40" customHeight="1">
+      <c r="A147" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES.standard.bold.high[2]</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold.high[2]</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ずっと、あんたの背中ばっか見てきた。今日で終わりにする</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="40" customHeight="1">
+      <c r="A148" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES.standard.bold.high[3]</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_CHALLENGER_LINES</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold.high[3]</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">リーダー――その肩書、重そうだな。譲ってもらうぜ</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="40" customHeight="1">
+      <c r="A149" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_LEADER_LINES.standard.bold.high[1]</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_LEADER_LINES</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold.high[1]</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">上等。叩き潰してやる</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="40" customHeight="1">
+      <c r="A150" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_LEADER_LINES.standard.bold.high[2]</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data-faction-dialogue.js</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">INTERNAL_CHALLENGE_PRE_LEADER_LINES</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold.high[2]</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">07 派閥イベント</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">若いの、その意気だけは買ってやる。リングは別だがな</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H45"/>
+  <autoFilter ref="A1:H150"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/標準×強気.xlsx
+++ b/セリフ編集/キャラタイプ別/標準×強気.xlsx
@@ -193,7 +193,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -205,7 +205,7 @@
     <row r="1">
       <c r="A1" t="inlineStr" s="11">
         <is>
-          <t xml:space="preserve">このタイプ(標準×強気)に該当するキャラクター: 8名</t>
+          <t xml:space="preserve">このタイプ(標準×強気)に該当するキャラクター: 7名</t>
         </is>
       </c>
     </row>
@@ -340,12 +340,12 @@
     <row r="9">
       <c r="A9" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">南谷杏</t>
+          <t xml:space="preserve">赤羽あんな</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Allround</t>
+          <t xml:space="preserve">Aerial</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
@@ -362,12 +362,12 @@
     <row r="10">
       <c r="A10" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">赤羽あんな</t>
+          <t xml:space="preserve">木村レイカ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Aerial</t>
+          <t xml:space="preserve">Grappler</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="2">
@@ -376,28 +376,6 @@
         </is>
       </c>
       <c r="D10" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">ファンサービス</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">木村レイカ</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Grappler</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">Neutral</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">負けず嫌い</t>
         </is>
@@ -411,7 +389,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H569"/>
+  <dimension ref="A1:H571"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -654,7 +632,7 @@
       </c>
       <c r="F7" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">見せてあげる…わたしの全力！</t>
+          <t xml:space="preserve">見せてあげる…私の全力！</t>
         </is>
       </c>
     </row>
@@ -718,7 +696,7 @@
       </c>
       <c r="F9" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（ここからが、あたしの時間！）</t>
+          <t xml:space="preserve">（ここからが、私の時間！）</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1016,7 @@
       </c>
       <c r="F19" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">待ってたぞ、この日を</t>
+          <t xml:space="preserve">待ってたよ、この日を</t>
         </is>
       </c>
     </row>
@@ -1262,7 +1240,7 @@
       </c>
       <c r="F26" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしの勝ち！</t>
+          <t xml:space="preserve">私の勝ち！</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1976,7 @@
       </c>
       <c r="F49" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">合わせろ、いくぞ！</t>
+          <t xml:space="preserve">合わせて、行くぞ！</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2136,7 @@
       </c>
       <c r="F54" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそっ…{partner}、悪い。私のミスだ。次は絶対だ。</t>
+          <t xml:space="preserve">くそっ…{partner}、ごめん。私のミスよ。次は絶対に取る。</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2904,7 @@
       </c>
       <c r="F78" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">逃がさないよ。今日ここで決着をつけから</t>
+          <t xml:space="preserve">逃がさないよ。今日ここで決着をつけるから</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3704,7 @@
       </c>
       <c r="F103" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すみません、負けました。でも、やってよかったです。</t>
+          <t xml:space="preserve">悪いわね、負けた。でも、やってよかったよ。</t>
         </is>
       </c>
     </row>
@@ -4270,7 +4248,7 @@
       </c>
       <c r="F120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あなたが上でした。認めます、今日は。</t>
+          <t xml:space="preserve">アンタが上だった。認めるわよ、今日は。</t>
         </is>
       </c>
     </row>
@@ -4942,7 +4920,7 @@
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あたしのことが邪魔なの？ はっきり言いなさいよ</t>
+          <t xml:space="preserve">…邪魔になったってこと？ はっきり言いなさいよ</t>
         </is>
       </c>
     </row>
@@ -5006,7 +4984,7 @@
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あたしがいなくなったら、この団体は終わりよ</t>
+          <t xml:space="preserve">私がいなくなったら、この団体は終わりよ</t>
         </is>
       </c>
     </row>
@@ -5038,7 +5016,7 @@
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あたしの時代だったよね？誰も文句言えないでしょ？</t>
+          <t xml:space="preserve">私の時代だったよね？誰も文句言えないでしょ？</t>
         </is>
       </c>
     </row>
@@ -6070,7 +6048,7 @@
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、私たちのメンバーのこと、もう少しだけ大事にしてもらえませんか。</t>
+          <t xml:space="preserve">社長、うちのメンバーのこと、もう少し大事にしてくれない？</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6208,7 @@
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうですか。失礼しました。</t>
+          <t xml:space="preserve">…そう。出すぎたこと言ったわね。</t>
         </is>
       </c>
     </row>
@@ -6326,7 +6304,7 @@
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうですか。わかりました。</t>
+          <t xml:space="preserve">…そう。わかった、今は引くわよ。</t>
         </is>
       </c>
     </row>
@@ -6454,7 +6432,7 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご配慮、ありがとうございます。お金の話、しちゃってすみません。</t>
+          <t xml:space="preserve">…ありがと、社長。お金の話は、言うべきだと思ったから</t>
         </is>
       </c>
     </row>
@@ -6518,7 +6496,7 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうですか。失礼しました。</t>
+          <t xml:space="preserve">…そっか。悪かったわね、無理言って。</t>
         </is>
       </c>
     </row>
@@ -6550,7 +6528,7 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご配慮ありがとうございます。</t>
+          <t xml:space="preserve">…その心配りは、ありがたく受け取るわ。</t>
         </is>
       </c>
     </row>
@@ -6582,7 +6560,7 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうですね、配慮が足りませんでした。次は声をかけます。</t>
+          <t xml:space="preserve">…そうね、気が回ってなかった。次は声かけるわよ。</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6592,7 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。仲間内の付き合いも大事ですから。</t>
+          <t xml:space="preserve">…そう言ってくれると助かる。仲間の付き合いも大事だからね。</t>
         </is>
       </c>
     </row>
@@ -6646,7 +6624,7 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そうですね、注意します。</t>
+          <t xml:space="preserve">…そうね、そこは改めるわ。</t>
         </is>
       </c>
     </row>
@@ -6678,7 +6656,7 @@
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。</t>
+          <t xml:space="preserve">…恩に着るわよ。</t>
         </is>
       </c>
     </row>
@@ -6742,7 +6720,7 @@
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。これも仕事のうちです。</t>
+          <t xml:space="preserve">…どうも。これも仕事のうちよ。</t>
         </is>
       </c>
     </row>
@@ -6774,7 +6752,7 @@
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご迷惑おかけしました。明日から、ちゃんと出ます。</t>
+          <t xml:space="preserve">…迷惑かけたわね。明日から、ちゃんと出るわよ。</t>
         </is>
       </c>
     </row>
@@ -6806,7 +6784,7 @@
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。</t>
+          <t xml:space="preserve">…礼を言うわ、素直に。</t>
         </is>
       </c>
     </row>
@@ -6838,7 +6816,7 @@
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そっちですか。…私たちのメンバーをちゃんと見てくれて、感謝します。</t>
+          <t xml:space="preserve">…そっちなんだ。…うちの子たちをちゃんと見ててくれて、感謝するわよ。</t>
         </is>
       </c>
     </row>
@@ -6870,7 +6848,7 @@
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…大丈夫だと思ってましたが、…少しだけ、休ませてもらいます。</t>
+          <t xml:space="preserve">…平気なつもりだったけど、…少しだけ、休ませてもらうわ。</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6912,7 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そっちですか。…メンバーにフォローを入れてくださると、私も楽になります。</t>
+          <t xml:space="preserve">…あぁ、そっち。…メンバーにフォロー入れてくれるなら、私も楽になる。</t>
         </is>
       </c>
     </row>
@@ -6998,7 +6976,7 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。</t>
+          <t xml:space="preserve">…ありがたいわね、それは。</t>
         </is>
       </c>
     </row>
@@ -7030,7 +7008,7 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご配慮、ありがとうございます。下の子にも声をかけてくださって。</t>
+          <t xml:space="preserve">…下の子にも声かけてくれたのね。…そういうの、嬉しいわ。</t>
         </is>
       </c>
     </row>
@@ -7062,7 +7040,7 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…わかりました。気をつけます。</t>
+          <t xml:space="preserve">…わかった。やりすぎないようにする。</t>
         </is>
       </c>
     </row>
@@ -7126,7 +7104,7 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ご配慮、ありがとうございます。</t>
+          <t xml:space="preserve">…気遣いは、ちゃんと届いてるわよ。</t>
         </is>
       </c>
     </row>
@@ -7158,7 +7136,7 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…わかりました。怪我させちゃ意味がないですもんね。少し、緩めます。</t>
+          <t xml:space="preserve">…わかった。怪我させたら意味ないもんね。少し、緩めるわ。</t>
         </is>
       </c>
     </row>
@@ -7190,7 +7168,7 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとうございます。このままで大丈夫です。</t>
+          <t xml:space="preserve">…心配いらないわよ、社長。このままで行く</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7200,7 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…そっちですか。下の子の負担を見てくださって、ありがとうございます。</t>
+          <t xml:space="preserve">…そこ見てたんだ。下の子の負担まで気にしてくれるなんて。…悪くないわね、社長。</t>
         </is>
       </c>
     </row>
@@ -7286,7 +7264,7 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">上等だ。受けて立つ</t>
+          <t xml:space="preserve">上等よ。受けて立つわ</t>
         </is>
       </c>
     </row>
@@ -7318,7 +7296,7 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人のやり方、もう付き合いきれねえわ。</t>
+          <t xml:space="preserve">あの人のやり方、もう付き合いきれないわ。</t>
         </is>
       </c>
     </row>
@@ -7350,7 +7328,7 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あたしらの声なんて、届いてないんだよ。上は。</t>
+          <t xml:space="preserve">こっちの声なんて、届いてないんだよ。上は。</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7456,7 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あたしが勝つ。それだけの話。</t>
+          <t xml:space="preserve">私が勝つ。それだけの話。</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7488,7 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次は、こうはいかねえ。覚えとけよ</t>
+          <t xml:space="preserve">……次は、こうはいかないわよ。覚えておきなさい</t>
         </is>
       </c>
     </row>
@@ -7542,7 +7520,7 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日のとこは、あたしの負けだ。だが、組は潰れねえ</t>
+          <t xml:space="preserve">今日のところは、私の負け。でも、この組は潰れないわ</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7712,7 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">見たかよ。これが格の違いってやつだ</t>
+          <t xml:space="preserve">見た？ これが格の違いってやつよ</t>
         </is>
       </c>
     </row>
@@ -7766,7 +7744,7 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう二度と、あたしらに楯突くんじゃねえぞ</t>
+          <t xml:space="preserve">もう二度と、こっちに楯突かないことね</t>
         </is>
       </c>
     </row>
@@ -7830,7 +7808,7 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……今日は、あたしの勝ちだ</t>
+          <t xml:space="preserve">……今日は、私の勝ち</t>
         </is>
       </c>
     </row>
@@ -7862,7 +7840,7 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次の番、誰でも構わねえ。来な</t>
+          <t xml:space="preserve">次の番、誰でも構わないわ。来なさいよ</t>
         </is>
       </c>
     </row>
@@ -7894,7 +7872,7 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あんたんとこの組、今夜で終わりだ。覚悟しときな</t>
+          <t xml:space="preserve">アンタんとこの組、今夜で終わりよ。覚悟しなさい</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7904,7 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あたしの背中にいる連中のためにも、今日は退かない</t>
+          <t xml:space="preserve">背中にいる子たちのためにも、今日は退かない</t>
         </is>
       </c>
     </row>
@@ -7958,7 +7936,7 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あんた一人潰せば、組ごと崩れる――遠慮しねえぞ</t>
+          <t xml:space="preserve">アンタ一人潰せば、組ごと崩れる――遠慮はしないわよ</t>
         </is>
       </c>
     </row>
@@ -8086,7 +8064,7 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">上等だ。やってもらおうじゃねえか</t>
+          <t xml:space="preserve">面白いじゃない。やってもらおうじゃないの</t>
         </is>
       </c>
     </row>
@@ -8118,7 +8096,7 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">受けて立つ。あたしんとこの組も、舐められっぱなしじゃ終われねえ</t>
+          <t xml:space="preserve">受けて立つわ。こっちの組も、舐められっぱなしじゃ終われない</t>
         </is>
       </c>
     </row>
@@ -8214,7 +8192,7 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いいだろう。来な</t>
+          <t xml:space="preserve">いいわよ。かかってきなさい</t>
         </is>
       </c>
     </row>
@@ -8246,7 +8224,7 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あんたの覚悟、リングで見せてみろよ</t>
+          <t xml:space="preserve">アンタの覚悟、リングで見せてもらうわよ</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8352,7 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">見たか。これがうちの組の力だ</t>
+          <t xml:space="preserve">今の、見えた？ これがうちの組の力よ</t>
         </is>
       </c>
     </row>
@@ -8406,7 +8384,7 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……ちっ。次の奴で取り返してくれ</t>
+          <t xml:space="preserve">……ちっ。次の子、取り返してちょうだい</t>
         </is>
       </c>
     </row>
@@ -8470,7 +8448,7 @@
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ序章だぜ</t>
+          <t xml:space="preserve">まだ序章よ</t>
         </is>
       </c>
     </row>
@@ -8566,7 +8544,7 @@
       </c>
       <c r="F254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今夜、あんたの組ごと踏み潰す。覚悟しときな</t>
+          <t xml:space="preserve">今夜、アンタの組ごと踏み潰す。覚悟はできてるわね</t>
         </is>
       </c>
     </row>
@@ -8598,7 +8576,7 @@
       </c>
       <c r="F255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選手全員、リングに上げな。一人残らず叩く</t>
+          <t xml:space="preserve">選手全員、リングに上げなさい。一人残らず叩く</t>
         </is>
       </c>
     </row>
@@ -8662,7 +8640,7 @@
       </c>
       <c r="F257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">上等だ。組ごと潰し合おうじゃねえか</t>
+          <t xml:space="preserve">上等よ。組ごと潰し合おうじゃない</t>
         </is>
       </c>
     </row>
@@ -8694,7 +8672,7 @@
       </c>
       <c r="F258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……次はねえぞ。覚えとけ</t>
+          <t xml:space="preserve">……次はないわ。忘れないことね</t>
         </is>
       </c>
     </row>
@@ -8790,7 +8768,7 @@
       </c>
       <c r="F261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……認めるしかねえな、今日は</t>
+          <t xml:space="preserve">……認めるしかないわね、今日は</t>
         </is>
       </c>
     </row>
@@ -8822,7 +8800,7 @@
       </c>
       <c r="F262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これで、あたしが先頭に立つ。文句あるか</t>
+          <t xml:space="preserve">これで、私が先頭に立つ。文句ある？</t>
         </is>
       </c>
     </row>
@@ -8950,7 +8928,7 @@
       </c>
       <c r="F266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">リーダー――その肩書、重そうだな。譲ってもらうぜ</t>
+          <t xml:space="preserve">リーダー――その肩書、重そうね。譲ってもらうわよ</t>
         </is>
       </c>
     </row>
@@ -9014,7 +8992,7 @@
       </c>
       <c r="F268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">若いの、その意気だけは買ってやる。リングは別だがな</t>
+          <t xml:space="preserve">新人さん、その意気だけは買ってあげる。リングは別だけどね</t>
         </is>
       </c>
     </row>
@@ -9110,7 +9088,7 @@
       </c>
       <c r="F271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（…体が勝手に動く。これが、あたしの限界の先——）</t>
+          <t xml:space="preserve">（…体が勝手に動く。これが、私の限界の先——）</t>
         </is>
       </c>
     </row>
@@ -9622,7 +9600,7 @@
       </c>
       <c r="F287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">期待してろ。最高の舞台を見せてやるから</t>
+          <t xml:space="preserve">期待してていいわよ。最高の舞台を見せてあげる</t>
         </is>
       </c>
     </row>
@@ -9750,7 +9728,7 @@
       </c>
       <c r="F291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…何やってんだわたし</t>
+          <t xml:space="preserve">…何やってんだ私</t>
         </is>
       </c>
     </row>
@@ -9782,7 +9760,7 @@
       </c>
       <c r="F292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けた？ わたしが？ …嘘でしょ</t>
+          <t xml:space="preserve">負けた？ 私が？ …嘘でしょ</t>
         </is>
       </c>
     </row>
@@ -9846,7 +9824,7 @@
       </c>
       <c r="F294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あたしが…怯えてる？ そんなはずない！</t>
+          <t xml:space="preserve">私が…怯えてる？ そんなはずない！</t>
         </is>
       </c>
     </row>
@@ -9885,7 +9863,7 @@
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.standard.bold[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.standard.bold[1]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9900,7 +9878,7 @@
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.standard.bold[1]</t>
+          <t xml:space="preserve">autumnWarChampion.standard.bold[1]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr" s="2">
@@ -9910,14 +9888,14 @@
       </c>
       <c r="F296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力と全力でぶつかった。いい時間だったよ。</t>
+          <t xml:space="preserve">対抗戦を制したのはうちだ。覚えておけ。</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.standard.bold[2]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.standard.bold[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9932,7 +9910,7 @@
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.standard.bold[2]</t>
+          <t xml:space="preserve">bestMatch.standard.bold[1]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr" s="2">
@@ -9942,14 +9920,14 @@
       </c>
       <c r="F297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの試合で出し惜しみなんてできなかった。全部出し切ったよ。</t>
+          <t xml:space="preserve">全力と全力でぶつかった。いい時間だったよ。</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.standard.bold[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.standard.bold[2]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9964,7 +9942,7 @@
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.bold[1]</t>
+          <t xml:space="preserve">bestMatch.standard.bold[2]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr" s="2">
@@ -9974,14 +9952,14 @@
       </c>
       <c r="F298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最強。これが私。</t>
+          <t xml:space="preserve">あの試合で出し惜しみなんてできなかった。全部出し切ったよ。</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.standard.bold[2]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.standard.bold[1]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9996,7 +9974,7 @@
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.bold[2]</t>
+          <t xml:space="preserve">champion.standard.bold[1]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr" s="2">
@@ -10006,14 +9984,14 @@
       </c>
       <c r="F299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">挑戦したいヤツは何人でも来なよ。結果は変わらないけどね！</t>
+          <t xml:space="preserve">最強。これが私。</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.standard.bold[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.standard.bold[2]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -10028,7 +10006,7 @@
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.standard.bold[1]</t>
+          <t xml:space="preserve">champion.standard.bold[2]</t>
         </is>
       </c>
       <c r="E300" t="inlineStr" s="2">
@@ -10038,14 +10016,14 @@
       </c>
       <c r="F300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全盛期はいつだって？「いつだって」だよ！</t>
+          <t xml:space="preserve">挑戦したいヤツは何人でも来なよ。結果は変わらないけどね！</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.standard.bold[2]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.standard.bold[1]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -10060,7 +10038,7 @@
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.standard.bold[2]</t>
+          <t xml:space="preserve">hallOfFame.standard.bold[1]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr" s="2">
@@ -10070,14 +10048,14 @@
       </c>
       <c r="F301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やり残したことなんて何もないよ。そういう私だからこの場に立てるんでしょ？</t>
+          <t xml:space="preserve">全盛期はいつだって？「いつだって」だよ！</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.standard.bold[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.standard.bold[2]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -10092,7 +10070,7 @@
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.standard.bold[1]</t>
+          <t xml:space="preserve">hallOfFame.standard.bold[2]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr" s="2">
@@ -10102,14 +10080,14 @@
       </c>
       <c r="F302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">リングの外でも全力でやってきた結果です！</t>
+          <t xml:space="preserve">やり残したことなんて何もないよ。そういう私だからこの場に立てるんでしょ？</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mediaAward.standard.bold[2]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.standard.bold[1]</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -10124,7 +10102,7 @@
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mediaAward.standard.bold[2]</t>
+          <t xml:space="preserve">mediaAward.standard.bold[1]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr" s="2">
@@ -10134,14 +10112,14 @@
       </c>
       <c r="F303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こういう賞、めちゃくちゃ嬉しいんですよ！</t>
+          <t xml:space="preserve">リングの外でも全力でやってきた結果です！</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.standard.bold[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mediaAward.standard.bold[2]</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -10156,7 +10134,7 @@
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.standard.bold[1]</t>
+          <t xml:space="preserve">mediaAward.standard.bold[2]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr" s="2">
@@ -10166,14 +10144,14 @@
       </c>
       <c r="F304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">誰よりも強かったでしょ？数字にも出てるし。</t>
+          <t xml:space="preserve">こういう賞、めちゃくちゃ嬉しいんですよ！</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.standard.bold[2]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.standard.bold[1]</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -10188,7 +10166,7 @@
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.standard.bold[2]</t>
+          <t xml:space="preserve">mvp.standard.bold[1]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr" s="2">
@@ -10198,14 +10176,14 @@
       </c>
       <c r="F305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この一年は、負ける気がしなかったね。全試合見てたでしょ？どうだった？</t>
+          <t xml:space="preserve">誰よりも強かったでしょ？数字にも出てるし。</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.standard.bold[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.standard.bold[2]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -10220,7 +10198,7 @@
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.standard.bold[1]</t>
+          <t xml:space="preserve">mvp.standard.bold[2]</t>
         </is>
       </c>
       <c r="E306" t="inlineStr" s="2">
@@ -10230,14 +10208,14 @@
       </c>
       <c r="F306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">新人王？ 通過点でしょ。来年はMVPを狙うからね</t>
+          <t xml:space="preserve">この一年は、負ける気がしなかったね。全試合見てたでしょ？どうだった？</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.standard.bold[2]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.standard.bold[1]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -10252,7 +10230,7 @@
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.standard.bold[2]</t>
+          <t xml:space="preserve">rookie.standard.bold[1]</t>
         </is>
       </c>
       <c r="E307" t="inlineStr" s="2">
@@ -10262,14 +10240,14 @@
       </c>
       <c r="F307" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最初から頂点しか見てない。この賞はスタートラインだよ</t>
+          <t xml:space="preserve">新人王？ 通過点でしょ。来年はMVPを狙うからね</t>
         </is>
       </c>
     </row>
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.standard.bold[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.standard.bold[2]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -10279,12 +10257,12 @@
       </c>
       <c r="C308" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.bold[1]</t>
+          <t xml:space="preserve">rookie.standard.bold[2]</t>
         </is>
       </c>
       <c r="E308" t="inlineStr" s="2">
@@ -10294,14 +10272,14 @@
       </c>
       <c r="F308" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">燃えてきたぜ、ドーム!! 全員ぶっ倒す!</t>
+          <t xml:space="preserve">最初から頂点しか見てない。この賞はスタートラインだよ</t>
         </is>
       </c>
     </row>
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.standard.bold[2]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.standard.bold[1]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10311,12 +10289,12 @@
       </c>
       <c r="C309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.bold[2]</t>
+          <t xml:space="preserve">springTagChampion.standard.bold[1]</t>
         </is>
       </c>
       <c r="E309" t="inlineStr" s="2">
@@ -10326,14 +10304,14 @@
       </c>
       <c r="F309" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここが一番いいとこだろ!? やってやんよ!</t>
+          <t xml:space="preserve">最高の相棒と獲った優勝だ。次は誰が来ても返り討ちにする。</t>
         </is>
       </c>
     </row>
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.standard.bold[3]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.standard.bold[1]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -10348,7 +10326,7 @@
       </c>
       <c r="D310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.bold[3]</t>
+          <t xml:space="preserve">standard.bold[1]</t>
         </is>
       </c>
       <c r="E310" t="inlineStr" s="2">
@@ -10358,14 +10336,14 @@
       </c>
       <c r="F310" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">観客全員、俺の試合に釘付けにしてやる!</t>
+          <t xml:space="preserve">燃えてきたよ、ドーム!! 全員ぶっ倒す!</t>
         </is>
       </c>
     </row>
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.standard.bold[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.standard.bold[2]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -10375,12 +10353,12 @@
       </c>
       <c r="C311" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.bold[1]</t>
+          <t xml:space="preserve">standard.bold[2]</t>
         </is>
       </c>
       <c r="E311" t="inlineStr" s="2">
@@ -10390,14 +10368,14 @@
       </c>
       <c r="F311" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やったぜ!! ドーム満員だ!! うおおおお!</t>
+          <t xml:space="preserve">ここが一番いいとこでしょ!? やってやるわよ!</t>
         </is>
       </c>
     </row>
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.standard.bold[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.standard.bold[3]</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10407,12 +10385,12 @@
       </c>
       <c r="C312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.bold[2]</t>
+          <t xml:space="preserve">standard.bold[3]</t>
         </is>
       </c>
       <c r="E312" t="inlineStr" s="2">
@@ -10422,14 +10400,14 @@
       </c>
       <c r="F312" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全員立ち上がってくれてたぜ!! 最高だ!!</t>
+          <t xml:space="preserve">観客全員、この試合に釘付けにしてみせる!</t>
         </is>
       </c>
     </row>
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.standard.bold[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.standard.bold[1]</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10444,7 +10422,7 @@
       </c>
       <c r="D313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.bold[3]</t>
+          <t xml:space="preserve">standard.bold[1]</t>
         </is>
       </c>
       <c r="E313" t="inlineStr" s="2">
@@ -10454,14 +10432,14 @@
       </c>
       <c r="F313" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次はもっと大きい舞台、作ろうぜ!!</t>
+          <t xml:space="preserve">やった!! ドーム満員だ!! うおおおお!</t>
         </is>
       </c>
     </row>
     <row r="314" ht="40" customHeight="1">
       <c r="A314" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.standard.bold[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.standard.bold[2]</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -10471,29 +10449,29 @@
       </c>
       <c r="C314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D314" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.standard.bold[1]</t>
+          <t xml:space="preserve">standard.bold[2]</t>
         </is>
       </c>
       <c r="E314" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F314" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ足りない。もっとできるはず！</t>
+          <t xml:space="preserve">全員立ち上がってくれてた!! 最高だ!!</t>
         </is>
       </c>
     </row>
     <row r="315" ht="40" customHeight="1">
       <c r="A315" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N1.standard.bold[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.standard.bold[3]</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
@@ -10503,29 +10481,29 @@
       </c>
       <c r="C315" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D315" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N1.standard.bold[2]</t>
+          <t xml:space="preserve">standard.bold[3]</t>
         </is>
       </c>
       <c r="E315" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F315" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この調子で上を目指す！</t>
+          <t xml:space="preserve">次はもっと大きい舞台、作ろう!!</t>
         </is>
       </c>
     </row>
     <row r="316" ht="40" customHeight="1">
       <c r="A316" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.standard.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.standard.bold[1]</t>
         </is>
       </c>
       <c r="B316" t="inlineStr" s="2">
@@ -10540,7 +10518,7 @@
       </c>
       <c r="D316" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.standard.bold[1]</t>
+          <t xml:space="preserve">N1.standard.bold[1]</t>
         </is>
       </c>
       <c r="E316" t="inlineStr" s="2">
@@ -10550,14 +10528,14 @@
       </c>
       <c r="F316" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間がいるから頑張れる。チームって、いいよね</t>
+          <t xml:space="preserve">まだ足りない。もっとできるはず！</t>
         </is>
       </c>
     </row>
     <row r="317" ht="40" customHeight="1">
       <c r="A317" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N2.standard.bold[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N1.standard.bold[2]</t>
         </is>
       </c>
       <c r="B317" t="inlineStr" s="2">
@@ -10572,7 +10550,7 @@
       </c>
       <c r="D317" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N2.standard.bold[2]</t>
+          <t xml:space="preserve">N1.standard.bold[2]</t>
         </is>
       </c>
       <c r="E317" t="inlineStr" s="2">
@@ -10582,14 +10560,14 @@
       </c>
       <c r="F317" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒だと燃えるんだよね</t>
+          <t xml:space="preserve">この調子で上を目指す！</t>
         </is>
       </c>
     </row>
     <row r="318" ht="40" customHeight="1">
       <c r="A318" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.standard.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.standard.bold[1]</t>
         </is>
       </c>
       <c r="B318" t="inlineStr" s="2">
@@ -10604,7 +10582,7 @@
       </c>
       <c r="D318" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.standard.bold[1]</t>
+          <t xml:space="preserve">N2.standard.bold[1]</t>
         </is>
       </c>
       <c r="E318" t="inlineStr" s="2">
@@ -10614,14 +10592,14 @@
       </c>
       <c r="F318" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">大丈夫。この程度。すぐ戻るよ</t>
+          <t xml:space="preserve">仲間がいるから頑張れる。チームって、いいよね</t>
         </is>
       </c>
     </row>
     <row r="319" ht="40" customHeight="1">
       <c r="A319" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N3.standard.bold[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N2.standard.bold[2]</t>
         </is>
       </c>
       <c r="B319" t="inlineStr" s="2">
@@ -10636,7 +10614,7 @@
       </c>
       <c r="D319" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N3.standard.bold[2]</t>
+          <t xml:space="preserve">N2.standard.bold[2]</t>
         </is>
       </c>
       <c r="E319" t="inlineStr" s="2">
@@ -10646,14 +10624,14 @@
       </c>
       <c r="F319" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなんじゃ終われない</t>
+          <t xml:space="preserve">一緒だと燃えるんだよね</t>
         </is>
       </c>
     </row>
     <row r="320" ht="40" customHeight="1">
       <c r="A320" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.standard.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.standard.bold[1]</t>
         </is>
       </c>
       <c r="B320" t="inlineStr" s="2">
@@ -10668,7 +10646,7 @@
       </c>
       <c r="D320" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.standard.bold[1]</t>
+          <t xml:space="preserve">N3.standard.bold[1]</t>
         </is>
       </c>
       <c r="E320" t="inlineStr" s="2">
@@ -10678,14 +10656,14 @@
       </c>
       <c r="F320" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この人気を足がかりに、私はもっと上に行く</t>
+          <t xml:space="preserve">大丈夫。この程度。すぐ戻るよ</t>
         </is>
       </c>
     </row>
     <row r="321" ht="40" customHeight="1">
       <c r="A321" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N4.standard.bold[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N3.standard.bold[2]</t>
         </is>
       </c>
       <c r="B321" t="inlineStr" s="2">
@@ -10700,7 +10678,7 @@
       </c>
       <c r="D321" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N4.standard.bold[2]</t>
+          <t xml:space="preserve">N3.standard.bold[2]</t>
         </is>
       </c>
       <c r="E321" t="inlineStr" s="2">
@@ -10710,14 +10688,14 @@
       </c>
       <c r="F321" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだまだここで終わるつもりはない</t>
+          <t xml:space="preserve">こんなんじゃ終われない</t>
         </is>
       </c>
     </row>
     <row r="322" ht="40" customHeight="1">
       <c r="A322" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.standard.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.standard.bold[1]</t>
         </is>
       </c>
       <c r="B322" t="inlineStr" s="2">
@@ -10732,7 +10710,7 @@
       </c>
       <c r="D322" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.standard.bold[1]</t>
+          <t xml:space="preserve">N4.standard.bold[1]</t>
         </is>
       </c>
       <c r="E322" t="inlineStr" s="2">
@@ -10742,14 +10720,14 @@
       </c>
       <c r="F322" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……この団体で、自分の夢は叶えられるんだろうか</t>
+          <t xml:space="preserve">この人気を足がかりに、私はもっと上に行く</t>
         </is>
       </c>
     </row>
     <row r="323" ht="40" customHeight="1">
       <c r="A323" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.standard.bold[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N4.standard.bold[2]</t>
         </is>
       </c>
       <c r="B323" t="inlineStr" s="2">
@@ -10764,7 +10742,7 @@
       </c>
       <c r="D323" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_low.standard.bold[2]</t>
+          <t xml:space="preserve">N4.standard.bold[2]</t>
         </is>
       </c>
       <c r="E323" t="inlineStr" s="2">
@@ -10774,14 +10752,14 @@
       </c>
       <c r="F323" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">先が見えなくて、焦ってる</t>
+          <t xml:space="preserve">まだまだここで終わるつもりはない</t>
         </is>
       </c>
     </row>
     <row r="324" ht="40" customHeight="1">
       <c r="A324" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.standard.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.standard.bold[1]</t>
         </is>
       </c>
       <c r="B324" t="inlineStr" s="2">
@@ -10796,7 +10774,7 @@
       </c>
       <c r="D324" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.standard.bold[1]</t>
+          <t xml:space="preserve">N5_low.standard.bold[1]</t>
         </is>
       </c>
       <c r="E324" t="inlineStr" s="2">
@@ -10806,14 +10784,14 @@
       </c>
       <c r="F324" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……このままで本当にいいのか、って考えちゃうことがある</t>
+          <t xml:space="preserve">……この団体で、自分の夢は叶えられるんだろうか</t>
         </is>
       </c>
     </row>
     <row r="325" ht="40" customHeight="1">
       <c r="A325" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.standard.bold[2]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_low.standard.bold[2]</t>
         </is>
       </c>
       <c r="B325" t="inlineStr" s="2">
@@ -10828,7 +10806,7 @@
       </c>
       <c r="D325" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">N5_warning.standard.bold[2]</t>
+          <t xml:space="preserve">N5_low.standard.bold[2]</t>
         </is>
       </c>
       <c r="E325" t="inlineStr" s="2">
@@ -10838,14 +10816,14 @@
       </c>
       <c r="F325" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近、何と戦ってるのか分からなくなる</t>
+          <t xml:space="preserve">先が見えなくて、焦ってる</t>
         </is>
       </c>
     </row>
     <row r="326" ht="40" customHeight="1">
       <c r="A326" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.standard.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.standard.bold[1]</t>
         </is>
       </c>
       <c r="B326" t="inlineStr" s="2">
@@ -10855,12 +10833,12 @@
       </c>
       <c r="C326" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D326" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">breakthrough.voice.standard.bold[1]</t>
+          <t xml:space="preserve">N5_warning.standard.bold[1]</t>
         </is>
       </c>
       <c r="E326" t="inlineStr" s="2">
@@ -10870,14 +10848,14 @@
       </c>
       <c r="F326" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだまだ強くなれる！この団体でなら</t>
+          <t xml:space="preserve">……このままで本当にいいのか、って考えちゃうことがある</t>
         </is>
       </c>
     </row>
     <row r="327" ht="40" customHeight="1">
       <c r="A327" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.standard.bold[1]</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES.N5_warning.standard.bold[2]</t>
         </is>
       </c>
       <c r="B327" t="inlineStr" s="2">
@@ -10887,12 +10865,12 @@
       </c>
       <c r="C327" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">NOTIF_DIALOGUES</t>
         </is>
       </c>
       <c r="D327" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.standard.bold[1]</t>
+          <t xml:space="preserve">N5_warning.standard.bold[2]</t>
         </is>
       </c>
       <c r="E327" t="inlineStr" s="2">
@@ -10902,14 +10880,14 @@
       </c>
       <c r="F327" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なんであの子と同じ扱いなわけ？</t>
+          <t xml:space="preserve">最近、何と戦ってるのか分からなくなる</t>
         </is>
       </c>
     </row>
     <row r="328" ht="40" customHeight="1">
       <c r="A328" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.standard.bold[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.standard.bold[1]</t>
         </is>
       </c>
       <c r="B328" t="inlineStr" s="2">
@@ -10924,7 +10902,7 @@
       </c>
       <c r="D328" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.standard.bold[2]</t>
+          <t xml:space="preserve">breakthrough.voice.standard.bold[1]</t>
         </is>
       </c>
       <c r="E328" t="inlineStr" s="2">
@@ -10934,14 +10912,14 @@
       </c>
       <c r="F328" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…納得いかない</t>
+          <t xml:space="preserve">…まだまだ強くなれる！この団体でなら</t>
         </is>
       </c>
     </row>
     <row r="329" ht="40" customHeight="1">
       <c r="A329" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.standard.bold[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.standard.bold[1]</t>
         </is>
       </c>
       <c r="B329" t="inlineStr" s="2">
@@ -10956,7 +10934,7 @@
       </c>
       <c r="D329" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G2.voice.standard.bold[1]</t>
+          <t xml:space="preserve">G1.voice.standard.bold[1]</t>
         </is>
       </c>
       <c r="E329" t="inlineStr" s="2">
@@ -10966,14 +10944,14 @@
       </c>
       <c r="F329" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…年功序列なんて古い。分かってる。分かってるけど</t>
+          <t xml:space="preserve">…なんであの子と同じ扱いなわけ？</t>
         </is>
       </c>
     </row>
     <row r="330" ht="40" customHeight="1">
       <c r="A330" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.standard.bold[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.standard.bold[2]</t>
         </is>
       </c>
       <c r="B330" t="inlineStr" s="2">
@@ -10988,7 +10966,7 @@
       </c>
       <c r="D330" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G2.voice.standard.bold[2]</t>
+          <t xml:space="preserve">G1.voice.standard.bold[2]</t>
         </is>
       </c>
       <c r="E330" t="inlineStr" s="2">
@@ -10998,14 +10976,14 @@
       </c>
       <c r="F330" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あたしだって負けてない</t>
+          <t xml:space="preserve">…納得いかない</t>
         </is>
       </c>
     </row>
     <row r="331" ht="40" customHeight="1">
       <c r="A331" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.standard.bold[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.standard.bold[1]</t>
         </is>
       </c>
       <c r="B331" t="inlineStr" s="2">
@@ -11020,7 +10998,7 @@
       </c>
       <c r="D331" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice.standard.bold[1]</t>
+          <t xml:space="preserve">G2.voice.standard.bold[1]</t>
         </is>
       </c>
       <c r="E331" t="inlineStr" s="2">
@@ -11030,14 +11008,14 @@
       </c>
       <c r="F331" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いつになったらあたしの番が来るの？</t>
+          <t xml:space="preserve">…年功序列なんて古い。分かってる。分かってるけど</t>
         </is>
       </c>
     </row>
     <row r="332" ht="40" customHeight="1">
       <c r="A332" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.standard.bold[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.standard.bold[2]</t>
         </is>
       </c>
       <c r="B332" t="inlineStr" s="2">
@@ -11052,7 +11030,7 @@
       </c>
       <c r="D332" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice.standard.bold[2]</t>
+          <t xml:space="preserve">G2.voice.standard.bold[2]</t>
         </is>
       </c>
       <c r="E332" t="inlineStr" s="2">
@@ -11062,14 +11040,14 @@
       </c>
       <c r="F332" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…待つのは好きじゃないな</t>
+          <t xml:space="preserve">…私だって負けてない</t>
         </is>
       </c>
     </row>
     <row r="333" ht="40" customHeight="1">
       <c r="A333" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.standard.bold[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.standard.bold[1]</t>
         </is>
       </c>
       <c r="B333" t="inlineStr" s="2">
@@ -11084,7 +11062,7 @@
       </c>
       <c r="D333" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G4.voice.standard.bold[1]</t>
+          <t xml:space="preserve">G3.voice.standard.bold[1]</t>
         </is>
       </c>
       <c r="E333" t="inlineStr" s="2">
@@ -11094,14 +11072,14 @@
       </c>
       <c r="F333" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…使ってくれなきゃ意味ないじゃん</t>
+          <t xml:space="preserve">…いつになったら私の番が来るの？</t>
         </is>
       </c>
     </row>
     <row r="334" ht="40" customHeight="1">
       <c r="A334" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.standard.bold[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.standard.bold[2]</t>
         </is>
       </c>
       <c r="B334" t="inlineStr" s="2">
@@ -11116,7 +11094,7 @@
       </c>
       <c r="D334" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G4.voice.standard.bold[2]</t>
+          <t xml:space="preserve">G3.voice.standard.bold[2]</t>
         </is>
       </c>
       <c r="E334" t="inlineStr" s="2">
@@ -11126,14 +11104,14 @@
       </c>
       <c r="F334" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あたしの居場所、あるのかな</t>
+          <t xml:space="preserve">…待つのは好きじゃないな</t>
         </is>
       </c>
     </row>
     <row r="335" ht="40" customHeight="1">
       <c r="A335" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.standard.bold[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.standard.bold[1]</t>
         </is>
       </c>
       <c r="B335" t="inlineStr" s="2">
@@ -11148,7 +11126,7 @@
       </c>
       <c r="D335" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R2.voice.standard.bold[1]</t>
+          <t xml:space="preserve">G4.voice.standard.bold[1]</t>
         </is>
       </c>
       <c r="E335" t="inlineStr" s="2">
@@ -11158,14 +11136,14 @@
       </c>
       <c r="F335" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…別にいいけど。わたしは一人でやれるし</t>
+          <t xml:space="preserve">…使ってくれなきゃ意味ないじゃん</t>
         </is>
       </c>
     </row>
     <row r="336" ht="40" customHeight="1">
       <c r="A336" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.standard.bold[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.standard.bold[2]</t>
         </is>
       </c>
       <c r="B336" t="inlineStr" s="2">
@@ -11180,7 +11158,7 @@
       </c>
       <c r="D336" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal.standard.bold[1]</t>
+          <t xml:space="preserve">G4.voice.standard.bold[2]</t>
         </is>
       </c>
       <c r="E336" t="inlineStr" s="2">
@@ -11190,14 +11168,14 @@
       </c>
       <c r="F336" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…バカ。なんで何も言わずに行くのよ</t>
+          <t xml:space="preserve">…私の居場所、あるのかな</t>
         </is>
       </c>
     </row>
     <row r="337" ht="40" customHeight="1">
       <c r="A337" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.standard.bold[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.standard.bold[1]</t>
         </is>
       </c>
       <c r="B337" t="inlineStr" s="2">
@@ -11212,7 +11190,7 @@
       </c>
       <c r="D337" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal.standard.bold[2]</t>
+          <t xml:space="preserve">R2.voice.standard.bold[1]</t>
         </is>
       </c>
       <c r="E337" t="inlineStr" s="2">
@@ -11222,14 +11200,14 @@
       </c>
       <c r="F337" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あいつがいないと、張り合いがないな</t>
+          <t xml:space="preserve">…別にいいけど。私は一人でやれるし</t>
         </is>
       </c>
     </row>
     <row r="338" ht="40" customHeight="1">
       <c r="A338" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.standard.bold[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.standard.bold[1]</t>
         </is>
       </c>
       <c r="B338" t="inlineStr" s="2">
@@ -11244,7 +11222,7 @@
       </c>
       <c r="D338" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R4.voice.standard.bold[1]</t>
+          <t xml:space="preserve">R3.modal.standard.bold[1]</t>
         </is>
       </c>
       <c r="E338" t="inlineStr" s="2">
@@ -11254,14 +11232,14 @@
       </c>
       <c r="F338" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ふん。まだまだこんなもんじゃないけどね</t>
+          <t xml:space="preserve">…バカ。なんで何も言わずに行くのよ</t>
         </is>
       </c>
     </row>
     <row r="339" ht="40" customHeight="1">
       <c r="A339" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.standard.bold[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.standard.bold[2]</t>
         </is>
       </c>
       <c r="B339" t="inlineStr" s="2">
@@ -11276,7 +11254,7 @@
       </c>
       <c r="D339" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R4.voice.standard.bold[2]</t>
+          <t xml:space="preserve">R3.modal.standard.bold[2]</t>
         </is>
       </c>
       <c r="E339" t="inlineStr" s="2">
@@ -11286,14 +11264,14 @@
       </c>
       <c r="F339" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝った。でも、まだ終わってない</t>
+          <t xml:space="preserve">…あいつがいないと、張り合いがないな</t>
         </is>
       </c>
     </row>
     <row r="340" ht="40" customHeight="1">
       <c r="A340" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.standard.bold[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.standard.bold[1]</t>
         </is>
       </c>
       <c r="B340" t="inlineStr" s="2">
@@ -11308,7 +11286,7 @@
       </c>
       <c r="D340" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice.standard.bold[1]</t>
+          <t xml:space="preserve">R4.voice.standard.bold[1]</t>
         </is>
       </c>
       <c r="E340" t="inlineStr" s="2">
@@ -11318,14 +11296,14 @@
       </c>
       <c r="F340" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…次は絶対に負けない</t>
+          <t xml:space="preserve">…ふん。まだまだこんなもんじゃないけどね</t>
         </is>
       </c>
     </row>
     <row r="341" ht="40" customHeight="1">
       <c r="A341" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.standard.bold[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.standard.bold[2]</t>
         </is>
       </c>
       <c r="B341" t="inlineStr" s="2">
@@ -11340,7 +11318,7 @@
       </c>
       <c r="D341" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice.standard.bold[2]</t>
+          <t xml:space="preserve">R4.voice.standard.bold[2]</t>
         </is>
       </c>
       <c r="E341" t="inlineStr" s="2">
@@ -11350,14 +11328,14 @@
       </c>
       <c r="F341" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この借りは必ず返す</t>
+          <t xml:space="preserve">…勝った。でも、まだ終わってない</t>
         </is>
       </c>
     </row>
     <row r="342" ht="40" customHeight="1">
       <c r="A342" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.standard.bold[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.standard.bold[1]</t>
         </is>
       </c>
       <c r="B342" t="inlineStr" s="2">
@@ -11372,7 +11350,7 @@
       </c>
       <c r="D342" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warVictory.voice.standard.bold[1]</t>
+          <t xml:space="preserve">R5.voice.standard.bold[1]</t>
         </is>
       </c>
       <c r="E342" t="inlineStr" s="2">
@@ -11382,14 +11360,14 @@
       </c>
       <c r="F342" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…わたしが勝つに決まってるでしょ。この団体を背負ってるんだから！</t>
+          <t xml:space="preserve">…次は絶対に負けない</t>
         </is>
       </c>
     </row>
     <row r="343" ht="40" customHeight="1">
       <c r="A343" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.standard.bold[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.standard.bold[2]</t>
         </is>
       </c>
       <c r="B343" t="inlineStr" s="2">
@@ -11399,29 +11377,29 @@
       </c>
       <c r="C343" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D343" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_insult.standard.bold[1]</t>
+          <t xml:space="preserve">R5.voice.standard.bold[2]</t>
         </is>
       </c>
       <c r="E343" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F343" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この額で私が喜ぶと思ったんですか</t>
+          <t xml:space="preserve">…この借りは必ず返す</t>
         </is>
       </c>
     </row>
     <row r="344" ht="40" customHeight="1">
       <c r="A344" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.standard.bold[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.standard.bold[1]</t>
         </is>
       </c>
       <c r="B344" t="inlineStr" s="2">
@@ -11431,29 +11409,29 @@
       </c>
       <c r="C344" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
       <c r="D344" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_insult.standard.bold[2]</t>
+          <t xml:space="preserve">warVictory.voice.standard.bold[1]</t>
         </is>
       </c>
       <c r="E344" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">10 ニュース・新聞・黒田記者コラム</t>
         </is>
       </c>
       <c r="F344" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なめられたものね。受け取れない</t>
+          <t xml:space="preserve">…私が勝つに決まってるでしょ。この団体を背負ってるんだから！</t>
         </is>
       </c>
     </row>
     <row r="345" ht="40" customHeight="1">
       <c r="A345" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_repeat.standard.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.standard.bold[1]</t>
         </is>
       </c>
       <c r="B345" t="inlineStr" s="2">
@@ -11468,7 +11446,7 @@
       </c>
       <c r="D345" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus_repeat.standard.bold[1]</t>
+          <t xml:space="preserve">bonus_insult.standard.bold[1]</t>
         </is>
       </c>
       <c r="E345" t="inlineStr" s="2">
@@ -11478,14 +11456,14 @@
       </c>
       <c r="F345" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…また金か。もういいよ</t>
+          <t xml:space="preserve">この額で私が喜ぶと思ったんですか</t>
         </is>
       </c>
     </row>
     <row r="346" ht="40" customHeight="1">
       <c r="A346" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.standard.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_insult.standard.bold[2]</t>
         </is>
       </c>
       <c r="B346" t="inlineStr" s="2">
@@ -11500,7 +11478,7 @@
       </c>
       <c r="D346" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.standard.bold[1]</t>
+          <t xml:space="preserve">bonus_insult.standard.bold[2]</t>
         </is>
       </c>
       <c r="E346" t="inlineStr" s="2">
@@ -11510,14 +11488,14 @@
       </c>
       <c r="F346" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これで負けていられない！</t>
+          <t xml:space="preserve">なめられたものね。受け取れない</t>
         </is>
       </c>
     </row>
     <row r="347" ht="40" customHeight="1">
       <c r="A347" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.standard.bold[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus_repeat.standard.bold[1]</t>
         </is>
       </c>
       <c r="B347" t="inlineStr" s="2">
@@ -11532,7 +11510,7 @@
       </c>
       <c r="D347" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.standard.bold[2]</t>
+          <t xml:space="preserve">bonus_repeat.standard.bold[1]</t>
         </is>
       </c>
       <c r="E347" t="inlineStr" s="2">
@@ -11542,14 +11520,14 @@
       </c>
       <c r="F347" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よし！もっと強くなります！</t>
+          <t xml:space="preserve">…また金か。もういいよ</t>
         </is>
       </c>
     </row>
     <row r="348" ht="40" customHeight="1">
       <c r="A348" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.standard.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.standard.bold[1]</t>
         </is>
       </c>
       <c r="B348" t="inlineStr" s="2">
@@ -11564,7 +11542,7 @@
       </c>
       <c r="D348" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.standard.bold[1]</t>
+          <t xml:space="preserve">bonus.standard.bold[1]</t>
         </is>
       </c>
       <c r="E348" t="inlineStr" s="2">
@@ -11574,14 +11552,14 @@
       </c>
       <c r="F348" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ライバルに差をつけるチャンスだね！</t>
+          <t xml:space="preserve">これで負けていられない！</t>
         </is>
       </c>
     </row>
     <row r="349" ht="40" customHeight="1">
       <c r="A349" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.standard.bold[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.bonus.standard.bold[2]</t>
         </is>
       </c>
       <c r="B349" t="inlineStr" s="2">
@@ -11596,7 +11574,7 @@
       </c>
       <c r="D349" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.standard.bold[2]</t>
+          <t xml:space="preserve">bonus.standard.bold[2]</t>
         </is>
       </c>
       <c r="E349" t="inlineStr" s="2">
@@ -11606,14 +11584,14 @@
       </c>
       <c r="F349" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">合宿から帰る頃には一回り強くなってやる！</t>
+          <t xml:space="preserve">よし！もっと強くなります！</t>
         </is>
       </c>
     </row>
     <row r="350" ht="40" customHeight="1">
       <c r="A350" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.standard.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.standard.bold[1]</t>
         </is>
       </c>
       <c r="B350" t="inlineStr" s="2">
@@ -11628,7 +11606,7 @@
       </c>
       <c r="D350" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.standard.bold[1]</t>
+          <t xml:space="preserve">camp.standard.bold[1]</t>
         </is>
       </c>
       <c r="E350" t="inlineStr" s="2">
@@ -11638,14 +11616,14 @@
       </c>
       <c r="F350" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">信じてくれるなら、絶対やるよ！</t>
+          <t xml:space="preserve">ライバルに差をつけるチャンスだね！</t>
         </is>
       </c>
     </row>
     <row r="351" ht="40" customHeight="1">
       <c r="A351" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.standard.bold[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.camp.standard.bold[2]</t>
         </is>
       </c>
       <c r="B351" t="inlineStr" s="2">
@@ -11660,7 +11638,7 @@
       </c>
       <c r="D351" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage_high_trust.standard.bold[2]</t>
+          <t xml:space="preserve">camp.standard.bold[2]</t>
         </is>
       </c>
       <c r="E351" t="inlineStr" s="2">
@@ -11670,14 +11648,14 @@
       </c>
       <c r="F351" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">期待には必ず応える！</t>
+          <t xml:space="preserve">合宿から帰る頃には一回り強くなってやる！</t>
         </is>
       </c>
     </row>
     <row r="352" ht="40" customHeight="1">
       <c r="A352" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.standard.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.standard.bold[1]</t>
         </is>
       </c>
       <c r="B352" t="inlineStr" s="2">
@@ -11692,7 +11670,7 @@
       </c>
       <c r="D352" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.standard.bold[1]</t>
+          <t xml:space="preserve">encourage_high_trust.standard.bold[1]</t>
         </is>
       </c>
       <c r="E352" t="inlineStr" s="2">
@@ -11702,14 +11680,14 @@
       </c>
       <c r="F352" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなところで止まってられない！次は絶対やるから！</t>
+          <t xml:space="preserve">信じてくれるなら、絶対やるよ！</t>
         </is>
       </c>
     </row>
     <row r="353" ht="40" customHeight="1">
       <c r="A353" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.standard.bold[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage_high_trust.standard.bold[2]</t>
         </is>
       </c>
       <c r="B353" t="inlineStr" s="2">
@@ -11724,7 +11702,7 @@
       </c>
       <c r="D353" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.standard.bold[2]</t>
+          <t xml:space="preserve">encourage_high_trust.standard.bold[2]</t>
         </is>
       </c>
       <c r="E353" t="inlineStr" s="2">
@@ -11734,14 +11712,14 @@
       </c>
       <c r="F353" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…分かった。まだ諦めない</t>
+          <t xml:space="preserve">期待には必ず応える！</t>
         </is>
       </c>
     </row>
     <row r="354" ht="40" customHeight="1">
       <c r="A354" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.standard.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.standard.bold[1]</t>
         </is>
       </c>
       <c r="B354" t="inlineStr" s="2">
@@ -11756,7 +11734,7 @@
       </c>
       <c r="D354" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.standard.bold[1]</t>
+          <t xml:space="preserve">encourage.standard.bold[1]</t>
         </is>
       </c>
       <c r="E354" t="inlineStr" s="2">
@@ -11766,14 +11744,14 @@
       </c>
       <c r="F354" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あれは徒党じゃない。私が呼んで、集まってくれた仲間です</t>
+          <t xml:space="preserve">こんなところで止まってられない！次は絶対やるから！</t>
         </is>
       </c>
     </row>
     <row r="355" ht="40" customHeight="1">
       <c r="A355" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.standard.bold[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.encourage.standard.bold[2]</t>
         </is>
       </c>
       <c r="B355" t="inlineStr" s="2">
@@ -11788,7 +11766,7 @@
       </c>
       <c r="D355" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.standard.bold[2]</t>
+          <t xml:space="preserve">encourage.standard.bold[2]</t>
         </is>
       </c>
       <c r="E355" t="inlineStr" s="2">
@@ -11798,14 +11776,14 @@
       </c>
       <c r="F355" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">納得はしていません。それでも、従います</t>
+          <t xml:space="preserve">…分かった。まだ諦めない</t>
         </is>
       </c>
     </row>
     <row r="356" ht="40" customHeight="1">
       <c r="A356" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.standard.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.standard.bold[1]</t>
         </is>
       </c>
       <c r="B356" t="inlineStr" s="2">
@@ -11820,7 +11798,7 @@
       </c>
       <c r="D356" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.standard.bold[1]</t>
+          <t xml:space="preserve">faction_decree.standard.bold[1]</t>
         </is>
       </c>
       <c r="E356" t="inlineStr" s="2">
@@ -11830,14 +11808,14 @@
       </c>
       <c r="F356" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと広い舞台に出たかった。ありがとう！</t>
+          <t xml:space="preserve">あれは徒党じゃない。私が呼んで、集まってくれた仲間です</t>
         </is>
       </c>
     </row>
     <row r="357" ht="40" customHeight="1">
       <c r="A357" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.standard.bold[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.faction_decree.standard.bold[2]</t>
         </is>
       </c>
       <c r="B357" t="inlineStr" s="2">
@@ -11852,7 +11830,7 @@
       </c>
       <c r="D357" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.standard.bold[2]</t>
+          <t xml:space="preserve">faction_decree.standard.bold[2]</t>
         </is>
       </c>
       <c r="E357" t="inlineStr" s="2">
@@ -11862,14 +11840,14 @@
       </c>
       <c r="F357" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">注目される場は大歓迎！存在感見せてあげる！</t>
+          <t xml:space="preserve">納得はしていません。それでも、従います</t>
         </is>
       </c>
     </row>
     <row r="358" ht="40" customHeight="1">
       <c r="A358" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.standard.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.standard.bold[1]</t>
         </is>
       </c>
       <c r="B358" t="inlineStr" s="2">
@@ -11884,7 +11862,7 @@
       </c>
       <c r="D358" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.standard.bold[1]</t>
+          <t xml:space="preserve">media.standard.bold[1]</t>
         </is>
       </c>
       <c r="E358" t="inlineStr" s="2">
@@ -11894,14 +11872,14 @@
       </c>
       <c r="F358" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽しいけど…次の興行ではもっと結果を出す！</t>
+          <t xml:space="preserve">もっと広い舞台に出たかった。ありがとう！</t>
         </is>
       </c>
     </row>
     <row r="359" ht="40" customHeight="1">
       <c r="A359" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.standard.bold[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.media.standard.bold[2]</t>
         </is>
       </c>
       <c r="B359" t="inlineStr" s="2">
@@ -11916,7 +11894,7 @@
       </c>
       <c r="D359" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.standard.bold[2]</t>
+          <t xml:space="preserve">media.standard.bold[2]</t>
         </is>
       </c>
       <c r="E359" t="inlineStr" s="2">
@@ -11926,14 +11904,14 @@
       </c>
       <c r="F359" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい雰囲気。チームが強くなってる証拠だね</t>
+          <t xml:space="preserve">注目される場は大歓迎！存在感見せてあげる！</t>
         </is>
       </c>
     </row>
     <row r="360" ht="40" customHeight="1">
       <c r="A360" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.standard.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.standard.bold[1]</t>
         </is>
       </c>
       <c r="B360" t="inlineStr" s="2">
@@ -11948,7 +11926,7 @@
       </c>
       <c r="D360" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.standard.bold[1]</t>
+          <t xml:space="preserve">party.standard.bold[1]</t>
         </is>
       </c>
       <c r="E360" t="inlineStr" s="2">
@@ -11958,14 +11936,14 @@
       </c>
       <c r="F360" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">リフレッシュして、もっと上を目指す！</t>
+          <t xml:space="preserve">楽しいけど…次の興行ではもっと結果を出す！</t>
         </is>
       </c>
     </row>
     <row r="361" ht="40" customHeight="1">
       <c r="A361" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.standard.bold[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.party.standard.bold[2]</t>
         </is>
       </c>
       <c r="B361" t="inlineStr" s="2">
@@ -11980,7 +11958,7 @@
       </c>
       <c r="D361" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.standard.bold[2]</t>
+          <t xml:space="preserve">party.standard.bold[2]</t>
         </is>
       </c>
       <c r="E361" t="inlineStr" s="2">
@@ -11990,14 +11968,14 @@
       </c>
       <c r="F361" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">充電して戻ってくる！</t>
+          <t xml:space="preserve">いい雰囲気。チームが強くなってる証拠だね</t>
         </is>
       </c>
     </row>
     <row r="362" ht="40" customHeight="1">
       <c r="A362" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.standard.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.standard.bold[1]</t>
         </is>
       </c>
       <c r="B362" t="inlineStr" s="2">
@@ -12012,7 +11990,7 @@
       </c>
       <c r="D362" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.standard.bold[1]</t>
+          <t xml:space="preserve">refresh_leave.standard.bold[1]</t>
         </is>
       </c>
       <c r="E362" t="inlineStr" s="2">
@@ -12022,14 +12000,14 @@
       </c>
       <c r="F362" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">早く戻る…！ こんなとこで止まってられない！</t>
+          <t xml:space="preserve">リフレッシュして、もっと上を目指す！</t>
         </is>
       </c>
     </row>
     <row r="363" ht="40" customHeight="1">
       <c r="A363" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.standard.bold[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.refresh_leave.standard.bold[2]</t>
         </is>
       </c>
       <c r="B363" t="inlineStr" s="2">
@@ -12044,7 +12022,7 @@
       </c>
       <c r="D363" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.standard.bold[2]</t>
+          <t xml:space="preserve">refresh_leave.standard.bold[2]</t>
         </is>
       </c>
       <c r="E363" t="inlineStr" s="2">
@@ -12054,14 +12032,14 @@
       </c>
       <c r="F363" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">すぐ治します！次の試合は絶対ものにする！</t>
+          <t xml:space="preserve">充電して戻ってくる！</t>
         </is>
       </c>
     </row>
     <row r="364" ht="40" customHeight="1">
       <c r="A364" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.standard.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.standard.bold[1]</t>
         </is>
       </c>
       <c r="B364" t="inlineStr" s="2">
@@ -12076,7 +12054,7 @@
       </c>
       <c r="D364" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.standard.bold[1]</t>
+          <t xml:space="preserve">special_treatment.standard.bold[1]</t>
         </is>
       </c>
       <c r="E364" t="inlineStr" s="2">
@@ -12086,14 +12064,14 @@
       </c>
       <c r="F364" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この環境を無駄にしない！絶対に結果を出す！</t>
+          <t xml:space="preserve">早く戻る…！ こんなとこで止まってられない！</t>
         </is>
       </c>
     </row>
     <row r="365" ht="40" customHeight="1">
       <c r="A365" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.standard.bold[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.special_treatment.standard.bold[2]</t>
         </is>
       </c>
       <c r="B365" t="inlineStr" s="2">
@@ -12108,7 +12086,7 @@
       </c>
       <c r="D365" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.standard.bold[2]</t>
+          <t xml:space="preserve">special_treatment.standard.bold[2]</t>
         </is>
       </c>
       <c r="E365" t="inlineStr" s="2">
@@ -12118,14 +12096,14 @@
       </c>
       <c r="F365" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の後押しね！限界まで追い込むよ！</t>
+          <t xml:space="preserve">すぐ治します！次の試合は絶対ものにする！</t>
         </is>
       </c>
     </row>
     <row r="366" ht="40" customHeight="1">
       <c r="A366" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.standard.bold[1]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.standard.bold[1]</t>
         </is>
       </c>
       <c r="B366" t="inlineStr" s="2">
@@ -12135,12 +12113,12 @@
       </c>
       <c r="C366" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D366" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.standard.bold[1]</t>
+          <t xml:space="preserve">trainer.standard.bold[1]</t>
         </is>
       </c>
       <c r="E366" t="inlineStr" s="2">
@@ -12150,14 +12128,14 @@
       </c>
       <c r="F366" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この露出を足がかりに、もっと大きな舞台へ進みたい</t>
+          <t xml:space="preserve">この環境を無駄にしない！絶対に結果を出す！</t>
         </is>
       </c>
     </row>
     <row r="367" ht="40" customHeight="1">
       <c r="A367" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.standard.bold[2]</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES.trainer.standard.bold[2]</t>
         </is>
       </c>
       <c r="B367" t="inlineStr" s="2">
@@ -12167,12 +12145,12 @@
       </c>
       <c r="C367" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CARE_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D367" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.standard.bold[2]</t>
+          <t xml:space="preserve">trainer.standard.bold[2]</t>
         </is>
       </c>
       <c r="E367" t="inlineStr" s="2">
@@ -12182,14 +12160,14 @@
       </c>
       <c r="F367" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私が出れば注目されるのは当然。楽しみにしてるよ</t>
+          <t xml:space="preserve">最高の後押しね！限界まで追い込むよ！</t>
         </is>
       </c>
     </row>
     <row r="368" ht="40" customHeight="1">
       <c r="A368" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.standard.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.standard.bold[1]</t>
         </is>
       </c>
       <c r="B368" t="inlineStr" s="2">
@@ -12204,7 +12182,7 @@
       </c>
       <c r="D368" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.standard.bold[1]</t>
+          <t xml:space="preserve">E1.standard.bold[1]</t>
         </is>
       </c>
       <c r="E368" t="inlineStr" s="2">
@@ -12214,14 +12192,14 @@
       </c>
       <c r="F368" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…本当のことを言うと、いい条件だと思ってる</t>
+          <t xml:space="preserve">この露出を足がかりに、もっと大きな舞台へ進みたい</t>
         </is>
       </c>
     </row>
     <row r="369" ht="40" customHeight="1">
       <c r="A369" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.standard.bold[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.standard.bold[2]</t>
         </is>
       </c>
       <c r="B369" t="inlineStr" s="2">
@@ -12236,7 +12214,7 @@
       </c>
       <c r="D369" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E6.standard.bold[2]</t>
+          <t xml:space="preserve">E1.standard.bold[2]</t>
         </is>
       </c>
       <c r="E369" t="inlineStr" s="2">
@@ -12246,14 +12224,14 @@
       </c>
       <c r="F369" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">他所から話が来た。考えてもいいでしょ？</t>
+          <t xml:space="preserve">私が出れば注目されるのは当然。楽しみにしてるよ</t>
         </is>
       </c>
     </row>
     <row r="370" ht="40" customHeight="1">
       <c r="A370" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.standard.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.standard.bold[1]</t>
         </is>
       </c>
       <c r="B370" t="inlineStr" s="2">
@@ -12268,7 +12246,7 @@
       </c>
       <c r="D370" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.standard.bold[1]</t>
+          <t xml:space="preserve">E6.standard.bold[1]</t>
         </is>
       </c>
       <c r="E370" t="inlineStr" s="2">
@@ -12278,14 +12256,14 @@
       </c>
       <c r="F370" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習？出してもくれないのに何の意味があるのよ？</t>
+          <t xml:space="preserve">…本当のことを言うと、いい条件だと思ってる</t>
         </is>
       </c>
     </row>
     <row r="371" ht="40" customHeight="1">
       <c r="A371" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.standard.bold[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E6.standard.bold[2]</t>
         </is>
       </c>
       <c r="B371" t="inlineStr" s="2">
@@ -12300,7 +12278,7 @@
       </c>
       <c r="D371" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_boycott.standard.bold[2]</t>
+          <t xml:space="preserve">E6.standard.bold[2]</t>
         </is>
       </c>
       <c r="E371" t="inlineStr" s="2">
@@ -12310,14 +12288,14 @@
       </c>
       <c r="F371" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">リングに上がれないなら練習しても仕方ないでしょ</t>
+          <t xml:space="preserve">他所から話が来た。考えてもいいでしょ？</t>
         </is>
       </c>
     </row>
     <row r="372" ht="40" customHeight="1">
       <c r="A372" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.standard.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.standard.bold[1]</t>
         </is>
       </c>
       <c r="B372" t="inlineStr" s="2">
@@ -12332,7 +12310,7 @@
       </c>
       <c r="D372" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_grumble.standard.bold[1]</t>
+          <t xml:space="preserve">S_boycott.standard.bold[1]</t>
         </is>
       </c>
       <c r="E372" t="inlineStr" s="2">
@@ -12342,14 +12320,14 @@
       </c>
       <c r="F372" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（「なんで私たちがこんな扱い受けなきゃいけないんだ」と大声で言っている）</t>
+          <t xml:space="preserve">練習？出してもくれないのに何の意味があるのよ？</t>
         </is>
       </c>
     </row>
     <row r="373" ht="40" customHeight="1">
       <c r="A373" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.standard.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_boycott.standard.bold[2]</t>
         </is>
       </c>
       <c r="B373" t="inlineStr" s="2">
@@ -12364,7 +12342,7 @@
       </c>
       <c r="D373" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S_sns.standard.bold[1]</t>
+          <t xml:space="preserve">S_boycott.standard.bold[2]</t>
         </is>
       </c>
       <c r="E373" t="inlineStr" s="2">
@@ -12374,14 +12352,14 @@
       </c>
       <c r="F373" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（SNSに「このまま終わるつもりはない」と宣言的な投稿）</t>
+          <t xml:space="preserve">リングに上がれないなら練習しても仕方ないでしょ</t>
         </is>
       </c>
     </row>
     <row r="374" ht="40" customHeight="1">
       <c r="A374" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.standard.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_grumble.standard.bold[1]</t>
         </is>
       </c>
       <c r="B374" t="inlineStr" s="2">
@@ -12396,7 +12374,7 @@
       </c>
       <c r="D374" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.standard.bold[1]</t>
+          <t xml:space="preserve">S_grumble.standard.bold[1]</t>
         </is>
       </c>
       <c r="E374" t="inlineStr" s="2">
@@ -12406,14 +12384,14 @@
       </c>
       <c r="F374" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンの座が欲しい。今すぐ組んでよ</t>
+          <t xml:space="preserve">（「なんで私たちがこんな扱い受けなきゃいけないんだ」と大声で言っている）</t>
         </is>
       </c>
     </row>
     <row r="375" ht="40" customHeight="1">
       <c r="A375" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.standard.bold[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S_sns.standard.bold[1]</t>
         </is>
       </c>
       <c r="B375" t="inlineStr" s="2">
@@ -12428,7 +12406,7 @@
       </c>
       <c r="D375" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S1.standard.bold[2]</t>
+          <t xml:space="preserve">S_sns.standard.bold[1]</t>
         </is>
       </c>
       <c r="E375" t="inlineStr" s="2">
@@ -12438,14 +12416,14 @@
       </c>
       <c r="F375" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルトを賭けた試合がしたい！</t>
+          <t xml:space="preserve">（SNSに「このまま終わるつもりはない」と宣言的な投稿）</t>
         </is>
       </c>
     </row>
     <row r="376" ht="40" customHeight="1">
       <c r="A376" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.standard.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.standard.bold[1]</t>
         </is>
       </c>
       <c r="B376" t="inlineStr" s="2">
@@ -12460,7 +12438,7 @@
       </c>
       <c r="D376" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.standard.bold[1]</t>
+          <t xml:space="preserve">S1.standard.bold[1]</t>
         </is>
       </c>
       <c r="E376" t="inlineStr" s="2">
@@ -12470,14 +12448,14 @@
       </c>
       <c r="F376" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの相手と戦わずにはいられない！早く試合を組んでくれ！</t>
+          <t xml:space="preserve">チャンピオンの座が欲しい。今すぐ組んでよ</t>
         </is>
       </c>
     </row>
     <row r="377" ht="40" customHeight="1">
       <c r="A377" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.standard.bold[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S1.standard.bold[2]</t>
         </is>
       </c>
       <c r="B377" t="inlineStr" s="2">
@@ -12492,7 +12470,7 @@
       </c>
       <c r="D377" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S2.standard.bold[2]</t>
+          <t xml:space="preserve">S1.standard.bold[2]</t>
         </is>
       </c>
       <c r="E377" t="inlineStr" s="2">
@@ -12502,14 +12480,14 @@
       </c>
       <c r="F377" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決着をつけたい。あいつと戦う機会をちょうだい！</t>
+          <t xml:space="preserve">ベルトを賭けた試合がしたい！</t>
         </is>
       </c>
     </row>
     <row r="378" ht="40" customHeight="1">
       <c r="A378" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.standard.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.standard.bold[1]</t>
         </is>
       </c>
       <c r="B378" t="inlineStr" s="2">
@@ -12524,7 +12502,7 @@
       </c>
       <c r="D378" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S3.standard.bold[1]</t>
+          <t xml:space="preserve">S2.standard.bold[1]</t>
         </is>
       </c>
       <c r="E378" t="inlineStr" s="2">
@@ -12534,14 +12512,14 @@
       </c>
       <c r="F378" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悔しいけど、体が限界みたい。少し休ませて</t>
+          <t xml:space="preserve">あの相手と戦わずにはいられない！早く試合を組んでくれ！</t>
         </is>
       </c>
     </row>
     <row r="379" ht="40" customHeight="1">
       <c r="A379" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.standard.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S2.standard.bold[2]</t>
         </is>
       </c>
       <c r="B379" t="inlineStr" s="2">
@@ -12556,7 +12534,7 @@
       </c>
       <c r="D379" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.standard.bold[1]</t>
+          <t xml:space="preserve">S2.standard.bold[2]</t>
         </is>
       </c>
       <c r="E379" t="inlineStr" s="2">
@@ -12566,14 +12544,14 @@
       </c>
       <c r="F379" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このままじゃ納得できない。改善してくれないなら移籍を考えるからね</t>
+          <t xml:space="preserve">決着をつけたい。あいつと戦う機会をちょうだい！</t>
         </is>
       </c>
     </row>
     <row r="380" ht="40" customHeight="1">
       <c r="A380" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.standard.bold[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S3.standard.bold[1]</t>
         </is>
       </c>
       <c r="B380" t="inlineStr" s="2">
@@ -12588,7 +12566,7 @@
       </c>
       <c r="D380" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_direct.standard.bold[2]</t>
+          <t xml:space="preserve">S3.standard.bold[1]</t>
         </is>
       </c>
       <c r="E380" t="inlineStr" s="2">
@@ -12598,14 +12576,14 @@
       </c>
       <c r="F380" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私の実力を発揮できていない。ここにいる意味はあるのかな</t>
+          <t xml:space="preserve">…悔しいけど、体が限界みたい。少し休ませて</t>
         </is>
       </c>
     </row>
     <row r="381" ht="40" customHeight="1">
       <c r="A381" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.standard.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.standard.bold[1]</t>
         </is>
       </c>
       <c r="B381" t="inlineStr" s="2">
@@ -12620,7 +12598,7 @@
       </c>
       <c r="D381" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S4_silent.standard.bold[1]</t>
+          <t xml:space="preserve">S4_direct.standard.bold[1]</t>
         </is>
       </c>
       <c r="E381" t="inlineStr" s="2">
@@ -12630,14 +12608,14 @@
       </c>
       <c r="F381" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…………（拳を握りしめている）</t>
+          <t xml:space="preserve">このままじゃ納得できない。改善してくれないなら移籍を考えるからね</t>
         </is>
       </c>
     </row>
     <row r="382" ht="40" customHeight="1">
       <c r="A382" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.standard.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_direct.standard.bold[2]</t>
         </is>
       </c>
       <c r="B382" t="inlineStr" s="2">
@@ -12652,7 +12630,7 @@
       </c>
       <c r="D382" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.standard.bold[1]</t>
+          <t xml:space="preserve">S4_direct.standard.bold[2]</t>
         </is>
       </c>
       <c r="E382" t="inlineStr" s="2">
@@ -12662,14 +12640,14 @@
       </c>
       <c r="F382" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと上を目指したい。特訓させて！</t>
+          <t xml:space="preserve">私の実力を発揮できていない。ここにいる意味はあるのかな</t>
         </is>
       </c>
     </row>
     <row r="383" ht="40" customHeight="1">
       <c r="A383" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.standard.bold[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S4_silent.standard.bold[1]</t>
         </is>
       </c>
       <c r="B383" t="inlineStr" s="2">
@@ -12684,7 +12662,7 @@
       </c>
       <c r="D383" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S5.standard.bold[2]</t>
+          <t xml:space="preserve">S4_silent.standard.bold[1]</t>
         </is>
       </c>
       <c r="E383" t="inlineStr" s="2">
@@ -12694,14 +12672,14 @@
       </c>
       <c r="F383" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今燃えてるの！とことんやらせて！</t>
+          <t xml:space="preserve">…………（拳を握りしめている）</t>
         </is>
       </c>
     </row>
     <row r="384" ht="40" customHeight="1">
       <c r="A384" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.standard.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.standard.bold[1]</t>
         </is>
       </c>
       <c r="B384" t="inlineStr" s="2">
@@ -12716,7 +12694,7 @@
       </c>
       <c r="D384" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">S6.standard.bold[1]</t>
+          <t xml:space="preserve">S5.standard.bold[1]</t>
         </is>
       </c>
       <c r="E384" t="inlineStr" s="2">
@@ -12726,14 +12704,14 @@
       </c>
       <c r="F384" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">若い子たちの面倒を見させてよ。それが私の役目だと思うから</t>
+          <t xml:space="preserve">もっと上を目指したい。特訓させて！</t>
         </is>
       </c>
     </row>
     <row r="385" ht="40" customHeight="1">
       <c r="A385" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.standard.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S5.standard.bold[2]</t>
         </is>
       </c>
       <c r="B385" t="inlineStr" s="2">
@@ -12743,12 +12721,12 @@
       </c>
       <c r="C385" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D385" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.accept.standard.bold[1]</t>
+          <t xml:space="preserve">S5.standard.bold[2]</t>
         </is>
       </c>
       <c r="E385" t="inlineStr" s="2">
@@ -12758,14 +12736,14 @@
       </c>
       <c r="F385" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">任せてよ、ばっちり爪痕残してくる!</t>
+          <t xml:space="preserve">今燃えてるの！とことんやらせて！</t>
         </is>
       </c>
     </row>
     <row r="386" ht="40" customHeight="1">
       <c r="A386" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.recommend.standard.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.S6.standard.bold[1]</t>
         </is>
       </c>
       <c r="B386" t="inlineStr" s="2">
@@ -12775,12 +12753,12 @@
       </c>
       <c r="C386" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D386" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.recommend.standard.bold[1]</t>
+          <t xml:space="preserve">S6.standard.bold[1]</t>
         </is>
       </c>
       <c r="E386" t="inlineStr" s="2">
@@ -12790,14 +12768,14 @@
       </c>
       <c r="F386" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お、わたしに来た!? いいよ、任せて!</t>
+          <t xml:space="preserve">若い子たちの面倒を見させてよ。それが私の役目だと思うから</t>
         </is>
       </c>
     </row>
     <row r="387" ht="40" customHeight="1">
       <c r="A387" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.standard.bold[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.standard.bold[1]</t>
         </is>
       </c>
       <c r="B387" t="inlineStr" s="2">
@@ -12807,12 +12785,12 @@
       </c>
       <c r="C387" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
         </is>
       </c>
       <c r="D387" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.standard.bold[1]</t>
+          <t xml:space="preserve">E1.accept.standard.bold[1]</t>
         </is>
       </c>
       <c r="E387" t="inlineStr" s="2">
@@ -12822,14 +12800,14 @@
       </c>
       <c r="F387" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそっ…こんなところで足を止めるわけにはいかないのに</t>
+          <t xml:space="preserve">任せてよ、ばっちり爪痕残してくる!</t>
         </is>
       </c>
     </row>
     <row r="388" ht="40" customHeight="1">
       <c r="A388" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.standard.bold[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.recommend.standard.bold[1]</t>
         </is>
       </c>
       <c r="B388" t="inlineStr" s="2">
@@ -12839,12 +12817,12 @@
       </c>
       <c r="C388" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
         </is>
       </c>
       <c r="D388" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1.standard.bold[2]</t>
+          <t xml:space="preserve">E1.recommend.standard.bold[1]</t>
         </is>
       </c>
       <c r="E388" t="inlineStr" s="2">
@@ -12854,14 +12832,14 @@
       </c>
       <c r="F388" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">大丈夫。この程度…すぐ直るから</t>
+          <t xml:space="preserve">お、私に来た!? いいよ、任せて!</t>
         </is>
       </c>
     </row>
     <row r="389" ht="40" customHeight="1">
       <c r="A389" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.standard.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.standard.bold[1]</t>
         </is>
       </c>
       <c r="B389" t="inlineStr" s="2">
@@ -12876,7 +12854,7 @@
       </c>
       <c r="D389" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.standard.bold[1]</t>
+          <t xml:space="preserve">B1.standard.bold[1]</t>
         </is>
       </c>
       <c r="E389" t="inlineStr" s="2">
@@ -12886,14 +12864,14 @@
       </c>
       <c r="F389" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あいつの態度が許せない。もう我慢の限界よ</t>
+          <t xml:space="preserve">くそっ…こんなところで足を止めるわけにはいかないのに</t>
         </is>
       </c>
     </row>
     <row r="390" ht="40" customHeight="1">
       <c r="A390" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.standard.bold[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B1.standard.bold[2]</t>
         </is>
       </c>
       <c r="B390" t="inlineStr" s="2">
@@ -12908,7 +12886,7 @@
       </c>
       <c r="D390" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter1.standard.bold[2]</t>
+          <t xml:space="preserve">B1.standard.bold[2]</t>
         </is>
       </c>
       <c r="E390" t="inlineStr" s="2">
@@ -12918,14 +12896,14 @@
       </c>
       <c r="F390" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チームのためにも、この問題ははっきりさせるべき！</t>
+          <t xml:space="preserve">大丈夫。この程度…すぐ直るから</t>
         </is>
       </c>
     </row>
     <row r="391" ht="40" customHeight="1">
       <c r="A391" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.standard.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.standard.bold[1]</t>
         </is>
       </c>
       <c r="B391" t="inlineStr" s="2">
@@ -12940,7 +12918,7 @@
       </c>
       <c r="D391" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.standard.bold[1]</t>
+          <t xml:space="preserve">B2_fighter1.standard.bold[1]</t>
         </is>
       </c>
       <c r="E391" t="inlineStr" s="2">
@@ -12950,14 +12928,14 @@
       </c>
       <c r="F391" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私だって黙ってない。向こうが謝るべきでしょ？</t>
+          <t xml:space="preserve">あいつの態度が許せない。もう我慢の限界よ</t>
         </is>
       </c>
     </row>
     <row r="392" ht="40" customHeight="1">
       <c r="A392" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.standard.bold[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter1.standard.bold[2]</t>
         </is>
       </c>
       <c r="B392" t="inlineStr" s="2">
@@ -12972,7 +12950,7 @@
       </c>
       <c r="D392" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_fighter2.standard.bold[2]</t>
+          <t xml:space="preserve">B2_fighter1.standard.bold[2]</t>
         </is>
       </c>
       <c r="E392" t="inlineStr" s="2">
@@ -12982,14 +12960,14 @@
       </c>
       <c r="F392" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">正面からぶつかって決着つけるしかないわね</t>
+          <t xml:space="preserve">チームのためにも、この問題ははっきりさせるべき！</t>
         </is>
       </c>
     </row>
     <row r="393" ht="40" customHeight="1">
       <c r="A393" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.standard.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.standard.bold[1]</t>
         </is>
       </c>
       <c r="B393" t="inlineStr" s="2">
@@ -13004,7 +12982,7 @@
       </c>
       <c r="D393" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.standard.bold[1]</t>
+          <t xml:space="preserve">B2_fighter2.standard.bold[1]</t>
         </is>
       </c>
       <c r="E393" t="inlineStr" s="2">
@@ -13014,14 +12992,14 @@
       </c>
       <c r="F393" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">そのブランドのイメージ、私が底上げしてやる</t>
+          <t xml:space="preserve">私だって黙ってない。向こうが謝るべきでしょ？</t>
         </is>
       </c>
     </row>
     <row r="394" ht="40" customHeight="1">
       <c r="A394" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.standard.bold[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B2_fighter2.standard.bold[2]</t>
         </is>
       </c>
       <c r="B394" t="inlineStr" s="2">
@@ -13036,7 +13014,7 @@
       </c>
       <c r="D394" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand.standard.bold[2]</t>
+          <t xml:space="preserve">B2_fighter2.standard.bold[2]</t>
         </is>
       </c>
       <c r="E394" t="inlineStr" s="2">
@@ -13046,14 +13024,14 @@
       </c>
       <c r="F394" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私が使ったら絶対売れる。任せて</t>
+          <t xml:space="preserve">正面からぶつかって決着つけるしかないわね</t>
         </is>
       </c>
     </row>
     <row r="395" ht="40" customHeight="1">
       <c r="A395" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.standard.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.standard.bold[1]</t>
         </is>
       </c>
       <c r="B395" t="inlineStr" s="2">
@@ -13068,7 +13046,7 @@
       </c>
       <c r="D395" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.standard.bold[1]</t>
+          <t xml:space="preserve">B4_brand.standard.bold[1]</t>
         </is>
       </c>
       <c r="E395" t="inlineStr" s="2">
@@ -13078,14 +13056,14 @@
       </c>
       <c r="F395" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">CMで私の顔を全国に売り込む。完璧にやってみせる</t>
+          <t xml:space="preserve">そのブランドのイメージ、私が底上げしてやる</t>
         </is>
       </c>
     </row>
     <row r="396" ht="40" customHeight="1">
       <c r="A396" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.standard.bold[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_brand.standard.bold[2]</t>
         </is>
       </c>
       <c r="B396" t="inlineStr" s="2">
@@ -13100,7 +13078,7 @@
       </c>
       <c r="D396" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm.standard.bold[2]</t>
+          <t xml:space="preserve">B4_brand.standard.bold[2]</t>
         </is>
       </c>
       <c r="E396" t="inlineStr" s="2">
@@ -13110,14 +13088,14 @@
       </c>
       <c r="F396" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">このチャンス、最大限に使ってやる</t>
+          <t xml:space="preserve">私が使ったら絶対売れる。任せて</t>
         </is>
       </c>
     </row>
     <row r="397" ht="40" customHeight="1">
       <c r="A397" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.standard.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.standard.bold[1]</t>
         </is>
       </c>
       <c r="B397" t="inlineStr" s="2">
@@ -13132,7 +13110,7 @@
       </c>
       <c r="D397" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.standard.bold[1]</t>
+          <t xml:space="preserve">B4_cm.standard.bold[1]</t>
         </is>
       </c>
       <c r="E397" t="inlineStr" s="2">
@@ -13142,14 +13120,14 @@
       </c>
       <c r="F397" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ファンに最高の思い出を作らせてやる</t>
+          <t xml:space="preserve">CMで私の顔を全国に売り込む。完璧にやってみせる</t>
         </is>
       </c>
     </row>
     <row r="398" ht="40" customHeight="1">
       <c r="A398" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.standard.bold[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_cm.standard.bold[2]</t>
         </is>
       </c>
       <c r="B398" t="inlineStr" s="2">
@@ -13164,7 +13142,7 @@
       </c>
       <c r="D398" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan.standard.bold[2]</t>
+          <t xml:space="preserve">B4_cm.standard.bold[2]</t>
         </is>
       </c>
       <c r="E398" t="inlineStr" s="2">
@@ -13174,14 +13152,14 @@
       </c>
       <c r="F398" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全員を笑顔にして帰らせる。それが私の仕事</t>
+          <t xml:space="preserve">このチャンス、最大限に使ってやる</t>
         </is>
       </c>
     </row>
     <row r="399" ht="40" customHeight="1">
       <c r="A399" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.standard.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.standard.bold[1]</t>
         </is>
       </c>
       <c r="B399" t="inlineStr" s="2">
@@ -13196,7 +13174,7 @@
       </c>
       <c r="D399" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.standard.bold[1]</t>
+          <t xml:space="preserve">B4_fan.standard.bold[1]</t>
         </is>
       </c>
       <c r="E399" t="inlineStr" s="2">
@@ -13206,14 +13184,14 @@
       </c>
       <c r="F399" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ランウェイも私のステージ。全部持っていく</t>
+          <t xml:space="preserve">ファンに最高の思い出を作らせてやる</t>
         </is>
       </c>
     </row>
     <row r="400" ht="40" customHeight="1">
       <c r="A400" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.standard.bold[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fan.standard.bold[2]</t>
         </is>
       </c>
       <c r="B400" t="inlineStr" s="2">
@@ -13228,7 +13206,7 @@
       </c>
       <c r="D400" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion.standard.bold[2]</t>
+          <t xml:space="preserve">B4_fan.standard.bold[2]</t>
         </is>
       </c>
       <c r="E400" t="inlineStr" s="2">
@@ -13238,14 +13216,14 @@
       </c>
       <c r="F400" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">プロレスもファッションも、どっちも私のもの</t>
+          <t xml:space="preserve">全員を笑顔にして帰らせる。それが私の仕事</t>
         </is>
       </c>
     </row>
     <row r="401" ht="40" customHeight="1">
       <c r="A401" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.standard.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.standard.bold[1]</t>
         </is>
       </c>
       <c r="B401" t="inlineStr" s="2">
@@ -13260,7 +13238,7 @@
       </c>
       <c r="D401" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.standard.bold[1]</t>
+          <t xml:space="preserve">B4_fashion.standard.bold[1]</t>
         </is>
       </c>
       <c r="E401" t="inlineStr" s="2">
@@ -13270,14 +13248,14 @@
       </c>
       <c r="F401" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私の強さと魅力、カメラに焼き付けてやる</t>
+          <t xml:space="preserve">ランウェイも私のステージ。全部持っていく</t>
         </is>
       </c>
     </row>
     <row r="402" ht="40" customHeight="1">
       <c r="A402" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.standard.bold[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_fashion.standard.bold[2]</t>
         </is>
       </c>
       <c r="B402" t="inlineStr" s="2">
@@ -13292,7 +13270,7 @@
       </c>
       <c r="D402" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure.standard.bold[2]</t>
+          <t xml:space="preserve">B4_fashion.standard.bold[2]</t>
         </is>
       </c>
       <c r="E402" t="inlineStr" s="2">
@@ -13302,14 +13280,14 @@
       </c>
       <c r="F402" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これで一気に知名度上げてやる</t>
+          <t xml:space="preserve">プロレスもファッションも、どっちも私のもの</t>
         </is>
       </c>
     </row>
     <row r="403" ht="40" customHeight="1">
       <c r="A403" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.standard.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.standard.bold[1]</t>
         </is>
       </c>
       <c r="B403" t="inlineStr" s="2">
@@ -13324,7 +13302,7 @@
       </c>
       <c r="D403" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.standard.bold[1]</t>
+          <t xml:space="preserve">B4_gravure.standard.bold[1]</t>
         </is>
       </c>
       <c r="E403" t="inlineStr" s="2">
@@ -13334,14 +13312,14 @@
       </c>
       <c r="F403" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">番組ジャックしてやる。全部持っていく</t>
+          <t xml:space="preserve">私の強さと魅力、カメラに焼き付けてやる</t>
         </is>
       </c>
     </row>
     <row r="404" ht="40" customHeight="1">
       <c r="A404" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.standard.bold[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_gravure.standard.bold[2]</t>
         </is>
       </c>
       <c r="B404" t="inlineStr" s="2">
@@ -13356,7 +13334,7 @@
       </c>
       <c r="D404" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety.standard.bold[2]</t>
+          <t xml:space="preserve">B4_gravure.standard.bold[2]</t>
         </is>
       </c>
       <c r="E404" t="inlineStr" s="2">
@@ -13366,14 +13344,14 @@
       </c>
       <c r="F404" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">トーク番組だろうと、私が主役に決まってる</t>
+          <t xml:space="preserve">これで一気に知名度上げてやる</t>
         </is>
       </c>
     </row>
     <row r="405" ht="40" customHeight="1">
       <c r="A405" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.standard.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.standard.bold[1]</t>
         </is>
       </c>
       <c r="B405" t="inlineStr" s="2">
@@ -13388,7 +13366,7 @@
       </c>
       <c r="D405" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.standard.bold[1]</t>
+          <t xml:space="preserve">B4_variety.standard.bold[1]</t>
         </is>
       </c>
       <c r="E405" t="inlineStr" s="2">
@@ -13398,14 +13376,14 @@
       </c>
       <c r="F405" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい機会ね。全国に私の実力を見せつけてやる</t>
+          <t xml:space="preserve">番組ジャックしてやる。全部持っていく</t>
         </is>
       </c>
     </row>
     <row r="406" ht="40" customHeight="1">
       <c r="A406" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.standard.bold[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4_variety.standard.bold[2]</t>
         </is>
       </c>
       <c r="B406" t="inlineStr" s="2">
@@ -13420,7 +13398,7 @@
       </c>
       <c r="D406" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.standard.bold[2]</t>
+          <t xml:space="preserve">B4_variety.standard.bold[2]</t>
         </is>
       </c>
       <c r="E406" t="inlineStr" s="2">
@@ -13430,14 +13408,14 @@
       </c>
       <c r="F406" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体の代表として、恥ずかしくない姿を見せる</t>
+          <t xml:space="preserve">トーク番組だろうと、私が主役に決まってる</t>
         </is>
       </c>
     </row>
     <row r="407" ht="40" customHeight="1">
       <c r="A407" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.standard.bold[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.standard.bold[1]</t>
         </is>
       </c>
       <c r="B407" t="inlineStr" s="2">
@@ -13447,29 +13425,29 @@
       </c>
       <c r="C407" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D407" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.bold[1]</t>
+          <t xml:space="preserve">B4.standard.bold[1]</t>
         </is>
       </c>
       <c r="E407" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F407" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">てっぺんを獲る。それ以外に興味はない</t>
+          <t xml:space="preserve">いい機会ね。全国に私の実力を見せつけてやる</t>
         </is>
       </c>
     </row>
     <row r="408" ht="40" customHeight="1">
       <c r="A408" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.standard.bold[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES.B4.standard.bold[2]</t>
         </is>
       </c>
       <c r="B408" t="inlineStr" s="2">
@@ -13479,29 +13457,29 @@
       </c>
       <c r="C408" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">LARGE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D408" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.bold[2]</t>
+          <t xml:space="preserve">B4.standard.bold[2]</t>
         </is>
       </c>
       <c r="E408" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F408" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私を選んでくれるなら、絶対に後悔はさせない！</t>
+          <t xml:space="preserve">団体の代表として、恥ずかしくない姿を見せる</t>
         </is>
       </c>
     </row>
     <row r="409" ht="40" customHeight="1">
       <c r="A409" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.standard.bold[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.standard.bold[1]</t>
         </is>
       </c>
       <c r="B409" t="inlineStr" s="2">
@@ -13511,7 +13489,7 @@
       </c>
       <c r="C409" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D409" t="inlineStr" s="12">
@@ -13526,14 +13504,14 @@
       </c>
       <c r="F409" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">てっぺんを獲りに来ました。ついてきてください</t>
+          <t xml:space="preserve">てっぺんを獲る。それ以外に興味はない</t>
         </is>
       </c>
     </row>
     <row r="410" ht="40" customHeight="1">
       <c r="A410" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.standard.bold[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.standard.bold[2]</t>
         </is>
       </c>
       <c r="B410" t="inlineStr" s="2">
@@ -13543,7 +13521,7 @@
       </c>
       <c r="C410" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D410" t="inlineStr" s="12">
@@ -13558,14 +13536,14 @@
       </c>
       <c r="F410" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体で、必ずチャンピオンになります</t>
+          <t xml:space="preserve">私を選んでくれるなら、絶対に後悔はさせない！</t>
         </is>
       </c>
     </row>
     <row r="411" ht="40" customHeight="1">
       <c r="A411" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.standard.bold[3]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.standard.bold[1]</t>
         </is>
       </c>
       <c r="B411" t="inlineStr" s="2">
@@ -13580,7 +13558,7 @@
       </c>
       <c r="D411" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.bold[3]</t>
+          <t xml:space="preserve">standard.bold[1]</t>
         </is>
       </c>
       <c r="E411" t="inlineStr" s="2">
@@ -13590,14 +13568,14 @@
       </c>
       <c r="F411" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">期待なんて軽く超えてみせる。見ててください</t>
+          <t xml:space="preserve">てっぺんを獲りに来ました。ついてきてください</t>
         </is>
       </c>
     </row>
     <row r="412" ht="40" customHeight="1">
       <c r="A412" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.standard.bold[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.standard.bold[2]</t>
         </is>
       </c>
       <c r="B412" t="inlineStr" s="2">
@@ -13607,12 +13585,12 @@
       </c>
       <c r="C412" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D412" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.bold[1]</t>
+          <t xml:space="preserve">standard.bold[2]</t>
         </is>
       </c>
       <c r="E412" t="inlineStr" s="2">
@@ -13622,14 +13600,14 @@
       </c>
       <c r="F412" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">てっぺんを獲るために来た。わかってるよな？</t>
+          <t xml:space="preserve">この団体で、必ずチャンピオンになります</t>
         </is>
       </c>
     </row>
     <row r="413" ht="40" customHeight="1">
       <c r="A413" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.standard.bold[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.standard.bold[3]</t>
         </is>
       </c>
       <c r="B413" t="inlineStr" s="2">
@@ -13639,12 +13617,12 @@
       </c>
       <c r="C413" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D413" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.bold[2]</t>
+          <t xml:space="preserve">standard.bold[3]</t>
         </is>
       </c>
       <c r="E413" t="inlineStr" s="2">
@@ -13654,14 +13632,14 @@
       </c>
       <c r="F413" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">新しい闘いの場…！燃えてきた！</t>
+          <t xml:space="preserve">期待なんて軽く超えてみせる。見ててください</t>
         </is>
       </c>
     </row>
     <row r="414" ht="40" customHeight="1">
       <c r="A414" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.standard.bold[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.standard.bold[1]</t>
         </is>
       </c>
       <c r="B414" t="inlineStr" s="2">
@@ -13671,7 +13649,7 @@
       </c>
       <c r="C414" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D414" t="inlineStr" s="12">
@@ -13686,14 +13664,14 @@
       </c>
       <c r="F414" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点まで一直線だ。邪魔はさせない</t>
+          <t xml:space="preserve">てっぺんを獲るために来た。わかってるよな？</t>
         </is>
       </c>
     </row>
     <row r="415" ht="40" customHeight="1">
       <c r="A415" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.standard.bold[2]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.standard.bold[2]</t>
         </is>
       </c>
       <c r="B415" t="inlineStr" s="2">
@@ -13703,7 +13681,7 @@
       </c>
       <c r="C415" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D415" t="inlineStr" s="12">
@@ -13718,14 +13696,14 @@
       </c>
       <c r="F415" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">燃えてきた…！早く試合がしたい！</t>
+          <t xml:space="preserve">新しい闘いの場…！燃えてきた！</t>
         </is>
       </c>
     </row>
     <row r="416" ht="40" customHeight="1">
       <c r="A416" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.standard.bold[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.standard.bold[1]</t>
         </is>
       </c>
       <c r="B416" t="inlineStr" s="2">
@@ -13735,7 +13713,7 @@
       </c>
       <c r="C416" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D416" t="inlineStr" s="12">
@@ -13750,14 +13728,14 @@
       </c>
       <c r="F416" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くっ…こんなところで止められるか！</t>
+          <t xml:space="preserve">頂点まで一直線だ。邪魔はさせない</t>
         </is>
       </c>
     </row>
     <row r="417" ht="40" customHeight="1">
       <c r="A417" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.standard.bold[2]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.standard.bold[2]</t>
         </is>
       </c>
       <c r="B417" t="inlineStr" s="2">
@@ -13767,7 +13745,7 @@
       </c>
       <c r="C417" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D417" t="inlineStr" s="12">
@@ -13782,14 +13760,14 @@
       </c>
       <c r="F417" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この程度、問題じゃない</t>
+          <t xml:space="preserve">燃えてきた…！早く試合がしたい！</t>
         </is>
       </c>
     </row>
     <row r="418" ht="40" customHeight="1">
       <c r="A418" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.standard.bold[3]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.standard.bold[1]</t>
         </is>
       </c>
       <c r="B418" t="inlineStr" s="2">
@@ -13804,7 +13782,7 @@
       </c>
       <c r="D418" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.bold[3]</t>
+          <t xml:space="preserve">standard.bold[1]</t>
         </is>
       </c>
       <c r="E418" t="inlineStr" s="2">
@@ -13814,14 +13792,14 @@
       </c>
       <c r="F418" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">早く戻る。絶対に遅れを取るもんか</t>
+          <t xml:space="preserve">くっ…こんなところで止められるか！</t>
         </is>
       </c>
     </row>
     <row r="419" ht="40" customHeight="1">
       <c r="A419" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.standard.bold[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.standard.bold[2]</t>
         </is>
       </c>
       <c r="B419" t="inlineStr" s="2">
@@ -13831,12 +13809,12 @@
       </c>
       <c r="C419" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D419" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.standard.bold[1]</t>
+          <t xml:space="preserve">standard.bold[2]</t>
         </is>
       </c>
       <c r="E419" t="inlineStr" s="2">
@@ -13846,14 +13824,14 @@
       </c>
       <c r="F419" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝った側が、いつまで覚えてなきゃいけないの</t>
+          <t xml:space="preserve">この程度、問題じゃない</t>
         </is>
       </c>
     </row>
     <row r="420" ht="40" customHeight="1">
       <c r="A420" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.standard.bold[2]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.standard.bold[3]</t>
         </is>
       </c>
       <c r="B420" t="inlineStr" s="2">
@@ -13863,12 +13841,12 @@
       </c>
       <c r="C420" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D420" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.standard.bold[2]</t>
+          <t xml:space="preserve">standard.bold[3]</t>
         </is>
       </c>
       <c r="E420" t="inlineStr" s="2">
@@ -13878,14 +13856,14 @@
       </c>
       <c r="F420" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">終わらせたのは私。付き合ってやるのは、これで最後</t>
+          <t xml:space="preserve">早く戻る。絶対に遅れを取るもんか</t>
         </is>
       </c>
     </row>
     <row r="421" ht="40" customHeight="1">
       <c r="A421" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.standard.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.standard.bold[1]</t>
         </is>
       </c>
       <c r="B421" t="inlineStr" s="2">
@@ -13900,7 +13878,7 @@
       </c>
       <c r="D421" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.standard.bold[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.standard.bold[1]</t>
         </is>
       </c>
       <c r="E421" t="inlineStr" s="2">
@@ -13910,14 +13888,14 @@
       </c>
       <c r="F421" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">終わりってことにされてる。でも私はまだ認めない</t>
+          <t xml:space="preserve">勝った側が、いつまで覚えてなきゃいけないの</t>
         </is>
       </c>
     </row>
     <row r="422" ht="40" customHeight="1">
       <c r="A422" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.standard.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.standard.bold[2]</t>
         </is>
       </c>
       <c r="B422" t="inlineStr" s="2">
@@ -13932,7 +13910,7 @@
       </c>
       <c r="D422" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.standard.bold[2]</t>
+          <t xml:space="preserve">bitterPrematch.ahead.standard.bold[2]</t>
         </is>
       </c>
       <c r="E422" t="inlineStr" s="2">
@@ -13942,14 +13920,14 @@
       </c>
       <c r="F422" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう格付けは済んでいるのかも。それでも・・・</t>
+          <t xml:space="preserve">終わらせたのは私。付き合ってやるのは、これで最後</t>
         </is>
       </c>
     </row>
     <row r="423" ht="40" customHeight="1">
       <c r="A423" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.standard.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.standard.bold[1]</t>
         </is>
       </c>
       <c r="B423" t="inlineStr" s="2">
@@ -13964,7 +13942,7 @@
       </c>
       <c r="D423" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.standard.bold[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind.standard.bold[1]</t>
         </is>
       </c>
       <c r="E423" t="inlineStr" s="2">
@@ -13974,14 +13952,14 @@
       </c>
       <c r="F423" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">てっぺんを獲る。それ以外に興味はない</t>
+          <t xml:space="preserve">終わりってことにされてる。でも私はまだ認めない</t>
         </is>
       </c>
     </row>
     <row r="424" ht="40" customHeight="1">
       <c r="A424" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.standard.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.standard.bold[2]</t>
         </is>
       </c>
       <c r="B424" t="inlineStr" s="2">
@@ -13996,7 +13974,7 @@
       </c>
       <c r="D424" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.standard.bold[2]</t>
+          <t xml:space="preserve">bitterPrematch.behind.standard.bold[2]</t>
         </is>
       </c>
       <c r="E424" t="inlineStr" s="2">
@@ -14006,14 +13984,14 @@
       </c>
       <c r="F424" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私を選んでくれるなら、絶対に後悔はさせない！</t>
+          <t xml:space="preserve">もう格付けは済んでいるのかも。それでも・・・</t>
         </is>
       </c>
     </row>
     <row r="425" ht="40" customHeight="1">
       <c r="A425" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.standard.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.standard.bold[1]</t>
         </is>
       </c>
       <c r="B425" t="inlineStr" s="2">
@@ -14028,7 +14006,7 @@
       </c>
       <c r="D425" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.standard.bold[1]</t>
+          <t xml:space="preserve">draftInterest.standard.bold[1]</t>
         </is>
       </c>
       <c r="E425" t="inlineStr" s="2">
@@ -14038,14 +14016,14 @@
       </c>
       <c r="F425" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">てっぺんを獲りに来ました。ついてきてください</t>
+          <t xml:space="preserve">てっぺんを獲る。それ以外に興味はない</t>
         </is>
       </c>
     </row>
     <row r="426" ht="40" customHeight="1">
       <c r="A426" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.standard.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.standard.bold[2]</t>
         </is>
       </c>
       <c r="B426" t="inlineStr" s="2">
@@ -14060,7 +14038,7 @@
       </c>
       <c r="D426" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.standard.bold[2]</t>
+          <t xml:space="preserve">draftInterest.standard.bold[2]</t>
         </is>
       </c>
       <c r="E426" t="inlineStr" s="2">
@@ -14070,14 +14048,14 @@
       </c>
       <c r="F426" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体で、必ずチャンピオンになります</t>
+          <t xml:space="preserve">私を選んでくれるなら、絶対に後悔はさせない！</t>
         </is>
       </c>
     </row>
     <row r="427" ht="40" customHeight="1">
       <c r="A427" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.standard.bold[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.standard.bold[1]</t>
         </is>
       </c>
       <c r="B427" t="inlineStr" s="2">
@@ -14092,7 +14070,7 @@
       </c>
       <c r="D427" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.standard.bold[3]</t>
+          <t xml:space="preserve">draftJoin.standard.bold[1]</t>
         </is>
       </c>
       <c r="E427" t="inlineStr" s="2">
@@ -14102,14 +14080,14 @@
       </c>
       <c r="F427" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">期待なんて軽く超えてみせる。見ててください</t>
+          <t xml:space="preserve">てっぺんを獲りに来ました。ついてきてください</t>
         </is>
       </c>
     </row>
     <row r="428" ht="40" customHeight="1">
       <c r="A428" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.standard.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.standard.bold[2]</t>
         </is>
       </c>
       <c r="B428" t="inlineStr" s="2">
@@ -14124,7 +14102,7 @@
       </c>
       <c r="D428" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.standard.bold[1]</t>
+          <t xml:space="preserve">draftJoin.standard.bold[2]</t>
         </is>
       </c>
       <c r="E428" t="inlineStr" s="2">
@@ -14134,14 +14112,14 @@
       </c>
       <c r="F428" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">フリーのままで終わる女じゃないって、証明する</t>
+          <t xml:space="preserve">この団体で、必ずチャンピオンになります</t>
         </is>
       </c>
     </row>
     <row r="429" ht="40" customHeight="1">
       <c r="A429" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.standard.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.standard.bold[3]</t>
         </is>
       </c>
       <c r="B429" t="inlineStr" s="2">
@@ -14156,7 +14134,7 @@
       </c>
       <c r="D429" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.standard.bold[2]</t>
+          <t xml:space="preserve">draftJoin.standard.bold[3]</t>
         </is>
       </c>
       <c r="E429" t="inlineStr" s="2">
@@ -14166,14 +14144,14 @@
       </c>
       <c r="F429" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">払ってくれた分は、全部利子つけて返してやる</t>
+          <t xml:space="preserve">期待なんて軽く超えてみせる。見ててください</t>
         </is>
       </c>
     </row>
     <row r="430" ht="40" customHeight="1">
       <c r="A430" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.standard.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.standard.bold[1]</t>
         </is>
       </c>
       <c r="B430" t="inlineStr" s="2">
@@ -14188,7 +14166,7 @@
       </c>
       <c r="D430" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.standard.bold[1]</t>
+          <t xml:space="preserve">faGreeting.standard.bold[1]</t>
         </is>
       </c>
       <c r="E430" t="inlineStr" s="2">
@@ -14198,14 +14176,14 @@
       </c>
       <c r="F430" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">てっぺんを獲るために来た。わかってるよな？</t>
+          <t xml:space="preserve">フリーのままで終わる女じゃないって、証明する</t>
         </is>
       </c>
     </row>
     <row r="431" ht="40" customHeight="1">
       <c r="A431" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.standard.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.standard.bold[2]</t>
         </is>
       </c>
       <c r="B431" t="inlineStr" s="2">
@@ -14220,7 +14198,7 @@
       </c>
       <c r="D431" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.standard.bold[2]</t>
+          <t xml:space="preserve">faGreeting.standard.bold[2]</t>
         </is>
       </c>
       <c r="E431" t="inlineStr" s="2">
@@ -14230,14 +14208,14 @@
       </c>
       <c r="F431" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">新しい闘いの場…！燃えてきた！</t>
+          <t xml:space="preserve">払ってくれた分は、全部利子つけて返してやる</t>
         </is>
       </c>
     </row>
     <row r="432" ht="40" customHeight="1">
       <c r="A432" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.standard.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.standard.bold[1]</t>
         </is>
       </c>
       <c r="B432" t="inlineStr" s="2">
@@ -14252,7 +14230,7 @@
       </c>
       <c r="D432" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.standard.bold[1]</t>
+          <t xml:space="preserve">faSigning.standard.bold[1]</t>
         </is>
       </c>
       <c r="E432" t="inlineStr" s="2">
@@ -14262,14 +14240,14 @@
       </c>
       <c r="F432" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">頂点まで一直線だ。邪魔はさせない</t>
+          <t xml:space="preserve">てっぺんを獲るために来た。わかってるよな？</t>
         </is>
       </c>
     </row>
     <row r="433" ht="40" customHeight="1">
       <c r="A433" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.standard.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.standard.bold[2]</t>
         </is>
       </c>
       <c r="B433" t="inlineStr" s="2">
@@ -14284,7 +14262,7 @@
       </c>
       <c r="D433" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.standard.bold[2]</t>
+          <t xml:space="preserve">faSigning.standard.bold[2]</t>
         </is>
       </c>
       <c r="E433" t="inlineStr" s="2">
@@ -14294,14 +14272,14 @@
       </c>
       <c r="F433" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">燃えてきた…！早く試合がしたい！</t>
+          <t xml:space="preserve">新しい闘いの場…！燃えてきた！</t>
         </is>
       </c>
     </row>
     <row r="434" ht="40" customHeight="1">
       <c r="A434" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.standard.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.standard.bold[1]</t>
         </is>
       </c>
       <c r="B434" t="inlineStr" s="2">
@@ -14316,7 +14294,7 @@
       </c>
       <c r="D434" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.standard.bold[1]</t>
+          <t xml:space="preserve">faWelcome.standard.bold[1]</t>
         </is>
       </c>
       <c r="E434" t="inlineStr" s="2">
@@ -14326,14 +14304,14 @@
       </c>
       <c r="F434" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">体が動きたがってる。もっとやらせてくれない?</t>
+          <t xml:space="preserve">頂点まで一直線だ。邪魔はさせない</t>
         </is>
       </c>
     </row>
     <row r="435" ht="40" customHeight="1">
       <c r="A435" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.standard.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.standard.bold[2]</t>
         </is>
       </c>
       <c r="B435" t="inlineStr" s="2">
@@ -14348,7 +14326,7 @@
       </c>
       <c r="D435" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.standard.bold[1]</t>
+          <t xml:space="preserve">faWelcome.standard.bold[2]</t>
         </is>
       </c>
       <c r="E435" t="inlineStr" s="2">
@@ -14358,14 +14336,14 @@
       </c>
       <c r="F435" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">重い。…でも止まらない。止まったら負けた気がする</t>
+          <t xml:space="preserve">燃えてきた…！早く試合がしたい！</t>
         </is>
       </c>
     </row>
     <row r="436" ht="40" customHeight="1">
       <c r="A436" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.standard.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.standard.bold[1]</t>
         </is>
       </c>
       <c r="B436" t="inlineStr" s="2">
@@ -14380,7 +14358,7 @@
       </c>
       <c r="D436" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.standard.bold[1]</t>
+          <t xml:space="preserve">heatSelf.fresh.standard.bold[1]</t>
         </is>
       </c>
       <c r="E436" t="inlineStr" s="2">
@@ -14390,14 +14368,14 @@
       </c>
       <c r="F436" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだやれる。…切れが鈍った? 気のせいだって</t>
+          <t xml:space="preserve">体が動きたがってる。もっとやらせてくれない?</t>
         </is>
       </c>
     </row>
     <row r="437" ht="40" customHeight="1">
       <c r="A437" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.standard.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.standard.bold[1]</t>
         </is>
       </c>
       <c r="B437" t="inlineStr" s="2">
@@ -14412,7 +14390,7 @@
       </c>
       <c r="D437" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.standard.bold[1]</t>
+          <t xml:space="preserve">heatSelf.heavy.standard.bold[1]</t>
         </is>
       </c>
       <c r="E437" t="inlineStr" s="2">
@@ -14422,14 +14400,14 @@
       </c>
       <c r="F437" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くっ…こんなところで止められるか！</t>
+          <t xml:space="preserve">重い。…でも止まらない。止まったら負けた気がする</t>
         </is>
       </c>
     </row>
     <row r="438" ht="40" customHeight="1">
       <c r="A438" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.standard.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.standard.bold[1]</t>
         </is>
       </c>
       <c r="B438" t="inlineStr" s="2">
@@ -14444,7 +14422,7 @@
       </c>
       <c r="D438" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.standard.bold[2]</t>
+          <t xml:space="preserve">heatSelf.warm.standard.bold[1]</t>
         </is>
       </c>
       <c r="E438" t="inlineStr" s="2">
@@ -14454,14 +14432,14 @@
       </c>
       <c r="F438" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この程度、問題じゃない</t>
+          <t xml:space="preserve">まだやれる。…切れが鈍った? 気のせいだって</t>
         </is>
       </c>
     </row>
     <row r="439" ht="40" customHeight="1">
       <c r="A439" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.standard.bold[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.standard.bold[1]</t>
         </is>
       </c>
       <c r="B439" t="inlineStr" s="2">
@@ -14476,7 +14454,7 @@
       </c>
       <c r="D439" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.standard.bold[3]</t>
+          <t xml:space="preserve">injury.standard.bold[1]</t>
         </is>
       </c>
       <c r="E439" t="inlineStr" s="2">
@@ -14486,14 +14464,14 @@
       </c>
       <c r="F439" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">早く戻る。絶対に遅れを取るもんか</t>
+          <t xml:space="preserve">くっ…こんなところで止められるか！</t>
         </is>
       </c>
     </row>
     <row r="440" ht="40" customHeight="1">
       <c r="A440" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.standard.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.standard.bold[2]</t>
         </is>
       </c>
       <c r="B440" t="inlineStr" s="2">
@@ -14508,7 +14486,7 @@
       </c>
       <c r="D440" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.standard.bold[1]</t>
+          <t xml:space="preserve">injury.standard.bold[2]</t>
         </is>
       </c>
       <c r="E440" t="inlineStr" s="2">
@@ -14518,14 +14496,14 @@
       </c>
       <c r="F440" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わかった。どこかで強くなって戻る</t>
+          <t xml:space="preserve">この程度、問題じゃない</t>
         </is>
       </c>
     </row>
     <row r="441" ht="40" customHeight="1">
       <c r="A441" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.standard.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.standard.bold[3]</t>
         </is>
       </c>
       <c r="B441" t="inlineStr" s="2">
@@ -14540,7 +14518,7 @@
       </c>
       <c r="D441" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.standard.bold[2]</t>
+          <t xml:space="preserve">injury.standard.bold[3]</t>
         </is>
       </c>
       <c r="E441" t="inlineStr" s="2">
@@ -14550,14 +14528,14 @@
       </c>
       <c r="F441" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいけど…次の場所で証明してみせる</t>
+          <t xml:space="preserve">早く戻る。絶対に遅れを取るもんか</t>
         </is>
       </c>
     </row>
     <row r="442" ht="40" customHeight="1">
       <c r="A442" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.standard.bold[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.standard.bold[1]</t>
         </is>
       </c>
       <c r="B442" t="inlineStr" s="2">
@@ -14572,7 +14550,7 @@
       </c>
       <c r="D442" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.standard.bold[3]</t>
+          <t xml:space="preserve">release.standard.bold[1]</t>
         </is>
       </c>
       <c r="E442" t="inlineStr" s="2">
@@ -14582,14 +14560,14 @@
       </c>
       <c r="F442" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここで終わるつもりはない。絶対に這い上がる</t>
+          <t xml:space="preserve">わかった。どこかで強くなって戻る</t>
         </is>
       </c>
     </row>
     <row r="443" ht="40" customHeight="1">
       <c r="A443" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.standard.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.standard.bold[2]</t>
         </is>
       </c>
       <c r="B443" t="inlineStr" s="2">
@@ -14604,7 +14582,7 @@
       </c>
       <c r="D443" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.standard.bold[1]</t>
+          <t xml:space="preserve">release.standard.bold[2]</t>
         </is>
       </c>
       <c r="E443" t="inlineStr" s="2">
@@ -14614,14 +14592,14 @@
       </c>
       <c r="F443" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">レンタルだからって舐めるなよ！全試合全力だ！</t>
+          <t xml:space="preserve">悔しいけど…次の場所で証明してみせる</t>
         </is>
       </c>
     </row>
     <row r="444" ht="40" customHeight="1">
       <c r="A444" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.standard.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.standard.bold[3]</t>
         </is>
       </c>
       <c r="B444" t="inlineStr" s="2">
@@ -14636,7 +14614,7 @@
       </c>
       <c r="D444" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.standard.bold[2]</t>
+          <t xml:space="preserve">release.standard.bold[3]</t>
         </is>
       </c>
       <c r="E444" t="inlineStr" s="2">
@@ -14646,14 +14624,14 @@
       </c>
       <c r="F444" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よその団体でも闘志は変わらない！燃えるぞ！</t>
+          <t xml:space="preserve">ここで終わるつもりはない。絶対に這い上がる</t>
         </is>
       </c>
     </row>
     <row r="445" ht="40" customHeight="1">
       <c r="A445" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.standard.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.standard.bold[1]</t>
         </is>
       </c>
       <c r="B445" t="inlineStr" s="2">
@@ -14668,7 +14646,7 @@
       </c>
       <c r="D445" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.standard.bold[1]</t>
+          <t xml:space="preserve">rentalGreeting.standard.bold[1]</t>
         </is>
       </c>
       <c r="E445" t="inlineStr" s="2">
@@ -14678,14 +14656,14 @@
       </c>
       <c r="F445" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">見る目あるじゃん。すぐ活躍してみせるよ</t>
+          <t xml:space="preserve">レンタルだからって舐めるなよ！全試合全力だ！</t>
         </is>
       </c>
     </row>
     <row r="446" ht="40" customHeight="1">
       <c r="A446" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.standard.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.standard.bold[2]</t>
         </is>
       </c>
       <c r="B446" t="inlineStr" s="2">
@@ -14700,7 +14678,7 @@
       </c>
       <c r="D446" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.standard.bold[2]</t>
+          <t xml:space="preserve">rentalGreeting.standard.bold[2]</t>
         </is>
       </c>
       <c r="E446" t="inlineStr" s="2">
@@ -14710,14 +14688,14 @@
       </c>
       <c r="F446" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">買われた実力、値段以上だったって言わせてみせるよ</t>
+          <t xml:space="preserve">よその団体でも闘志は変わらない！燃えるぞ！</t>
         </is>
       </c>
     </row>
     <row r="447" ht="40" customHeight="1">
       <c r="A447" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.standard.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.standard.bold[1]</t>
         </is>
       </c>
       <c r="B447" t="inlineStr" s="2">
@@ -14732,7 +14710,7 @@
       </c>
       <c r="D447" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.standard.bold[1]</t>
+          <t xml:space="preserve">scoutGreeting.standard.bold[1]</t>
         </is>
       </c>
       <c r="E447" t="inlineStr" s="2">
@@ -14742,14 +14720,14 @@
       </c>
       <c r="F447" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くっ…！こんなの認めない！もう一回やらせてくれ！</t>
+          <t xml:space="preserve">見る目あるじゃん。すぐ活躍してみせるよ</t>
         </is>
       </c>
     </row>
     <row r="448" ht="40" customHeight="1">
       <c r="A448" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.standard.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.standard.bold[2]</t>
         </is>
       </c>
       <c r="B448" t="inlineStr" s="2">
@@ -14764,7 +14742,7 @@
       </c>
       <c r="D448" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.standard.bold[2]</t>
+          <t xml:space="preserve">scoutGreeting.standard.bold[2]</t>
         </is>
       </c>
       <c r="E448" t="inlineStr" s="2">
@@ -14774,14 +14752,14 @@
       </c>
       <c r="F448" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…今日は認める。でもこの借りは必ず返す</t>
+          <t xml:space="preserve">買われた実力、値段以上だったって言わせてみせるよ</t>
         </is>
       </c>
     </row>
     <row r="449" ht="40" customHeight="1">
       <c r="A449" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.standard.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.standard.bold[1]</t>
         </is>
       </c>
       <c r="B449" t="inlineStr" s="2">
@@ -14796,7 +14774,7 @@
       </c>
       <c r="D449" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.standard.bold[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.standard.bold[1]</t>
         </is>
       </c>
       <c r="E449" t="inlineStr" s="2">
@@ -14806,14 +14784,14 @@
       </c>
       <c r="F449" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ誰にもこの座は譲れない。もっと来い！</t>
+          <t xml:space="preserve">くっ…！こんなの認めない！もう一回やらせてくれ！</t>
         </is>
       </c>
     </row>
     <row r="450" ht="40" customHeight="1">
       <c r="A450" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.standard.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.standard.bold[2]</t>
         </is>
       </c>
       <c r="B450" t="inlineStr" s="2">
@@ -14828,7 +14806,7 @@
       </c>
       <c r="D450" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.standard.bold[2]</t>
+          <t xml:space="preserve">titleChallengeLoss.standard.bold[2]</t>
         </is>
       </c>
       <c r="E450" t="inlineStr" s="2">
@@ -14838,14 +14816,14 @@
       </c>
       <c r="F450" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛は通過点。私が目指すのはもっと先だ</t>
+          <t xml:space="preserve">…今日は認める。でもこの借りは必ず返す</t>
         </is>
       </c>
     </row>
     <row r="451" ht="40" customHeight="1">
       <c r="A451" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.standard.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.standard.bold[1]</t>
         </is>
       </c>
       <c r="B451" t="inlineStr" s="2">
@@ -14860,7 +14838,7 @@
       </c>
       <c r="D451" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.standard.bold[1]</t>
+          <t xml:space="preserve">titleDefense.standard.bold[1]</t>
         </is>
       </c>
       <c r="E451" t="inlineStr" s="2">
@@ -14870,14 +14848,14 @@
       </c>
       <c r="F451" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嘘だろ…！私のベルトが…！絶対に取り返す！</t>
+          <t xml:space="preserve">まだ誰にもこの座は譲れない。もっと来い！</t>
         </is>
       </c>
     </row>
     <row r="452" ht="40" customHeight="1">
       <c r="A452" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.standard.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.standard.bold[2]</t>
         </is>
       </c>
       <c r="B452" t="inlineStr" s="2">
@@ -14892,7 +14870,7 @@
       </c>
       <c r="D452" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.standard.bold[2]</t>
+          <t xml:space="preserve">titleDefense.standard.bold[2]</t>
         </is>
       </c>
       <c r="E452" t="inlineStr" s="2">
@@ -14902,14 +14880,14 @@
       </c>
       <c r="F452" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルトを失った…でもこの悔しさが次の炎になる</t>
+          <t xml:space="preserve">防衛は通過点。私が目指すのはもっと先だ</t>
         </is>
       </c>
     </row>
     <row r="453" ht="40" customHeight="1">
       <c r="A453" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.standard.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.standard.bold[1]</t>
         </is>
       </c>
       <c r="B453" t="inlineStr" s="2">
@@ -14924,7 +14902,7 @@
       </c>
       <c r="D453" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.standard.bold[1]</t>
+          <t xml:space="preserve">titleLoss.standard.bold[1]</t>
         </is>
       </c>
       <c r="E453" t="inlineStr" s="2">
@@ -14934,14 +14912,14 @@
       </c>
       <c r="F453" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">てっぺんに立った。でもまだ足りない…もっと上へ</t>
+          <t xml:space="preserve">嘘だろ…！私のベルトが…！絶対に取り返す！</t>
         </is>
       </c>
     </row>
     <row r="454" ht="40" customHeight="1">
       <c r="A454" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.standard.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.standard.bold[2]</t>
         </is>
       </c>
       <c r="B454" t="inlineStr" s="2">
@@ -14956,7 +14934,7 @@
       </c>
       <c r="D454" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.standard.bold[2]</t>
+          <t xml:space="preserve">titleLoss.standard.bold[2]</t>
         </is>
       </c>
       <c r="E454" t="inlineStr" s="2">
@@ -14966,14 +14944,14 @@
       </c>
       <c r="F454" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この炎は消えない。ベルトを懸けて、もっと熱い闘いを！</t>
+          <t xml:space="preserve">ベルトを失った…でもこの悔しさが次の炎になる</t>
         </is>
       </c>
     </row>
     <row r="455" ht="40" customHeight="1">
       <c r="A455" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.standard.bold[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.standard.bold[1]</t>
         </is>
       </c>
       <c r="B455" t="inlineStr" s="2">
@@ -14983,12 +14961,12 @@
       </c>
       <c r="C455" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D455" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.bold[1]</t>
+          <t xml:space="preserve">titleWin.standard.bold[1]</t>
         </is>
       </c>
       <c r="E455" t="inlineStr" s="2">
@@ -14998,14 +14976,14 @@
       </c>
       <c r="F455" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わかった。どこかで強くなって戻る</t>
+          <t xml:space="preserve">てっぺんに立った。でもまだ足りない…もっと上へ</t>
         </is>
       </c>
     </row>
     <row r="456" ht="40" customHeight="1">
       <c r="A456" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.standard.bold[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.standard.bold[2]</t>
         </is>
       </c>
       <c r="B456" t="inlineStr" s="2">
@@ -15015,12 +14993,12 @@
       </c>
       <c r="C456" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D456" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.bold[2]</t>
+          <t xml:space="preserve">titleWin.standard.bold[2]</t>
         </is>
       </c>
       <c r="E456" t="inlineStr" s="2">
@@ -15030,14 +15008,14 @@
       </c>
       <c r="F456" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいけど…次の場所で証明してみせる</t>
+          <t xml:space="preserve">この炎は消えない。ベルトを懸けて、もっと熱い闘いを！</t>
         </is>
       </c>
     </row>
     <row r="457" ht="40" customHeight="1">
       <c r="A457" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.standard.bold[3]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.standard.bold[1]</t>
         </is>
       </c>
       <c r="B457" t="inlineStr" s="2">
@@ -15052,7 +15030,7 @@
       </c>
       <c r="D457" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.bold[3]</t>
+          <t xml:space="preserve">standard.bold[1]</t>
         </is>
       </c>
       <c r="E457" t="inlineStr" s="2">
@@ -15062,14 +15040,14 @@
       </c>
       <c r="F457" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここで終わるつもりはない。絶対に這い上がる</t>
+          <t xml:space="preserve">わかった。どこかで強くなって戻る</t>
         </is>
       </c>
     </row>
     <row r="458" ht="40" customHeight="1">
       <c r="A458" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.standard.bold[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.standard.bold[2]</t>
         </is>
       </c>
       <c r="B458" t="inlineStr" s="2">
@@ -15079,12 +15057,12 @@
       </c>
       <c r="C458" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D458" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.bold[1]</t>
+          <t xml:space="preserve">standard.bold[2]</t>
         </is>
       </c>
       <c r="E458" t="inlineStr" s="2">
@@ -15094,14 +15072,14 @@
       </c>
       <c r="F458" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">レンタルだからって舐めるなよ！全試合全力だ！</t>
+          <t xml:space="preserve">悔しいけど…次の場所で証明してみせる</t>
         </is>
       </c>
     </row>
     <row r="459" ht="40" customHeight="1">
       <c r="A459" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.standard.bold[2]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.standard.bold[3]</t>
         </is>
       </c>
       <c r="B459" t="inlineStr" s="2">
@@ -15111,12 +15089,12 @@
       </c>
       <c r="C459" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D459" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.bold[2]</t>
+          <t xml:space="preserve">standard.bold[3]</t>
         </is>
       </c>
       <c r="E459" t="inlineStr" s="2">
@@ -15126,14 +15104,14 @@
       </c>
       <c r="F459" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よその団体でも闘志は変わらない！燃えるぞ！</t>
+          <t xml:space="preserve">ここで終わるつもりはない。絶対に這い上がる</t>
         </is>
       </c>
     </row>
     <row r="460" ht="40" customHeight="1">
       <c r="A460" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.standard.bold[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.standard.bold[1]</t>
         </is>
       </c>
       <c r="B460" t="inlineStr" s="2">
@@ -15143,7 +15121,7 @@
       </c>
       <c r="C460" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D460" t="inlineStr" s="12">
@@ -15158,14 +15136,14 @@
       </c>
       <c r="F460" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くっ…！こんなの認めない！もう一回やらせてくれ！</t>
+          <t xml:space="preserve">レンタルだからって舐めるなよ！全試合全力だ！</t>
         </is>
       </c>
     </row>
     <row r="461" ht="40" customHeight="1">
       <c r="A461" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.standard.bold[2]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.standard.bold[2]</t>
         </is>
       </c>
       <c r="B461" t="inlineStr" s="2">
@@ -15175,7 +15153,7 @@
       </c>
       <c r="C461" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D461" t="inlineStr" s="12">
@@ -15190,14 +15168,14 @@
       </c>
       <c r="F461" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…今日は認める。でもこの借りは必ず返す</t>
+          <t xml:space="preserve">よその団体でも闘志は変わらない！燃えるぞ！</t>
         </is>
       </c>
     </row>
     <row r="462" ht="40" customHeight="1">
       <c r="A462" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.standard.bold[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.standard.bold[1]</t>
         </is>
       </c>
       <c r="B462" t="inlineStr" s="2">
@@ -15207,7 +15185,7 @@
       </c>
       <c r="C462" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D462" t="inlineStr" s="12">
@@ -15222,14 +15200,14 @@
       </c>
       <c r="F462" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ誰にもこの座は譲れない。もっと来い！</t>
+          <t xml:space="preserve">くっ…！こんなの認めない！もう一回やらせてくれ！</t>
         </is>
       </c>
     </row>
     <row r="463" ht="40" customHeight="1">
       <c r="A463" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.standard.bold[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.standard.bold[2]</t>
         </is>
       </c>
       <c r="B463" t="inlineStr" s="2">
@@ -15239,7 +15217,7 @@
       </c>
       <c r="C463" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D463" t="inlineStr" s="12">
@@ -15254,14 +15232,14 @@
       </c>
       <c r="F463" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">防衛は通過点。私が目指すのはもっと先だ</t>
+          <t xml:space="preserve">…今日は認める。でもこの借りは必ず返す</t>
         </is>
       </c>
     </row>
     <row r="464" ht="40" customHeight="1">
       <c r="A464" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.standard.bold[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.standard.bold[1]</t>
         </is>
       </c>
       <c r="B464" t="inlineStr" s="2">
@@ -15271,7 +15249,7 @@
       </c>
       <c r="C464" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D464" t="inlineStr" s="12">
@@ -15286,14 +15264,14 @@
       </c>
       <c r="F464" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">嘘だろ…！私のベルトが…！絶対に取り返す！</t>
+          <t xml:space="preserve">まだ誰にもこの座は譲れない。もっと来い！</t>
         </is>
       </c>
     </row>
     <row r="465" ht="40" customHeight="1">
       <c r="A465" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.standard.bold[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.standard.bold[2]</t>
         </is>
       </c>
       <c r="B465" t="inlineStr" s="2">
@@ -15303,7 +15281,7 @@
       </c>
       <c r="C465" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D465" t="inlineStr" s="12">
@@ -15318,14 +15296,14 @@
       </c>
       <c r="F465" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルトを失った…でもこの悔しさが次の炎になる</t>
+          <t xml:space="preserve">防衛は通過点。私が目指すのはもっと先だ</t>
         </is>
       </c>
     </row>
     <row r="466" ht="40" customHeight="1">
       <c r="A466" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.standard.bold[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.standard.bold[1]</t>
         </is>
       </c>
       <c r="B466" t="inlineStr" s="2">
@@ -15335,7 +15313,7 @@
       </c>
       <c r="C466" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D466" t="inlineStr" s="12">
@@ -15350,14 +15328,14 @@
       </c>
       <c r="F466" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">てっぺんに立った。でもまだ足りない…もっと上へ</t>
+          <t xml:space="preserve">嘘だろ…！私のベルトが…！絶対に取り返す！</t>
         </is>
       </c>
     </row>
     <row r="467" ht="40" customHeight="1">
       <c r="A467" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.standard.bold[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.standard.bold[2]</t>
         </is>
       </c>
       <c r="B467" t="inlineStr" s="2">
@@ -15367,7 +15345,7 @@
       </c>
       <c r="C467" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D467" t="inlineStr" s="12">
@@ -15382,14 +15360,14 @@
       </c>
       <c r="F467" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この炎は消えない。ベルトを懸けて、もっと熱い闘いを！</t>
+          <t xml:space="preserve">ベルトを失った…でもこの悔しさが次の炎になる</t>
         </is>
       </c>
     </row>
     <row r="468" ht="40" customHeight="1">
       <c r="A468" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.standard[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.standard.bold[1]</t>
         </is>
       </c>
       <c r="B468" t="inlineStr" s="2">
@@ -15399,29 +15377,29 @@
       </c>
       <c r="C468" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D468" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.bold.standard[1]</t>
+          <t xml:space="preserve">standard.bold[1]</t>
         </is>
       </c>
       <c r="E468" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F468" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">合わない。どうしても合わない</t>
+          <t xml:space="preserve">てっぺんに立った。でもまだ足りない…もっと上へ</t>
         </is>
       </c>
     </row>
     <row r="469" ht="40" customHeight="1">
       <c r="A469" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.standard[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.standard.bold[2]</t>
         </is>
       </c>
       <c r="B469" t="inlineStr" s="2">
@@ -15431,29 +15409,29 @@
       </c>
       <c r="C469" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D469" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.bold.standard[2]</t>
+          <t xml:space="preserve">standard.bold[2]</t>
         </is>
       </c>
       <c r="E469" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F469" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これ以上は無理ね。それだけ</t>
+          <t xml:space="preserve">この炎は消えない。ベルトを懸けて、もっと熱い闘いを！</t>
         </is>
       </c>
     </row>
     <row r="470" ht="40" customHeight="1">
       <c r="A470" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.standard[1]</t>
         </is>
       </c>
       <c r="B470" t="inlineStr" s="2">
@@ -15468,7 +15446,7 @@
       </c>
       <c r="D470" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.bold.standard[1]</t>
+          <t xml:space="preserve">bond_39_down.bold.standard[1]</t>
         </is>
       </c>
       <c r="E470" t="inlineStr" s="2">
@@ -15478,14 +15456,14 @@
       </c>
       <c r="F470" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんか壁作ってない？ 気に入らないな</t>
+          <t xml:space="preserve">合わない。どうしても合わない</t>
         </is>
       </c>
     </row>
     <row r="471" ht="40" customHeight="1">
       <c r="A471" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.bold.standard[2]</t>
         </is>
       </c>
       <c r="B471" t="inlineStr" s="2">
@@ -15500,7 +15478,7 @@
       </c>
       <c r="D471" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.bold.standard[2]</t>
+          <t xml:space="preserve">bond_39_down.bold.standard[2]</t>
         </is>
       </c>
       <c r="E471" t="inlineStr" s="2">
@@ -15510,14 +15488,14 @@
       </c>
       <c r="F471" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">前はもっと話してたのに。…何なの</t>
+          <t xml:space="preserve">これ以上は無理ね。それだけ</t>
         </is>
       </c>
     </row>
     <row r="472" ht="40" customHeight="1">
       <c r="A472" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.bold.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.standard[1]</t>
         </is>
       </c>
       <c r="B472" t="inlineStr" s="2">
@@ -15532,7 +15510,7 @@
       </c>
       <c r="D472" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.bold.standard[1]</t>
+          <t xml:space="preserve">bond_59_down.bold.standard[1]</t>
         </is>
       </c>
       <c r="E472" t="inlineStr" s="2">
@@ -15542,14 +15520,14 @@
       </c>
       <c r="F472" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい空気ね。背中を預けられそう</t>
+          <t xml:space="preserve">なんか壁作ってない？ 気に入らないな</t>
         </is>
       </c>
     </row>
     <row r="473" ht="40" customHeight="1">
       <c r="A473" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.bold.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.bold.standard[2]</t>
         </is>
       </c>
       <c r="B473" t="inlineStr" s="2">
@@ -15564,7 +15542,7 @@
       </c>
       <c r="D473" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.bold.standard[2]</t>
+          <t xml:space="preserve">bond_59_down.bold.standard[2]</t>
         </is>
       </c>
       <c r="E473" t="inlineStr" s="2">
@@ -15574,14 +15552,14 @@
       </c>
       <c r="F473" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なかなかやるじゃない。認めてあげてもいいかな</t>
+          <t xml:space="preserve">前はもっと話してたのに。…何なの</t>
         </is>
       </c>
     </row>
     <row r="474" ht="40" customHeight="1">
       <c r="A474" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.bold.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.bold.standard[1]</t>
         </is>
       </c>
       <c r="B474" t="inlineStr" s="2">
@@ -15596,7 +15574,7 @@
       </c>
       <c r="D474" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.bold.standard[1]</t>
+          <t xml:space="preserve">bond_60_up.bold.standard[1]</t>
         </is>
       </c>
       <c r="E474" t="inlineStr" s="2">
@@ -15606,14 +15584,14 @@
       </c>
       <c r="F474" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高のコンビね。誰にも負けない</t>
+          <t xml:space="preserve">いい空気ね。背中を預けられそう</t>
         </is>
       </c>
     </row>
     <row r="475" ht="40" customHeight="1">
       <c r="A475" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.bold.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.bold.standard[2]</t>
         </is>
       </c>
       <c r="B475" t="inlineStr" s="2">
@@ -15628,7 +15606,7 @@
       </c>
       <c r="D475" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.bold.standard[2]</t>
+          <t xml:space="preserve">bond_60_up.bold.standard[2]</t>
         </is>
       </c>
       <c r="E475" t="inlineStr" s="2">
@@ -15638,14 +15616,14 @@
       </c>
       <c r="F475" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">二人なら怖いものなんてない</t>
+          <t xml:space="preserve">なかなかやるじゃない。認めてあげてもいいかな</t>
         </is>
       </c>
     </row>
     <row r="476" ht="40" customHeight="1">
       <c r="A476" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.bold.standard[1]</t>
         </is>
       </c>
       <c r="B476" t="inlineStr" s="2">
@@ -15660,7 +15638,7 @@
       </c>
       <c r="D476" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.bold.standard[1]</t>
+          <t xml:space="preserve">bond_80_up.bold.standard[1]</t>
         </is>
       </c>
       <c r="E476" t="inlineStr" s="2">
@@ -15670,14 +15648,14 @@
       </c>
       <c r="F476" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……もう終わったこと</t>
+          <t xml:space="preserve">最高のコンビね。誰にも負けない</t>
         </is>
       </c>
     </row>
     <row r="477" ht="40" customHeight="1">
       <c r="A477" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.bold.standard[2]</t>
         </is>
       </c>
       <c r="B477" t="inlineStr" s="2">
@@ -15692,7 +15670,7 @@
       </c>
       <c r="D477" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.bold.standard[2]</t>
+          <t xml:space="preserve">bond_80_up.bold.standard[2]</t>
         </is>
       </c>
       <c r="E477" t="inlineStr" s="2">
@@ -15702,14 +15680,14 @@
       </c>
       <c r="F477" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決着はついた。次に進む</t>
+          <t xml:space="preserve">二人なら怖いものなんてない</t>
         </is>
       </c>
     </row>
     <row r="478" ht="40" customHeight="1">
       <c r="A478" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.bold.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.standard[1]</t>
         </is>
       </c>
       <c r="B478" t="inlineStr" s="2">
@@ -15724,7 +15702,7 @@
       </c>
       <c r="D478" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.bold.standard[1]</t>
+          <t xml:space="preserve">rivalry_29_down.bold.standard[1]</t>
         </is>
       </c>
       <c r="E478" t="inlineStr" s="2">
@@ -15734,14 +15712,14 @@
       </c>
       <c r="F478" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">面白いじゃない。超えてみせるわ</t>
+          <t xml:space="preserve">……もう終わったこと</t>
         </is>
       </c>
     </row>
     <row r="479" ht="40" customHeight="1">
       <c r="A479" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.bold.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.bold.standard[2]</t>
         </is>
       </c>
       <c r="B479" t="inlineStr" s="2">
@@ -15756,7 +15734,7 @@
       </c>
       <c r="D479" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.bold.standard[2]</t>
+          <t xml:space="preserve">rivalry_29_down.bold.standard[2]</t>
         </is>
       </c>
       <c r="E479" t="inlineStr" s="2">
@@ -15766,14 +15744,14 @@
       </c>
       <c r="F479" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ようやく面白い相手が出てきた</t>
+          <t xml:space="preserve">決着はついた。次に進む</t>
         </is>
       </c>
     </row>
     <row r="480" ht="40" customHeight="1">
       <c r="A480" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.bold.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.bold.standard[1]</t>
         </is>
       </c>
       <c r="B480" t="inlineStr" s="2">
@@ -15788,7 +15766,7 @@
       </c>
       <c r="D480" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.bold.standard[1]</t>
+          <t xml:space="preserve">rivalry_30_up.bold.standard[1]</t>
         </is>
       </c>
       <c r="E480" t="inlineStr" s="2">
@@ -15798,14 +15776,14 @@
       </c>
       <c r="F480" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力を出せる相手。最高の敵ね</t>
+          <t xml:space="preserve">面白いじゃない。超えてみせるわ</t>
         </is>
       </c>
     </row>
     <row r="481" ht="40" customHeight="1">
       <c r="A481" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.bold.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.bold.standard[2]</t>
         </is>
       </c>
       <c r="B481" t="inlineStr" s="2">
@@ -15820,7 +15798,7 @@
       </c>
       <c r="D481" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.bold.standard[2]</t>
+          <t xml:space="preserve">rivalry_30_up.bold.standard[2]</t>
         </is>
       </c>
       <c r="E481" t="inlineStr" s="2">
@@ -15830,14 +15808,14 @@
       </c>
       <c r="F481" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">超える。それが今の私の全て</t>
+          <t xml:space="preserve">ようやく面白い相手が出てきた</t>
         </is>
       </c>
     </row>
     <row r="482" ht="40" customHeight="1">
       <c r="A482" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.bold.standard[1]</t>
         </is>
       </c>
       <c r="B482" t="inlineStr" s="2">
@@ -15852,7 +15830,7 @@
       </c>
       <c r="D482" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.bold.standard[1]</t>
+          <t xml:space="preserve">rivalry_50_up.bold.standard[1]</t>
         </is>
       </c>
       <c r="E482" t="inlineStr" s="2">
@@ -15862,14 +15840,14 @@
       </c>
       <c r="F482" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この人がいるから強くなれた。感謝してる…でも負けない</t>
+          <t xml:space="preserve">全力を出せる相手。最高の敵ね</t>
         </is>
       </c>
     </row>
     <row r="483" ht="40" customHeight="1">
       <c r="A483" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.bold.standard[2]</t>
         </is>
       </c>
       <c r="B483" t="inlineStr" s="2">
@@ -15884,7 +15862,7 @@
       </c>
       <c r="D483" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.bold.standard[2]</t>
+          <t xml:space="preserve">rivalry_50_up.bold.standard[2]</t>
         </is>
       </c>
       <c r="E483" t="inlineStr" s="2">
@@ -15894,14 +15872,14 @@
       </c>
       <c r="F483" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この戦いは一生続く。望むところよ</t>
+          <t xml:space="preserve">超える。それが今の私の全て</t>
         </is>
       </c>
     </row>
     <row r="484" ht="40" customHeight="1">
       <c r="A484" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.bold.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.standard[1]</t>
         </is>
       </c>
       <c r="B484" t="inlineStr" s="2">
@@ -15916,7 +15894,7 @@
       </c>
       <c r="D484" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.bold.standard[1]</t>
+          <t xml:space="preserve">rivalry_70_up.bold.standard[1]</t>
         </is>
       </c>
       <c r="E484" t="inlineStr" s="2">
@@ -15926,14 +15904,14 @@
       </c>
       <c r="F484" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここが最高の場所。私がもっと強くしてみせる</t>
+          <t xml:space="preserve">この人がいるから強くなれた。感謝してる…でも負けない</t>
         </is>
       </c>
     </row>
     <row r="485" ht="40" customHeight="1">
       <c r="A485" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.bold.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.bold.standard[2]</t>
         </is>
       </c>
       <c r="B485" t="inlineStr" s="2">
@@ -15948,7 +15926,7 @@
       </c>
       <c r="D485" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.bold.standard[2]</t>
+          <t xml:space="preserve">rivalry_70_up.bold.standard[2]</t>
         </is>
       </c>
       <c r="E485" t="inlineStr" s="2">
@@ -15958,14 +15936,14 @@
       </c>
       <c r="F485" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体を背負っていく覚悟はできてるよ</t>
+          <t xml:space="preserve">この戦いは一生続く。望むところよ</t>
         </is>
       </c>
     </row>
     <row r="486" ht="40" customHeight="1">
       <c r="A486" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.bold.standard[1]</t>
         </is>
       </c>
       <c r="B486" t="inlineStr" s="2">
@@ -15980,7 +15958,7 @@
       </c>
       <c r="D486" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.bold.standard[1]</t>
+          <t xml:space="preserve">trust_above_75.bold.standard[1]</t>
         </is>
       </c>
       <c r="E486" t="inlineStr" s="2">
@@ -15990,14 +15968,14 @@
       </c>
       <c r="F486" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふざけないで。私の価値がわからないなら、もう付き合いきれない</t>
+          <t xml:space="preserve">ここが最高の場所。私がもっと強くしてみせる</t>
         </is>
       </c>
     </row>
     <row r="487" ht="40" customHeight="1">
       <c r="A487" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.bold.standard[2]</t>
         </is>
       </c>
       <c r="B487" t="inlineStr" s="2">
@@ -16012,7 +15990,7 @@
       </c>
       <c r="D487" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.bold.standard[2]</t>
+          <t xml:space="preserve">trust_above_75.bold.standard[2]</t>
         </is>
       </c>
       <c r="E487" t="inlineStr" s="2">
@@ -16022,14 +16000,14 @@
       </c>
       <c r="F487" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この扱いは許せない。覚えておいて</t>
+          <t xml:space="preserve">この団体を背負っていく覚悟はできてるよ</t>
         </is>
       </c>
     </row>
     <row r="488" ht="40" customHeight="1">
       <c r="A488" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.bold.standard[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.standard[1]</t>
         </is>
       </c>
       <c r="B488" t="inlineStr" s="2">
@@ -16044,7 +16022,7 @@
       </c>
       <c r="D488" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.bold.standard[1]</t>
+          <t xml:space="preserve">trust_below_20.bold.standard[1]</t>
         </is>
       </c>
       <c r="E488" t="inlineStr" s="2">
@@ -16054,14 +16032,14 @@
       </c>
       <c r="F488" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この扱いは何？ 私の実力、わかってるの</t>
+          <t xml:space="preserve">ふざけないで。私の価値がわからないなら、もう付き合いきれない</t>
         </is>
       </c>
     </row>
     <row r="489" ht="40" customHeight="1">
       <c r="A489" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.bold.standard[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.bold.standard[2]</t>
         </is>
       </c>
       <c r="B489" t="inlineStr" s="2">
@@ -16076,7 +16054,7 @@
       </c>
       <c r="D489" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.bold.standard[2]</t>
+          <t xml:space="preserve">trust_below_20.bold.standard[2]</t>
         </is>
       </c>
       <c r="E489" t="inlineStr" s="2">
@@ -16086,14 +16064,14 @@
       </c>
       <c r="F489" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここにいていいのか…考え直す時期かもしれない</t>
+          <t xml:space="preserve">この扱いは許せない。覚えておいて</t>
         </is>
       </c>
     </row>
     <row r="490" ht="40" customHeight="1">
       <c r="A490" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.standard.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.bold.standard[1]</t>
         </is>
       </c>
       <c r="B490" t="inlineStr" s="2">
@@ -16103,12 +16081,12 @@
       </c>
       <c r="C490" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D490" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.standard.bold[1]</t>
+          <t xml:space="preserve">trust_below_35.bold.standard[1]</t>
         </is>
       </c>
       <c r="E490" t="inlineStr" s="2">
@@ -16118,14 +16096,14 @@
       </c>
       <c r="F490" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けたけど…悔しいけど…いい試合だった</t>
+          <t xml:space="preserve">この扱いは何？ 私の実力、わかってるの</t>
         </is>
       </c>
     </row>
     <row r="491" ht="40" customHeight="1">
       <c r="A491" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.standard.bold[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.bold.standard[2]</t>
         </is>
       </c>
       <c r="B491" t="inlineStr" s="2">
@@ -16135,12 +16113,12 @@
       </c>
       <c r="C491" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D491" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.goodLoss.standard.bold[2]</t>
+          <t xml:space="preserve">trust_below_35.bold.standard[2]</t>
         </is>
       </c>
       <c r="E491" t="inlineStr" s="2">
@@ -16150,14 +16128,14 @@
       </c>
       <c r="F491" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちっ…認めてあげる。今日は向こうが上だった</t>
+          <t xml:space="preserve">ここにいていいのか…考え直す時期かもしれない</t>
         </is>
       </c>
     </row>
     <row r="492" ht="40" customHeight="1">
       <c r="A492" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.standard.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.standard.bold[1]</t>
         </is>
       </c>
       <c r="B492" t="inlineStr" s="2">
@@ -16172,7 +16150,7 @@
       </c>
       <c r="D492" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.standard.bold[1]</t>
+          <t xml:space="preserve">GL-01.goodLoss.standard.bold[1]</t>
         </is>
       </c>
       <c r="E492" t="inlineStr" s="2">
@@ -16182,14 +16160,14 @@
       </c>
       <c r="F492" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これがあたしの実力よ！ 最高の試合で最高の勝利！</t>
+          <t xml:space="preserve">負けたけど…悔しいけど…いい試合だった</t>
         </is>
       </c>
     </row>
     <row r="493" ht="40" customHeight="1">
       <c r="A493" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.standard.bold[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.goodLoss.standard.bold[2]</t>
         </is>
       </c>
       <c r="B493" t="inlineStr" s="2">
@@ -16204,7 +16182,7 @@
       </c>
       <c r="D493" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.greatWin.standard.bold[2]</t>
+          <t xml:space="preserve">GL-01.goodLoss.standard.bold[2]</t>
         </is>
       </c>
       <c r="E493" t="inlineStr" s="2">
@@ -16214,14 +16192,14 @@
       </c>
       <c r="F493" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">見たか！ これがあたしの全力だ！</t>
+          <t xml:space="preserve">ちっ…認めてあげる。今日は向こうが上だった</t>
         </is>
       </c>
     </row>
     <row r="494" ht="40" customHeight="1">
       <c r="A494" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.standard.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.standard.bold[1]</t>
         </is>
       </c>
       <c r="B494" t="inlineStr" s="2">
@@ -16236,7 +16214,7 @@
       </c>
       <c r="D494" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.standard.bold[1]</t>
+          <t xml:space="preserve">GL-01.greatWin.standard.bold[1]</t>
         </is>
       </c>
       <c r="E494" t="inlineStr" s="2">
@@ -16246,14 +16224,14 @@
       </c>
       <c r="F494" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">くそっ…こんなはずじゃない</t>
+          <t xml:space="preserve">これが私の実力よ！ 最高の試合で最高の勝利！</t>
         </is>
       </c>
     </row>
     <row r="495" ht="40" customHeight="1">
       <c r="A495" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.standard.bold[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.greatWin.standard.bold[2]</t>
         </is>
       </c>
       <c r="B495" t="inlineStr" s="2">
@@ -16268,7 +16246,7 @@
       </c>
       <c r="D495" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.loss.standard.bold[2]</t>
+          <t xml:space="preserve">GL-01.greatWin.standard.bold[2]</t>
         </is>
       </c>
       <c r="E495" t="inlineStr" s="2">
@@ -16278,14 +16256,14 @@
       </c>
       <c r="F495" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この借りは必ず返す</t>
+          <t xml:space="preserve">見たでしょ！ これが私の全力よ！</t>
         </is>
       </c>
     </row>
     <row r="496" ht="40" customHeight="1">
       <c r="A496" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.standard.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.standard.bold[1]</t>
         </is>
       </c>
       <c r="B496" t="inlineStr" s="2">
@@ -16300,7 +16278,7 @@
       </c>
       <c r="D496" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.standard.bold[1]</t>
+          <t xml:space="preserve">GL-01.loss.standard.bold[1]</t>
         </is>
       </c>
       <c r="E496" t="inlineStr" s="2">
@@ -16310,14 +16288,14 @@
       </c>
       <c r="F496" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">楽勝！ わたしに勝てるわけないでしょ</t>
+          <t xml:space="preserve">くそっ…こんなはずじゃない</t>
         </is>
       </c>
     </row>
     <row r="497" ht="40" customHeight="1">
       <c r="A497" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.standard.bold[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.loss.standard.bold[2]</t>
         </is>
       </c>
       <c r="B497" t="inlineStr" s="2">
@@ -16332,7 +16310,7 @@
       </c>
       <c r="D497" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-01.win.standard.bold[2]</t>
+          <t xml:space="preserve">GL-01.loss.standard.bold[2]</t>
         </is>
       </c>
       <c r="E497" t="inlineStr" s="2">
@@ -16342,14 +16320,14 @@
       </c>
       <c r="F497" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当たり前よ。この程度で負けるわけないじゃない</t>
+          <t xml:space="preserve">この借りは必ず返す</t>
         </is>
       </c>
     </row>
     <row r="498" ht="40" customHeight="1">
       <c r="A498" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.standard.bold[1]</t>
         </is>
       </c>
       <c r="B498" t="inlineStr" s="2">
@@ -16364,7 +16342,7 @@
       </c>
       <c r="D498" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.standard.bold[1]</t>
+          <t xml:space="preserve">GL-01.win.standard.bold[1]</t>
         </is>
       </c>
       <c r="E498" t="inlineStr" s="2">
@@ -16374,14 +16352,14 @@
       </c>
       <c r="F498" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだまだ！ もっと追い込むよ！</t>
+          <t xml:space="preserve">楽勝！ 私に勝てるわけないでしょ</t>
         </is>
       </c>
     </row>
     <row r="499" ht="40" customHeight="1">
       <c r="A499" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.bold[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-01.win.standard.bold[2]</t>
         </is>
       </c>
       <c r="B499" t="inlineStr" s="2">
@@ -16396,7 +16374,7 @@
       </c>
       <c r="D499" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.standard.bold[2]</t>
+          <t xml:space="preserve">GL-01.win.standard.bold[2]</t>
         </is>
       </c>
       <c r="E499" t="inlineStr" s="2">
@@ -16406,14 +16384,14 @@
       </c>
       <c r="F499" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなもんで満足できるない！ 次！</t>
+          <t xml:space="preserve">当たり前よ。この程度で負けるわけないじゃない</t>
         </is>
       </c>
     </row>
     <row r="500" ht="40" customHeight="1">
       <c r="A500" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.standard.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.bold[1]</t>
         </is>
       </c>
       <c r="B500" t="inlineStr" s="2">
@@ -16428,7 +16406,7 @@
       </c>
       <c r="D500" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.standard.bold[1]</t>
+          <t xml:space="preserve">GL-02.standard.bold[1]</t>
         </is>
       </c>
       <c r="E500" t="inlineStr" s="2">
@@ -16438,14 +16416,14 @@
       </c>
       <c r="F500" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何だよ最近の扱いは。わたしを軽く見てるの？</t>
+          <t xml:space="preserve">まだまだ！ もっと追い込むよ！</t>
         </is>
       </c>
     </row>
     <row r="501" ht="40" customHeight="1">
       <c r="A501" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.standard.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.bold[2]</t>
         </is>
       </c>
       <c r="B501" t="inlineStr" s="2">
@@ -16460,7 +16438,7 @@
       </c>
       <c r="D501" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.standard.bold[1]</t>
+          <t xml:space="preserve">GL-02.standard.bold[2]</t>
         </is>
       </c>
       <c r="E501" t="inlineStr" s="2">
@@ -16470,14 +16448,14 @@
       </c>
       <c r="F501" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体、やっぱり最高！ もっと盛り上げてみせる！</t>
+          <t xml:space="preserve">こんなもんで満足できない！ 次！</t>
         </is>
       </c>
     </row>
     <row r="502" ht="40" customHeight="1">
       <c r="A502" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.standard.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.standard.bold[1]</t>
         </is>
       </c>
       <c r="B502" t="inlineStr" s="2">
@@ -16492,7 +16470,7 @@
       </c>
       <c r="D502" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.standard.bold[1]</t>
+          <t xml:space="preserve">GL-03.down.standard.bold[1]</t>
         </is>
       </c>
       <c r="E502" t="inlineStr" s="2">
@@ -16502,14 +16480,14 @@
       </c>
       <c r="F502" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい仲間だよ。一緒に強くなろう</t>
+          <t xml:space="preserve">何だよ最近の扱いは。私を軽く見てるの？</t>
         </is>
       </c>
     </row>
     <row r="503" ht="40" customHeight="1">
       <c r="A503" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.standard.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.standard.bold[1]</t>
         </is>
       </c>
       <c r="B503" t="inlineStr" s="2">
@@ -16524,7 +16502,7 @@
       </c>
       <c r="D503" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.standard.bold[1]</t>
+          <t xml:space="preserve">GL-03.up.standard.bold[1]</t>
         </is>
       </c>
       <c r="E503" t="inlineStr" s="2">
@@ -16534,14 +16512,14 @@
       </c>
       <c r="F503" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けてたまるか。見てなさいよ！</t>
+          <t xml:space="preserve">この団体、やっぱり最高！ もっと盛り上げてみせる！</t>
         </is>
       </c>
     </row>
     <row r="504" ht="40" customHeight="1">
       <c r="A504" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.standard.bold[1]</t>
         </is>
       </c>
       <c r="B504" t="inlineStr" s="2">
@@ -16556,7 +16534,7 @@
       </c>
       <c r="D504" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.standard.bold[1]</t>
+          <t xml:space="preserve">GL-04.standard.bold[1]</t>
         </is>
       </c>
       <c r="E504" t="inlineStr" s="2">
@@ -16566,14 +16544,14 @@
       </c>
       <c r="F504" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんでわたしを使わないの！ 実力は見せてるでしょ！</t>
+          <t xml:space="preserve">いい仲間だよ。一緒に強くなろう</t>
         </is>
       </c>
     </row>
     <row r="505" ht="40" customHeight="1">
       <c r="A505" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.bold[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.standard.bold[1]</t>
         </is>
       </c>
       <c r="B505" t="inlineStr" s="2">
@@ -16588,7 +16566,7 @@
       </c>
       <c r="D505" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.standard.bold[2]</t>
+          <t xml:space="preserve">GL-05.standard.bold[1]</t>
         </is>
       </c>
       <c r="E505" t="inlineStr" s="2">
@@ -16598,14 +16576,14 @@
       </c>
       <c r="F505" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">リングに上がらせて！ くすぶってる場合じゃないのよ！</t>
+          <t xml:space="preserve">負けてたまるか。見てなさいよ！</t>
         </is>
       </c>
     </row>
     <row r="506" ht="40" customHeight="1">
       <c r="A506" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.standard.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.bold[1]</t>
         </is>
       </c>
       <c r="B506" t="inlineStr" s="2">
@@ -16620,7 +16598,7 @@
       </c>
       <c r="D506" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.standard.bold[1]</t>
+          <t xml:space="preserve">GL-06.standard.bold[1]</t>
         </is>
       </c>
       <c r="E506" t="inlineStr" s="2">
@@ -16630,14 +16608,14 @@
       </c>
       <c r="F506" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちっ、体がなまってる…休んでる場合じゃないのに</t>
+          <t xml:space="preserve">なんで私を使わないの！ 実力は見せてるでしょ！</t>
         </is>
       </c>
     </row>
     <row r="507" ht="40" customHeight="1">
       <c r="A507" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.bold[2]</t>
         </is>
       </c>
       <c r="B507" t="inlineStr" s="2">
@@ -16652,7 +16630,7 @@
       </c>
       <c r="D507" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.standard.bold[1]</t>
+          <t xml:space="preserve">GL-06.standard.bold[2]</t>
         </is>
       </c>
       <c r="E507" t="inlineStr" s="2">
@@ -16662,14 +16640,14 @@
       </c>
       <c r="F507" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…このまま終わるつもりはないから！</t>
+          <t xml:space="preserve">リングに上がらせて！ くすぶってる場合じゃないのよ！</t>
         </is>
       </c>
     </row>
     <row r="508" ht="40" customHeight="1">
       <c r="A508" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.bold[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.standard.bold[1]</t>
         </is>
       </c>
       <c r="B508" t="inlineStr" s="2">
@@ -16684,7 +16662,7 @@
       </c>
       <c r="D508" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.standard.bold[2]</t>
+          <t xml:space="preserve">GL-07.standard.bold[1]</t>
         </is>
       </c>
       <c r="E508" t="inlineStr" s="2">
@@ -16694,14 +16672,14 @@
       </c>
       <c r="F508" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いつまで負け続ける気だ…！ 目を覚ませ、わたし！</t>
+          <t xml:space="preserve">ちっ、体がなまってる…休んでる場合じゃないのに</t>
         </is>
       </c>
     </row>
     <row r="509" ht="40" customHeight="1">
       <c r="A509" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.standard.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.bold[1]</t>
         </is>
       </c>
       <c r="B509" t="inlineStr" s="2">
@@ -16716,7 +16694,7 @@
       </c>
       <c r="D509" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.standard.bold[1]</t>
+          <t xml:space="preserve">GL-08.standard.bold[1]</t>
         </is>
       </c>
       <c r="E509" t="inlineStr" s="2">
@@ -16726,14 +16704,14 @@
       </c>
       <c r="F509" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">絶好調！ この波に乗って一気に行くぞ！</t>
+          <t xml:space="preserve">…このまま終わるつもりはないから！</t>
         </is>
       </c>
     </row>
     <row r="510" ht="40" customHeight="1">
       <c r="A510" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.standard.bold[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.bold[2]</t>
         </is>
       </c>
       <c r="B510" t="inlineStr" s="2">
@@ -16748,7 +16726,7 @@
       </c>
       <c r="D510" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.standard.bold[2]</t>
+          <t xml:space="preserve">GL-08.standard.bold[2]</t>
         </is>
       </c>
       <c r="E510" t="inlineStr" s="2">
@@ -16758,14 +16736,14 @@
       </c>
       <c r="F510" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今のわたしを止められるやつはいない！</t>
+          <t xml:space="preserve">いつまで負け続ける気だ…！ 目を覚ませ、私！</t>
         </is>
       </c>
     </row>
     <row r="511" ht="40" customHeight="1">
       <c r="A511" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.standard.bold[1]</t>
         </is>
       </c>
       <c r="B511" t="inlineStr" s="2">
@@ -16780,7 +16758,7 @@
       </c>
       <c r="D511" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.standard.bold[1]</t>
+          <t xml:space="preserve">GL-09.standard.bold[1]</t>
         </is>
       </c>
       <c r="E511" t="inlineStr" s="2">
@@ -16790,14 +16768,14 @@
       </c>
       <c r="F511" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなとこで寝てる場合じゃない…！</t>
+          <t xml:space="preserve">絶好調！ この波に乗って一気に行くぞ！</t>
         </is>
       </c>
     </row>
     <row r="512" ht="40" customHeight="1">
       <c r="A512" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.bold[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.standard.bold[2]</t>
         </is>
       </c>
       <c r="B512" t="inlineStr" s="2">
@@ -16812,7 +16790,7 @@
       </c>
       <c r="D512" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.standard.bold[2]</t>
+          <t xml:space="preserve">GL-09.standard.bold[2]</t>
         </is>
       </c>
       <c r="E512" t="inlineStr" s="2">
@@ -16822,14 +16800,14 @@
       </c>
       <c r="F512" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わたしがいない間に追い抜かれるのは耐えられない！</t>
+          <t xml:space="preserve">今の私を止められるやつはいない！</t>
         </is>
       </c>
     </row>
     <row r="513" ht="40" customHeight="1">
       <c r="A513" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.bold[1]</t>
         </is>
       </c>
       <c r="B513" t="inlineStr" s="2">
@@ -16839,12 +16817,12 @@
       </c>
       <c r="C513" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D513" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.bold[1]</t>
+          <t xml:space="preserve">GL-10.standard.bold[1]</t>
         </is>
       </c>
       <c r="E513" t="inlineStr" s="2">
@@ -16854,14 +16832,14 @@
       </c>
       <c r="F513" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……身体のキレも普通に戻ってきちゃったかな。でも、いい感覚は体が覚えてるよ！</t>
+          <t xml:space="preserve">こんなとこで寝てる場合じゃない…！</t>
         </is>
       </c>
     </row>
     <row r="514" ht="40" customHeight="1">
       <c r="A514" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.bold[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.bold[2]</t>
         </is>
       </c>
       <c r="B514" t="inlineStr" s="2">
@@ -16871,12 +16849,12 @@
       </c>
       <c r="C514" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D514" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.bold[2]</t>
+          <t xml:space="preserve">GL-10.standard.bold[2]</t>
         </is>
       </c>
       <c r="E514" t="inlineStr" s="2">
@@ -16886,14 +16864,14 @@
       </c>
       <c r="F514" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの好調で掴んだ感覚は忘れない。次に繋げてみせる</t>
+          <t xml:space="preserve">私がいない間に追い抜かれるのは耐えられない！</t>
         </is>
       </c>
     </row>
     <row r="515" ht="40" customHeight="1">
       <c r="A515" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.bold[1]</t>
         </is>
       </c>
       <c r="B515" t="inlineStr" s="2">
@@ -16903,29 +16881,29 @@
       </c>
       <c r="C515" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D515" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.bold[1]</t>
+          <t xml:space="preserve">standard.bold[1]</t>
         </is>
       </c>
       <c r="E515" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F515" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">傷だらけで結構。最後まで残ったのはこっちだ。全部持っていく</t>
+          <t xml:space="preserve">……身体のキレも普通に戻ってきちゃったかな。でも、いい感覚は体が覚えてるよ！</t>
         </is>
       </c>
     </row>
     <row r="516" ht="40" customHeight="1">
       <c r="A516" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.bold[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.bold[2]</t>
         </is>
       </c>
       <c r="B516" t="inlineStr" s="2">
@@ -16935,29 +16913,29 @@
       </c>
       <c r="C516" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D516" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.bold[2]</t>
+          <t xml:space="preserve">standard.bold[2]</t>
         </is>
       </c>
       <c r="E516" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F516" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで抜いてきて、最後で退くわけないでしょ。獲りにいく</t>
+          <t xml:space="preserve">あの好調で掴んだ感覚は忘れない。次に繋げてみせる</t>
         </is>
       </c>
     </row>
     <row r="517" ht="40" customHeight="1">
       <c r="A517" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.bold[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.bold[1]</t>
         </is>
       </c>
       <c r="B517" t="inlineStr" s="2">
@@ -16972,7 +16950,7 @@
       </c>
       <c r="D517" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.bold[3]</t>
+          <t xml:space="preserve">preFinal.standard.bold[1]</t>
         </is>
       </c>
       <c r="E517" t="inlineStr" s="2">
@@ -16982,14 +16960,14 @@
       </c>
       <c r="F517" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体は重いけど、心は決まってる。この一戦、全部あたしがもらう</t>
+          <t xml:space="preserve">傷だらけで結構。最後まで残ったのはこっちだ。全部持っていく</t>
         </is>
       </c>
     </row>
     <row r="518" ht="40" customHeight="1">
       <c r="A518" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.bold[2]</t>
         </is>
       </c>
       <c r="B518" t="inlineStr" s="2">
@@ -17004,7 +16982,7 @@
       </c>
       <c r="D518" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.bold[1]</t>
+          <t xml:space="preserve">preFinal.standard.bold[2]</t>
         </is>
       </c>
       <c r="E518" t="inlineStr" s="2">
@@ -17014,14 +16992,14 @@
       </c>
       <c r="F518" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人並んでようが関係ない。真っ向から薙ぎ倒して、次に繋ぐ</t>
+          <t xml:space="preserve">ここまで抜いてきて、最後で退くわけないでしょ。獲りにいく</t>
         </is>
       </c>
     </row>
     <row r="519" ht="40" customHeight="1">
       <c r="A519" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.bold[3]</t>
         </is>
       </c>
       <c r="B519" t="inlineStr" s="2">
@@ -17036,7 +17014,7 @@
       </c>
       <c r="D519" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.bold[2]</t>
+          <t xml:space="preserve">preFinal.standard.bold[3]</t>
         </is>
       </c>
       <c r="E519" t="inlineStr" s="2">
@@ -17046,14 +17024,14 @@
       </c>
       <c r="F519" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">来るなら来い。このリングを抜けさせると思ってんのか</t>
+          <t xml:space="preserve">身体は重いけど、心は決まってる。この一戦、全部私がもらう</t>
         </is>
       </c>
     </row>
     <row r="520" ht="40" customHeight="1">
       <c r="A520" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.bold[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.bold[1]</t>
         </is>
       </c>
       <c r="B520" t="inlineStr" s="2">
@@ -17068,7 +17046,7 @@
       </c>
       <c r="D520" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.bold[3]</t>
+          <t xml:space="preserve">preMatch.standard.bold[1]</t>
         </is>
       </c>
       <c r="E520" t="inlineStr" s="2">
@@ -17078,14 +17056,14 @@
       </c>
       <c r="F520" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手が誰だろうと、結果は変わらない。最後に立ってるのはあたしだ</t>
+          <t xml:space="preserve">何人並んでようが関係ない。真っ向から薙ぎ倒して、次に繋ぐ</t>
         </is>
       </c>
     </row>
     <row r="521" ht="40" customHeight="1">
       <c r="A521" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.bold[2]</t>
         </is>
       </c>
       <c r="B521" t="inlineStr" s="2">
@@ -17100,7 +17078,7 @@
       </c>
       <c r="D521" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.standard.bold[1]</t>
+          <t xml:space="preserve">preMatch.standard.bold[2]</t>
         </is>
       </c>
       <c r="E521" t="inlineStr" s="2">
@@ -17110,14 +17088,14 @@
       </c>
       <c r="F521" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人落とした。…息は上がってる。だから何だ? 次、まとめて来い</t>
+          <t xml:space="preserve">来るなら来い。このリングを抜けさせると思ってんのか</t>
         </is>
       </c>
     </row>
     <row r="522" ht="40" customHeight="1">
       <c r="A522" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.bold[3]</t>
         </is>
       </c>
       <c r="B522" t="inlineStr" s="2">
@@ -17132,7 +17110,7 @@
       </c>
       <c r="D522" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.standard.bold[2]</t>
+          <t xml:space="preserve">preMatch.standard.bold[3]</t>
         </is>
       </c>
       <c r="E522" t="inlineStr" s="2">
@@ -17142,14 +17120,14 @@
       </c>
       <c r="F522" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ立ってる。このリングを抜けたきゃ、あたしを倒してからにしな。次だ</t>
+          <t xml:space="preserve">相手が誰だろうと、結果は変わらない。最後に立ってるのは私よ</t>
         </is>
       </c>
     </row>
     <row r="523" ht="40" customHeight="1">
       <c r="A523" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.bold[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.bold[1]</t>
         </is>
       </c>
       <c r="B523" t="inlineStr" s="2">
@@ -17164,7 +17142,7 @@
       </c>
       <c r="D523" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.standard.bold[3]</t>
+          <t xml:space="preserve">survivor.standard.bold[1]</t>
         </is>
       </c>
       <c r="E523" t="inlineStr" s="2">
@@ -17174,14 +17152,14 @@
       </c>
       <c r="F523" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一丁上がり。…息は切れてるけど、拳はまだ握れる。次、出てきな</t>
+          <t xml:space="preserve">一人落とした。…息は上がってる。だから何だ? 次、まとめて来い</t>
         </is>
       </c>
     </row>
     <row r="524" ht="40" customHeight="1">
       <c r="A524" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.bold[2]</t>
         </is>
       </c>
       <c r="B524" t="inlineStr" s="2">
@@ -17191,12 +17169,12 @@
       </c>
       <c r="C524" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D524" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.bold[1]</t>
+          <t xml:space="preserve">survivor.standard.bold[2]</t>
         </is>
       </c>
       <c r="E524" t="inlineStr" s="2">
@@ -17206,14 +17184,14 @@
       </c>
       <c r="F524" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体の三人が、一番強かった。今日の答えは、それで十分でしょ</t>
+          <t xml:space="preserve">まだ立ってる。このリングを抜けたいなら、私を倒してからにしなさい。次</t>
         </is>
       </c>
     </row>
     <row r="525" ht="40" customHeight="1">
       <c r="A525" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.bold[3]</t>
         </is>
       </c>
       <c r="B525" t="inlineStr" s="2">
@@ -17223,12 +17201,12 @@
       </c>
       <c r="C525" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D525" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.bold[2]</t>
+          <t xml:space="preserve">survivor.standard.bold[3]</t>
         </is>
       </c>
       <c r="E525" t="inlineStr" s="2">
@@ -17238,14 +17216,14 @@
       </c>
       <c r="F525" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人で最強を証明した。これ以上の答えがあるなら聞いてみたいね</t>
+          <t xml:space="preserve">一丁上がり。…息は切れてるけど、拳はまだ握れる。次、出てきな</t>
         </is>
       </c>
     </row>
     <row r="526" ht="40" customHeight="1">
       <c r="A526" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.bold[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.bold[1]</t>
         </is>
       </c>
       <c r="B526" t="inlineStr" s="2">
@@ -17260,7 +17238,7 @@
       </c>
       <c r="D526" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.bold[3]</t>
+          <t xml:space="preserve">champion.standard.bold[1]</t>
         </is>
       </c>
       <c r="E526" t="inlineStr" s="2">
@@ -17270,14 +17248,14 @@
       </c>
       <c r="F526" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間が信じてくれたから、最後まで攻められた。この三人に勝てる奴はいない</t>
+          <t xml:space="preserve">この団体の三人が、一番強かった。今日の答えは、それで十分でしょ</t>
         </is>
       </c>
     </row>
     <row r="527" ht="40" customHeight="1">
       <c r="A527" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.bold[2]</t>
         </is>
       </c>
       <c r="B527" t="inlineStr" s="2">
@@ -17292,7 +17270,7 @@
       </c>
       <c r="D527" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.standard.bold[1]</t>
+          <t xml:space="preserve">champion.standard.bold[2]</t>
         </is>
       </c>
       <c r="E527" t="inlineStr" s="2">
@@ -17302,14 +17280,14 @@
       </c>
       <c r="F527" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">賞はもらう。でも優勝旗は向こうだ。次は、あれごと奪う</t>
+          <t xml:space="preserve">三人で最強を証明した。これ以上の答えがあるなら聞いてみたいね</t>
         </is>
       </c>
     </row>
     <row r="528" ht="40" customHeight="1">
       <c r="A528" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.bold[3]</t>
         </is>
       </c>
       <c r="B528" t="inlineStr" s="2">
@@ -17324,7 +17302,7 @@
       </c>
       <c r="D528" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.standard.bold[2]</t>
+          <t xml:space="preserve">champion.standard.bold[3]</t>
         </is>
       </c>
       <c r="E528" t="inlineStr" s="2">
@@ -17334,14 +17312,14 @@
       </c>
       <c r="F528" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVP？ そんなもんで満足できるかよ。次は団体ごと叩き潰す</t>
+          <t xml:space="preserve">仲間が信じてくれたから、最後まで攻められた。この三人に勝てる奴はいない</t>
         </is>
       </c>
     </row>
     <row r="529" ht="40" customHeight="1">
       <c r="A529" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.bold[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.bold[1]</t>
         </is>
       </c>
       <c r="B529" t="inlineStr" s="2">
@@ -17356,7 +17334,7 @@
       </c>
       <c r="D529" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.standard.bold[3]</t>
+          <t xml:space="preserve">defiant.standard.bold[1]</t>
         </is>
       </c>
       <c r="E529" t="inlineStr" s="2">
@@ -17366,14 +17344,14 @@
       </c>
       <c r="F529" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">個人で勝っても、チームが負けたら意味がない。次は絶対に獲る</t>
+          <t xml:space="preserve">賞はもらう。でも優勝旗は向こうだ。次は、あれごと奪う</t>
         </is>
       </c>
     </row>
     <row r="530" ht="40" customHeight="1">
       <c r="A530" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.bold[2]</t>
         </is>
       </c>
       <c r="B530" t="inlineStr" s="2">
@@ -17388,7 +17366,7 @@
       </c>
       <c r="D530" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.standard.bold[1]</t>
+          <t xml:space="preserve">defiant.standard.bold[2]</t>
         </is>
       </c>
       <c r="E530" t="inlineStr" s="2">
@@ -17398,14 +17376,14 @@
       </c>
       <c r="F530" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人だろうが四人だろうが、立って来るなら倒す。今日はそれを証明しただけ</t>
+          <t xml:space="preserve">MVP？ そんなもんで満足できるわけないでしょ。次は団体ごと叩き潰す</t>
         </is>
       </c>
     </row>
     <row r="531" ht="40" customHeight="1">
       <c r="A531" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.bold[3]</t>
         </is>
       </c>
       <c r="B531" t="inlineStr" s="2">
@@ -17420,7 +17398,7 @@
       </c>
       <c r="D531" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.standard.bold[2]</t>
+          <t xml:space="preserve">defiant.standard.bold[3]</t>
         </is>
       </c>
       <c r="E531" t="inlineStr" s="2">
@@ -17430,14 +17408,14 @@
       </c>
       <c r="F531" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次が来るなら、何人でもいい。あたしの拳はまだ握れてる</t>
+          <t xml:space="preserve">個人で勝っても、チームが負けたら意味がない。次は絶対に獲る</t>
         </is>
       </c>
     </row>
     <row r="532" ht="40" customHeight="1">
       <c r="A532" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.bold[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.bold[1]</t>
         </is>
       </c>
       <c r="B532" t="inlineStr" s="2">
@@ -17452,7 +17430,7 @@
       </c>
       <c r="D532" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.standard.bold[3]</t>
+          <t xml:space="preserve">gauntlet.standard.bold[1]</t>
         </is>
       </c>
       <c r="E532" t="inlineStr" s="2">
@@ -17462,14 +17440,14 @@
       </c>
       <c r="F532" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全員まとめて相手にしてやった。文句あるなら、もう一回並べ</t>
+          <t xml:space="preserve">三人だろうが四人だろうが、立って来るなら倒す。今日はそれを証明しただけ</t>
         </is>
       </c>
     </row>
     <row r="533" ht="40" customHeight="1">
       <c r="A533" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.bold[2]</t>
         </is>
       </c>
       <c r="B533" t="inlineStr" s="2">
@@ -17479,12 +17457,12 @@
       </c>
       <c r="C533" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D533" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.bold[1]</t>
+          <t xml:space="preserve">gauntlet.standard.bold[2]</t>
         </is>
       </c>
       <c r="E533" t="inlineStr" s="2">
@@ -17494,14 +17472,14 @@
       </c>
       <c r="F533" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">言ったでしょ？ 私が最強だって</t>
+          <t xml:space="preserve">次が来るなら、何人でもいい。この拳はまだ握れてる</t>
         </is>
       </c>
     </row>
     <row r="534" ht="40" customHeight="1">
       <c r="A534" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.bold[3]</t>
         </is>
       </c>
       <c r="B534" t="inlineStr" s="2">
@@ -17511,12 +17489,12 @@
       </c>
       <c r="C534" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D534" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.bold[2]</t>
+          <t xml:space="preserve">gauntlet.standard.bold[3]</t>
         </is>
       </c>
       <c r="E534" t="inlineStr" s="2">
@@ -17526,14 +17504,14 @@
       </c>
       <c r="F534" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">はい優勝。当然の結果ね</t>
+          <t xml:space="preserve">全員まとめて相手にしてやった。文句あるなら、もう一回並べ</t>
         </is>
       </c>
     </row>
     <row r="535" ht="40" customHeight="1">
       <c r="A535" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.bold[1]</t>
         </is>
       </c>
       <c r="B535" t="inlineStr" s="2">
@@ -17548,7 +17526,7 @@
       </c>
       <c r="D535" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.standard.bold[1]</t>
+          <t xml:space="preserve">champion.standard.bold[1]</t>
         </is>
       </c>
       <c r="E535" t="inlineStr" s="2">
@@ -17558,14 +17536,14 @@
       </c>
       <c r="F535" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなはずじゃ…！ 次は絶対に見返す！</t>
+          <t xml:space="preserve">言ったでしょ？ 私が最強だって</t>
         </is>
       </c>
     </row>
     <row r="536" ht="40" customHeight="1">
       <c r="A536" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.bold[2]</t>
         </is>
       </c>
       <c r="B536" t="inlineStr" s="2">
@@ -17580,7 +17558,7 @@
       </c>
       <c r="D536" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.standard.bold[2]</t>
+          <t xml:space="preserve">champion.standard.bold[2]</t>
         </is>
       </c>
       <c r="E536" t="inlineStr" s="2">
@@ -17590,14 +17568,14 @@
       </c>
       <c r="F536" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">認めない。次は絶対に勝つ</t>
+          <t xml:space="preserve">はい優勝。当然の結果ね</t>
         </is>
       </c>
     </row>
     <row r="537" ht="40" customHeight="1">
       <c r="A537" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.bold[1]</t>
         </is>
       </c>
       <c r="B537" t="inlineStr" s="2">
@@ -17612,7 +17590,7 @@
       </c>
       <c r="D537" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.standard.bold[1]</t>
+          <t xml:space="preserve">postLose.standard.bold[1]</t>
         </is>
       </c>
       <c r="E537" t="inlineStr" s="2">
@@ -17622,14 +17600,14 @@
       </c>
       <c r="F537" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然の結果よ。次も同じ</t>
+          <t xml:space="preserve">こんなはずじゃ…！ 次は絶対に見返す！</t>
         </is>
       </c>
     </row>
     <row r="538" ht="40" customHeight="1">
       <c r="A538" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.bold[2]</t>
         </is>
       </c>
       <c r="B538" t="inlineStr" s="2">
@@ -17644,7 +17622,7 @@
       </c>
       <c r="D538" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.standard.bold[2]</t>
+          <t xml:space="preserve">postLose.standard.bold[2]</t>
         </is>
       </c>
       <c r="E538" t="inlineStr" s="2">
@@ -17654,14 +17632,14 @@
       </c>
       <c r="F538" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふん。この程度じゃ止まらないわよ</t>
+          <t xml:space="preserve">認めない。次は絶対に勝つ</t>
         </is>
       </c>
     </row>
     <row r="539" ht="40" customHeight="1">
       <c r="A539" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.bold[1]</t>
         </is>
       </c>
       <c r="B539" t="inlineStr" s="2">
@@ -17676,7 +17654,7 @@
       </c>
       <c r="D539" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.standard.bold[1]</t>
+          <t xml:space="preserve">postMatchWin.standard.bold[1]</t>
         </is>
       </c>
       <c r="E539" t="inlineStr" s="2">
@@ -17686,14 +17664,14 @@
       </c>
       <c r="F539" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然の結果ね。次は優勝よ</t>
+          <t xml:space="preserve">当然の結果よ。次も同じ</t>
         </is>
       </c>
     </row>
     <row r="540" ht="40" customHeight="1">
       <c r="A540" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.bold[2]</t>
         </is>
       </c>
       <c r="B540" t="inlineStr" s="2">
@@ -17708,7 +17686,7 @@
       </c>
       <c r="D540" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.standard.bold[2]</t>
+          <t xml:space="preserve">postMatchWin.standard.bold[2]</t>
         </is>
       </c>
       <c r="E540" t="inlineStr" s="2">
@@ -17718,14 +17696,14 @@
       </c>
       <c r="F540" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この程度で満足するわけないでしょ</t>
+          <t xml:space="preserve">ふん。この程度じゃ止まらないわよ</t>
         </is>
       </c>
     </row>
     <row r="541" ht="40" customHeight="1">
       <c r="A541" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.bold[1]</t>
         </is>
       </c>
       <c r="B541" t="inlineStr" s="2">
@@ -17740,7 +17718,7 @@
       </c>
       <c r="D541" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.bold[1]</t>
+          <t xml:space="preserve">postWin.standard.bold[1]</t>
         </is>
       </c>
       <c r="E541" t="inlineStr" s="2">
@@ -17750,14 +17728,14 @@
       </c>
       <c r="F541" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来て負けるわけないでしょ。最後も私が獲る</t>
+          <t xml:space="preserve">当然の結果ね。次は優勝よ</t>
         </is>
       </c>
     </row>
     <row r="542" ht="40" customHeight="1">
       <c r="A542" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.bold[2]</t>
         </is>
       </c>
       <c r="B542" t="inlineStr" s="2">
@@ -17772,7 +17750,7 @@
       </c>
       <c r="D542" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.bold[2]</t>
+          <t xml:space="preserve">postWin.standard.bold[2]</t>
         </is>
       </c>
       <c r="E542" t="inlineStr" s="2">
@@ -17782,14 +17760,14 @@
       </c>
       <c r="F542" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">さあ、最後の獲物ね。楽しませてもらうわ</t>
+          <t xml:space="preserve">この程度で満足するわけないでしょ</t>
         </is>
       </c>
     </row>
     <row r="543" ht="40" customHeight="1">
       <c r="A543" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.bold[1]</t>
         </is>
       </c>
       <c r="B543" t="inlineStr" s="2">
@@ -17804,7 +17782,7 @@
       </c>
       <c r="D543" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.bold[1]</t>
+          <t xml:space="preserve">preFinal.standard.bold[1]</t>
         </is>
       </c>
       <c r="E543" t="inlineStr" s="2">
@@ -17814,14 +17792,14 @@
       </c>
       <c r="F543" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">目の前の相手を叩き潰す。それだけよ</t>
+          <t xml:space="preserve">ここまで来て負けるわけないでしょ。最後も私が獲る</t>
         </is>
       </c>
     </row>
     <row r="544" ht="40" customHeight="1">
       <c r="A544" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.bold[2]</t>
         </is>
       </c>
       <c r="B544" t="inlineStr" s="2">
@@ -17836,7 +17814,7 @@
       </c>
       <c r="D544" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.bold[2]</t>
+          <t xml:space="preserve">preFinal.standard.bold[2]</t>
         </is>
       </c>
       <c r="E544" t="inlineStr" s="2">
@@ -17846,14 +17824,14 @@
       </c>
       <c r="F544" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝つのは私。最初から決まってることよ</t>
+          <t xml:space="preserve">さあ、最後の獲物ね。楽しませてもらうわ</t>
         </is>
       </c>
     </row>
     <row r="545" ht="40" customHeight="1">
       <c r="A545" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.bold[1]</t>
         </is>
       </c>
       <c r="B545" t="inlineStr" s="2">
@@ -17868,7 +17846,7 @@
       </c>
       <c r="D545" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.standard.bold[1]</t>
+          <t xml:space="preserve">preMatch.standard.bold[1]</t>
         </is>
       </c>
       <c r="E545" t="inlineStr" s="2">
@@ -17878,14 +17856,14 @@
       </c>
       <c r="F545" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然。呼ばれなかったら怒ってたわ</t>
+          <t xml:space="preserve">目の前の相手を叩き潰す。それだけよ</t>
         </is>
       </c>
     </row>
     <row r="546" ht="40" customHeight="1">
       <c r="A546" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.bold[2]</t>
         </is>
       </c>
       <c r="B546" t="inlineStr" s="2">
@@ -17900,7 +17878,7 @@
       </c>
       <c r="D546" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.standard.bold[2]</t>
+          <t xml:space="preserve">preMatch.standard.bold[2]</t>
         </is>
       </c>
       <c r="E546" t="inlineStr" s="2">
@@ -17910,14 +17888,14 @@
       </c>
       <c r="F546" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふん、やっと正当な評価をしてくれたわけね</t>
+          <t xml:space="preserve">勝つのは私。最初から決まってることよ</t>
         </is>
       </c>
     </row>
     <row r="547" ht="40" customHeight="1">
       <c r="A547" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.bold[1]</t>
         </is>
       </c>
       <c r="B547" t="inlineStr" s="2">
@@ -17927,12 +17905,12 @@
       </c>
       <c r="C547" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D547" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.bold[1]</t>
+          <t xml:space="preserve">summon.standard.bold[1]</t>
         </is>
       </c>
       <c r="E547" t="inlineStr" s="2">
@@ -17942,14 +17920,14 @@
       </c>
       <c r="F547" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ぶっ飛ばしてやる！</t>
+          <t xml:space="preserve">当然。呼ばれなかったら怒ってたわ</t>
         </is>
       </c>
     </row>
     <row r="548" ht="40" customHeight="1">
       <c r="A548" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.bold[2]</t>
         </is>
       </c>
       <c r="B548" t="inlineStr" s="2">
@@ -17959,12 +17937,12 @@
       </c>
       <c r="C548" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D548" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.bold[2]</t>
+          <t xml:space="preserve">summon.standard.bold[2]</t>
         </is>
       </c>
       <c r="E548" t="inlineStr" s="2">
@@ -17974,14 +17952,14 @@
       </c>
       <c r="F548" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私の実力、思い知らせてあげる</t>
+          <t xml:space="preserve">ふん、やっと正当な評価をしてくれたわけね</t>
         </is>
       </c>
     </row>
     <row r="549" ht="40" customHeight="1">
       <c r="A549" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.bold[3]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.bold[1]</t>
         </is>
       </c>
       <c r="B549" t="inlineStr" s="2">
@@ -17996,7 +17974,7 @@
       </c>
       <c r="D549" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.bold[3]</t>
+          <t xml:space="preserve">standard.bold[1]</t>
         </is>
       </c>
       <c r="E549" t="inlineStr" s="2">
@@ -18006,14 +17984,14 @@
       </c>
       <c r="F549" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">容赦しないわ。覚悟しなさい！</t>
+          <t xml:space="preserve">ぶっ飛ばしてやる！</t>
         </is>
       </c>
     </row>
     <row r="550" ht="40" customHeight="1">
       <c r="A550" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.bold[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.bold[2]</t>
         </is>
       </c>
       <c r="B550" t="inlineStr" s="2">
@@ -18023,12 +18001,12 @@
       </c>
       <c r="C550" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D550" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.bold[1]</t>
+          <t xml:space="preserve">standard.bold[2]</t>
         </is>
       </c>
       <c r="E550" t="inlineStr" s="2">
@@ -18038,14 +18016,14 @@
       </c>
       <c r="F550" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この瞬間をずっと待ってた……！ いい気分！</t>
+          <t xml:space="preserve">私の実力、思い知らせてあげる</t>
         </is>
       </c>
     </row>
     <row r="551" ht="40" customHeight="1">
       <c r="A551" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.bold[2]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.bold[3]</t>
         </is>
       </c>
       <c r="B551" t="inlineStr" s="2">
@@ -18055,12 +18033,12 @@
       </c>
       <c r="C551" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D551" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.bold[2]</t>
+          <t xml:space="preserve">standard.bold[3]</t>
         </is>
       </c>
       <c r="E551" t="inlineStr" s="2">
@@ -18070,14 +18048,14 @@
       </c>
       <c r="F551" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これが一番の景色か……！ 私のものね……！</t>
+          <t xml:space="preserve">容赦しないわ。覚悟しなさい！</t>
         </is>
       </c>
     </row>
     <row r="552" ht="40" customHeight="1">
       <c r="A552" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.bold[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.bold[1]</t>
         </is>
       </c>
       <c r="B552" t="inlineStr" s="2">
@@ -18087,7 +18065,7 @@
       </c>
       <c r="C552" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D552" t="inlineStr" s="12">
@@ -18102,14 +18080,14 @@
       </c>
       <c r="F552" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">聞いてあきれる。そんな団体に負けるわけないでしょ</t>
+          <t xml:space="preserve">この瞬間をずっと待ってた……！ いい気分！</t>
         </is>
       </c>
     </row>
     <row r="553" ht="40" customHeight="1">
       <c r="A553" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.bold[2]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.bold[2]</t>
         </is>
       </c>
       <c r="B553" t="inlineStr" s="2">
@@ -18119,7 +18097,7 @@
       </c>
       <c r="C553" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D553" t="inlineStr" s="12">
@@ -18134,14 +18112,14 @@
       </c>
       <c r="F553" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あんたたちの看板選手？ 笑わせないで</t>
+          <t xml:space="preserve">これが一番の景色か……！ 私のものね……！</t>
         </is>
       </c>
     </row>
     <row r="554" ht="40" customHeight="1">
       <c r="A554" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.bold[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.bold[1]</t>
         </is>
       </c>
       <c r="B554" t="inlineStr" s="2">
@@ -18151,7 +18129,7 @@
       </c>
       <c r="C554" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D554" t="inlineStr" s="12">
@@ -18166,14 +18144,14 @@
       </c>
       <c r="F554" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">はっ、やっぱりね。戦う前から結果は見えてたわ</t>
+          <t xml:space="preserve">聞いてあきれる。そんな団体に負けるわけないでしょ</t>
         </is>
       </c>
     </row>
     <row r="555" ht="40" customHeight="1">
       <c r="A555" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.bold[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.bold[2]</t>
         </is>
       </c>
       <c r="B555" t="inlineStr" s="2">
@@ -18183,7 +18161,7 @@
       </c>
       <c r="C555" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D555" t="inlineStr" s="12">
@@ -18198,14 +18176,14 @@
       </c>
       <c r="F555" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">逃げるの？ まあ、賢い判断よね</t>
+          <t xml:space="preserve">あんたたちの看板選手？ 笑わせないで</t>
         </is>
       </c>
     </row>
     <row r="556" ht="40" customHeight="1">
       <c r="A556" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.bold[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.bold[1]</t>
         </is>
       </c>
       <c r="B556" t="inlineStr" s="2">
@@ -18215,12 +18193,12 @@
       </c>
       <c r="C556" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D556" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.standard.bold[1]</t>
+          <t xml:space="preserve">standard.bold[1]</t>
         </is>
       </c>
       <c r="E556" t="inlineStr" s="2">
@@ -18230,14 +18208,14 @@
       </c>
       <c r="F556" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなの認めない…！ 絶対にリベンジしてやる</t>
+          <t xml:space="preserve">はっ、やっぱりね。戦う前から結果は見えてたわ</t>
         </is>
       </c>
     </row>
     <row r="557" ht="40" customHeight="1">
       <c r="A557" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.bold[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.bold[2]</t>
         </is>
       </c>
       <c r="B557" t="inlineStr" s="2">
@@ -18247,12 +18225,12 @@
       </c>
       <c r="C557" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D557" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.standard.bold[2]</t>
+          <t xml:space="preserve">standard.bold[2]</t>
         </is>
       </c>
       <c r="E557" t="inlineStr" s="2">
@@ -18262,14 +18240,14 @@
       </c>
       <c r="F557" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">たまたまよ、たまたま。次は潰す</t>
+          <t xml:space="preserve">逃げるの？ まあ、賢い判断よね</t>
         </is>
       </c>
     </row>
     <row r="558" ht="40" customHeight="1">
       <c r="A558" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.bold[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.bold[1]</t>
         </is>
       </c>
       <c r="B558" t="inlineStr" s="2">
@@ -18284,7 +18262,7 @@
       </c>
       <c r="D558" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.standard.bold[1]</t>
+          <t xml:space="preserve">result_lose.standard.bold[1]</t>
         </is>
       </c>
       <c r="E558" t="inlineStr" s="2">
@@ -18294,14 +18272,14 @@
       </c>
       <c r="F558" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然の結果でしょ。格が違うのよ</t>
+          <t xml:space="preserve">こんなの認めない…！ 絶対にリベンジしてやる</t>
         </is>
       </c>
     </row>
     <row r="559" ht="40" customHeight="1">
       <c r="A559" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.bold[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.bold[2]</t>
         </is>
       </c>
       <c r="B559" t="inlineStr" s="2">
@@ -18316,7 +18294,7 @@
       </c>
       <c r="D559" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.standard.bold[2]</t>
+          <t xml:space="preserve">result_lose.standard.bold[2]</t>
         </is>
       </c>
       <c r="E559" t="inlineStr" s="2">
@@ -18326,14 +18304,14 @@
       </c>
       <c r="F559" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう二度と歯向かわないことね</t>
+          <t xml:space="preserve">たまたまよ、たまたま。次は潰す</t>
         </is>
       </c>
     </row>
     <row r="560" ht="40" customHeight="1">
       <c r="A560" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.standard.bold[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.bold[1]</t>
         </is>
       </c>
       <c r="B560" t="inlineStr" s="2">
@@ -18343,12 +18321,12 @@
       </c>
       <c r="C560" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D560" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.bold[1]</t>
+          <t xml:space="preserve">result_win.standard.bold[1]</t>
         </is>
       </c>
       <c r="E560" t="inlineStr" s="2">
@@ -18358,14 +18336,14 @@
       </c>
       <c r="F560" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然でしょ！ うちの団体を甘く見ないでよね！</t>
+          <t xml:space="preserve">当然の結果でしょ。格が違うのよ</t>
         </is>
       </c>
     </row>
     <row r="561" ht="40" customHeight="1">
       <c r="A561" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.standard.bold[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.bold[2]</t>
         </is>
       </c>
       <c r="B561" t="inlineStr" s="2">
@@ -18375,12 +18353,12 @@
       </c>
       <c r="C561" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D561" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.bold[2]</t>
+          <t xml:space="preserve">result_win.standard.bold[2]</t>
         </is>
       </c>
       <c r="E561" t="inlineStr" s="2">
@@ -18390,14 +18368,14 @@
       </c>
       <c r="F561" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この勝利は団体のみんなの勝利よ！</t>
+          <t xml:space="preserve">もう二度と歯向かわないことね</t>
         </is>
       </c>
     </row>
     <row r="562" ht="40" customHeight="1">
       <c r="A562" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.standard.bold[3]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.standard.bold[1]</t>
         </is>
       </c>
       <c r="B562" t="inlineStr" s="2">
@@ -18412,7 +18390,7 @@
       </c>
       <c r="D562" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.bold[3]</t>
+          <t xml:space="preserve">standard.bold[1]</t>
         </is>
       </c>
       <c r="E562" t="inlineStr" s="2">
@@ -18422,14 +18400,14 @@
       </c>
       <c r="F562" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">はっ、他所の団体なんてこんなもんよ！</t>
+          <t xml:space="preserve">当然でしょ！ うちの団体を甘く見ないでよね！</t>
         </is>
       </c>
     </row>
     <row r="563" ht="40" customHeight="1">
       <c r="A563" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.standard.bold[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.standard.bold[2]</t>
         </is>
       </c>
       <c r="B563" t="inlineStr" s="2">
@@ -18439,29 +18417,29 @@
       </c>
       <c r="C563" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D563" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.standard.bold[1]</t>
+          <t xml:space="preserve">standard.bold[2]</t>
         </is>
       </c>
       <c r="E563" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F563" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここが頂点？…でもまだ先がある気がする</t>
+          <t xml:space="preserve">この勝利は団体のみんなの勝利よ！</t>
         </is>
       </c>
     </row>
     <row r="564" ht="40" customHeight="1">
       <c r="A564" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.standard.bold[2]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.standard.bold[3]</t>
         </is>
       </c>
       <c r="B564" t="inlineStr" s="2">
@@ -18471,29 +18449,29 @@
       </c>
       <c r="C564" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D564" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.standard.bold[2]</t>
+          <t xml:space="preserve">standard.bold[3]</t>
         </is>
       </c>
       <c r="E564" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F564" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここで終わりじゃない。もっと強くなって、もっと上を目指す</t>
+          <t xml:space="preserve">はっ、他所の団体なんてこんなもんよ！</t>
         </is>
       </c>
     </row>
     <row r="565" ht="40" customHeight="1">
       <c r="A565" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.standard.bold[3]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter.standard.bold[1]</t>
         </is>
       </c>
       <c r="B565" t="inlineStr" s="2">
@@ -18508,7 +18486,7 @@
       </c>
       <c r="D565" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.standard.bold[3]</t>
+          <t xml:space="preserve">fighter.standard.bold[1]</t>
         </is>
       </c>
       <c r="E565" t="inlineStr" s="2">
@@ -18518,14 +18496,14 @@
       </c>
       <c r="F565" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私たちの戦いが業界を変えたってことね。誇りに思うよ</t>
+          <t xml:space="preserve">ここが頂点？…でもまだ先がある気がする</t>
         </is>
       </c>
     </row>
     <row r="566" ht="40" customHeight="1">
       <c r="A566" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.standard.bold[1]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter.standard.bold[2]</t>
         </is>
       </c>
       <c r="B566" t="inlineStr" s="2">
@@ -18535,29 +18513,29 @@
       </c>
       <c r="C566" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
       <c r="D566" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.bold[1]</t>
+          <t xml:space="preserve">fighter.standard.bold[2]</t>
         </is>
       </c>
       <c r="E566" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
       <c r="F566" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">フリーのままで終わる女じゃないって、証明する</t>
+          <t xml:space="preserve">ここで終わりじゃない。もっと強くなって、もっと上を目指す</t>
         </is>
       </c>
     </row>
     <row r="567" ht="40" customHeight="1">
       <c r="A567" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.standard.bold[2]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter.standard.bold[3]</t>
         </is>
       </c>
       <c r="B567" t="inlineStr" s="2">
@@ -18567,29 +18545,29 @@
       </c>
       <c r="C567" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
       <c r="D567" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.bold[2]</t>
+          <t xml:space="preserve">fighter.standard.bold[3]</t>
         </is>
       </c>
       <c r="E567" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
       <c r="F567" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">払ってくれた分は、全部利子つけて返してやる</t>
+          <t xml:space="preserve">私たちの戦いが業界を変えたってことね。誇りに思うよ</t>
         </is>
       </c>
     </row>
     <row r="568" ht="40" customHeight="1">
       <c r="A568" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.standard.bold[1]</t>
+          <t xml:space="preserve">FA_GREETING_LINES.standard.bold[1]</t>
         </is>
       </c>
       <c r="B568" t="inlineStr" s="2">
@@ -18599,7 +18577,7 @@
       </c>
       <c r="C568" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
         </is>
       </c>
       <c r="D568" t="inlineStr" s="12">
@@ -18614,44 +18592,108 @@
       </c>
       <c r="F568" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">見る目あるじゃん。すぐ活躍してみせるよ</t>
+          <t xml:space="preserve">フリーのままで終わる女じゃないって、証明する</t>
         </is>
       </c>
     </row>
     <row r="569" ht="40" customHeight="1">
       <c r="A569" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">FA_GREETING_LINES.standard.bold[2]</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold[2]</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">払ってくれた分は、全部利子つけて返してやる</t>
+        </is>
+      </c>
+    </row>
+    <row r="570" ht="40" customHeight="1">
+      <c r="A570" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">見る目あるじゃん。すぐ活躍してみせるよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="571" ht="40" customHeight="1">
+      <c r="A571" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.standard.bold[2]</t>
         </is>
       </c>
-      <c r="B569" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C569" t="inlineStr" s="2">
+      <c r="B571" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D569" t="inlineStr" s="12">
+      <c r="D571" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">standard.bold[2]</t>
         </is>
       </c>
-      <c r="E569" t="inlineStr" s="2">
+      <c r="E571" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F569" t="inlineStr" s="3">
+      <c r="F571" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">買われた実力、値段以上だったって言わせてみせるよ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H569"/>
+  <autoFilter ref="A1:H571"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/標準×強気.xlsx
+++ b/セリフ編集/キャラタイプ別/標準×強気.xlsx
@@ -389,7 +389,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H571"/>
+  <dimension ref="A1:H573"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -16391,7 +16391,7 @@
     <row r="500" ht="40" customHeight="1">
       <c r="A500" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02-hostile.standard.bold[1]</t>
         </is>
       </c>
       <c r="B500" t="inlineStr" s="2">
@@ -16406,7 +16406,7 @@
       </c>
       <c r="D500" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.standard.bold[1]</t>
+          <t xml:space="preserve">GL-02-hostile.standard.bold[1]</t>
         </is>
       </c>
       <c r="E500" t="inlineStr" s="2">
@@ -16416,14 +16416,14 @@
       </c>
       <c r="F500" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだまだ！ もっと追い込むよ！</t>
+          <t xml:space="preserve">次は絶対やってやる。燃えてきた！</t>
         </is>
       </c>
     </row>
     <row r="501" ht="40" customHeight="1">
       <c r="A501" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.bold[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02-hostile.standard.bold[2]</t>
         </is>
       </c>
       <c r="B501" t="inlineStr" s="2">
@@ -16438,7 +16438,7 @@
       </c>
       <c r="D501" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-02.standard.bold[2]</t>
+          <t xml:space="preserve">GL-02-hostile.standard.bold[2]</t>
         </is>
       </c>
       <c r="E501" t="inlineStr" s="2">
@@ -16448,14 +16448,14 @@
       </c>
       <c r="F501" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなもんで満足できない！ 次！</t>
+          <t xml:space="preserve">あいつがいる限り、手を抜けるわけがない</t>
         </is>
       </c>
     </row>
     <row r="502" ht="40" customHeight="1">
       <c r="A502" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.standard.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.bold[1]</t>
         </is>
       </c>
       <c r="B502" t="inlineStr" s="2">
@@ -16470,7 +16470,7 @@
       </c>
       <c r="D502" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.down.standard.bold[1]</t>
+          <t xml:space="preserve">GL-02.standard.bold[1]</t>
         </is>
       </c>
       <c r="E502" t="inlineStr" s="2">
@@ -16480,14 +16480,14 @@
       </c>
       <c r="F502" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何だよ最近の扱いは。私を軽く見てるの？</t>
+          <t xml:space="preserve">まだまだ！ もっと追い込むよ！</t>
         </is>
       </c>
     </row>
     <row r="503" ht="40" customHeight="1">
       <c r="A503" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.standard.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-02.standard.bold[2]</t>
         </is>
       </c>
       <c r="B503" t="inlineStr" s="2">
@@ -16502,7 +16502,7 @@
       </c>
       <c r="D503" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-03.up.standard.bold[1]</t>
+          <t xml:space="preserve">GL-02.standard.bold[2]</t>
         </is>
       </c>
       <c r="E503" t="inlineStr" s="2">
@@ -16512,14 +16512,14 @@
       </c>
       <c r="F503" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体、やっぱり最高！ もっと盛り上げてみせる！</t>
+          <t xml:space="preserve">こんなもんで満足できない！ 次！</t>
         </is>
       </c>
     </row>
     <row r="504" ht="40" customHeight="1">
       <c r="A504" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.standard.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.down.standard.bold[1]</t>
         </is>
       </c>
       <c r="B504" t="inlineStr" s="2">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="D504" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-04.standard.bold[1]</t>
+          <t xml:space="preserve">GL-03.down.standard.bold[1]</t>
         </is>
       </c>
       <c r="E504" t="inlineStr" s="2">
@@ -16544,14 +16544,14 @@
       </c>
       <c r="F504" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい仲間だよ。一緒に強くなろう</t>
+          <t xml:space="preserve">何だよ最近の扱いは。私を軽く見てるの？</t>
         </is>
       </c>
     </row>
     <row r="505" ht="40" customHeight="1">
       <c r="A505" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.standard.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-03.up.standard.bold[1]</t>
         </is>
       </c>
       <c r="B505" t="inlineStr" s="2">
@@ -16566,7 +16566,7 @@
       </c>
       <c r="D505" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-05.standard.bold[1]</t>
+          <t xml:space="preserve">GL-03.up.standard.bold[1]</t>
         </is>
       </c>
       <c r="E505" t="inlineStr" s="2">
@@ -16576,14 +16576,14 @@
       </c>
       <c r="F505" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けてたまるか。見てなさいよ！</t>
+          <t xml:space="preserve">この団体、やっぱり最高！ もっと盛り上げてみせる！</t>
         </is>
       </c>
     </row>
     <row r="506" ht="40" customHeight="1">
       <c r="A506" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-04.standard.bold[1]</t>
         </is>
       </c>
       <c r="B506" t="inlineStr" s="2">
@@ -16598,7 +16598,7 @@
       </c>
       <c r="D506" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.standard.bold[1]</t>
+          <t xml:space="preserve">GL-04.standard.bold[1]</t>
         </is>
       </c>
       <c r="E506" t="inlineStr" s="2">
@@ -16608,14 +16608,14 @@
       </c>
       <c r="F506" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんで私を使わないの！ 実力は見せてるでしょ！</t>
+          <t xml:space="preserve">いい仲間だよ。一緒に強くなろう</t>
         </is>
       </c>
     </row>
     <row r="507" ht="40" customHeight="1">
       <c r="A507" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.bold[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-05.standard.bold[1]</t>
         </is>
       </c>
       <c r="B507" t="inlineStr" s="2">
@@ -16630,7 +16630,7 @@
       </c>
       <c r="D507" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-06.standard.bold[2]</t>
+          <t xml:space="preserve">GL-05.standard.bold[1]</t>
         </is>
       </c>
       <c r="E507" t="inlineStr" s="2">
@@ -16640,14 +16640,14 @@
       </c>
       <c r="F507" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">リングに上がらせて！ くすぶってる場合じゃないのよ！</t>
+          <t xml:space="preserve">負けてたまるか。見てなさいよ！</t>
         </is>
       </c>
     </row>
     <row r="508" ht="40" customHeight="1">
       <c r="A508" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.standard.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.bold[1]</t>
         </is>
       </c>
       <c r="B508" t="inlineStr" s="2">
@@ -16662,7 +16662,7 @@
       </c>
       <c r="D508" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-07.standard.bold[1]</t>
+          <t xml:space="preserve">GL-06.standard.bold[1]</t>
         </is>
       </c>
       <c r="E508" t="inlineStr" s="2">
@@ -16672,14 +16672,14 @@
       </c>
       <c r="F508" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ちっ、体がなまってる…休んでる場合じゃないのに</t>
+          <t xml:space="preserve">なんで私を使わないの！ 実力は見せてるでしょ！</t>
         </is>
       </c>
     </row>
     <row r="509" ht="40" customHeight="1">
       <c r="A509" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-06.standard.bold[2]</t>
         </is>
       </c>
       <c r="B509" t="inlineStr" s="2">
@@ -16694,7 +16694,7 @@
       </c>
       <c r="D509" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.standard.bold[1]</t>
+          <t xml:space="preserve">GL-06.standard.bold[2]</t>
         </is>
       </c>
       <c r="E509" t="inlineStr" s="2">
@@ -16704,14 +16704,14 @@
       </c>
       <c r="F509" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…このまま終わるつもりはないから！</t>
+          <t xml:space="preserve">リングに上がらせて！ くすぶってる場合じゃないのよ！</t>
         </is>
       </c>
     </row>
     <row r="510" ht="40" customHeight="1">
       <c r="A510" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.bold[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-07.standard.bold[1]</t>
         </is>
       </c>
       <c r="B510" t="inlineStr" s="2">
@@ -16726,7 +16726,7 @@
       </c>
       <c r="D510" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-08.standard.bold[2]</t>
+          <t xml:space="preserve">GL-07.standard.bold[1]</t>
         </is>
       </c>
       <c r="E510" t="inlineStr" s="2">
@@ -16736,14 +16736,14 @@
       </c>
       <c r="F510" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いつまで負け続ける気だ…！ 目を覚ませ、私！</t>
+          <t xml:space="preserve">ちっ、体がなまってる…休んでる場合じゃないのに</t>
         </is>
       </c>
     </row>
     <row r="511" ht="40" customHeight="1">
       <c r="A511" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.standard.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.bold[1]</t>
         </is>
       </c>
       <c r="B511" t="inlineStr" s="2">
@@ -16758,7 +16758,7 @@
       </c>
       <c r="D511" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.standard.bold[1]</t>
+          <t xml:space="preserve">GL-08.standard.bold[1]</t>
         </is>
       </c>
       <c r="E511" t="inlineStr" s="2">
@@ -16768,14 +16768,14 @@
       </c>
       <c r="F511" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">絶好調！ この波に乗って一気に行くぞ！</t>
+          <t xml:space="preserve">…このまま終わるつもりはないから！</t>
         </is>
       </c>
     </row>
     <row r="512" ht="40" customHeight="1">
       <c r="A512" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.standard.bold[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-08.standard.bold[2]</t>
         </is>
       </c>
       <c r="B512" t="inlineStr" s="2">
@@ -16790,7 +16790,7 @@
       </c>
       <c r="D512" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-09.standard.bold[2]</t>
+          <t xml:space="preserve">GL-08.standard.bold[2]</t>
         </is>
       </c>
       <c r="E512" t="inlineStr" s="2">
@@ -16800,14 +16800,14 @@
       </c>
       <c r="F512" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今の私を止められるやつはいない！</t>
+          <t xml:space="preserve">いつまで負け続ける気だ…！ 目を覚ませ、私！</t>
         </is>
       </c>
     </row>
     <row r="513" ht="40" customHeight="1">
       <c r="A513" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.standard.bold[1]</t>
         </is>
       </c>
       <c r="B513" t="inlineStr" s="2">
@@ -16822,7 +16822,7 @@
       </c>
       <c r="D513" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.standard.bold[1]</t>
+          <t xml:space="preserve">GL-09.standard.bold[1]</t>
         </is>
       </c>
       <c r="E513" t="inlineStr" s="2">
@@ -16832,14 +16832,14 @@
       </c>
       <c r="F513" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなとこで寝てる場合じゃない…！</t>
+          <t xml:space="preserve">絶好調！ この波に乗って一気に行くぞ！</t>
         </is>
       </c>
     </row>
     <row r="514" ht="40" customHeight="1">
       <c r="A514" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.bold[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-09.standard.bold[2]</t>
         </is>
       </c>
       <c r="B514" t="inlineStr" s="2">
@@ -16854,7 +16854,7 @@
       </c>
       <c r="D514" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">GL-10.standard.bold[2]</t>
+          <t xml:space="preserve">GL-09.standard.bold[2]</t>
         </is>
       </c>
       <c r="E514" t="inlineStr" s="2">
@@ -16864,14 +16864,14 @@
       </c>
       <c r="F514" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私がいない間に追い抜かれるのは耐えられない！</t>
+          <t xml:space="preserve">今の私を止められるやつはいない！</t>
         </is>
       </c>
     </row>
     <row r="515" ht="40" customHeight="1">
       <c r="A515" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.bold[1]</t>
         </is>
       </c>
       <c r="B515" t="inlineStr" s="2">
@@ -16881,12 +16881,12 @@
       </c>
       <c r="C515" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D515" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.bold[1]</t>
+          <t xml:space="preserve">GL-10.standard.bold[1]</t>
         </is>
       </c>
       <c r="E515" t="inlineStr" s="2">
@@ -16896,14 +16896,14 @@
       </c>
       <c r="F515" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……身体のキレも普通に戻ってきちゃったかな。でも、いい感覚は体が覚えてるよ！</t>
+          <t xml:space="preserve">こんなとこで寝てる場合じゃない…！</t>
         </is>
       </c>
     </row>
     <row r="516" ht="40" customHeight="1">
       <c r="A516" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.bold[2]</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES.GL-10.standard.bold[2]</t>
         </is>
       </c>
       <c r="B516" t="inlineStr" s="2">
@@ -16913,12 +16913,12 @@
       </c>
       <c r="C516" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_B_LINES</t>
         </is>
       </c>
       <c r="D516" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.bold[2]</t>
+          <t xml:space="preserve">GL-10.standard.bold[2]</t>
         </is>
       </c>
       <c r="E516" t="inlineStr" s="2">
@@ -16928,14 +16928,14 @@
       </c>
       <c r="F516" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの好調で掴んだ感覚は忘れない。次に繋げてみせる</t>
+          <t xml:space="preserve">私がいない間に追い抜かれるのは耐えられない！</t>
         </is>
       </c>
     </row>
     <row r="517" ht="40" customHeight="1">
       <c r="A517" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.bold[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.bold[1]</t>
         </is>
       </c>
       <c r="B517" t="inlineStr" s="2">
@@ -16945,29 +16945,29 @@
       </c>
       <c r="C517" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D517" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.bold[1]</t>
+          <t xml:space="preserve">standard.bold[1]</t>
         </is>
       </c>
       <c r="E517" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F517" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">傷だらけで結構。最後まで残ったのはこっちだ。全部持っていく</t>
+          <t xml:space="preserve">……身体のキレも普通に戻ってきちゃったかな。でも、いい感覚は体が覚えてるよ！</t>
         </is>
       </c>
     </row>
     <row r="518" ht="40" customHeight="1">
       <c r="A518" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.bold[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.standard.bold[2]</t>
         </is>
       </c>
       <c r="B518" t="inlineStr" s="2">
@@ -16977,29 +16977,29 @@
       </c>
       <c r="C518" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D518" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.bold[2]</t>
+          <t xml:space="preserve">standard.bold[2]</t>
         </is>
       </c>
       <c r="E518" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F518" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで抜いてきて、最後で退くわけないでしょ。獲りにいく</t>
+          <t xml:space="preserve">あの好調で掴んだ感覚は忘れない。次に繋げてみせる</t>
         </is>
       </c>
     </row>
     <row r="519" ht="40" customHeight="1">
       <c r="A519" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.bold[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.bold[1]</t>
         </is>
       </c>
       <c r="B519" t="inlineStr" s="2">
@@ -17014,7 +17014,7 @@
       </c>
       <c r="D519" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.bold[3]</t>
+          <t xml:space="preserve">preFinal.standard.bold[1]</t>
         </is>
       </c>
       <c r="E519" t="inlineStr" s="2">
@@ -17024,14 +17024,14 @@
       </c>
       <c r="F519" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">身体は重いけど、心は決まってる。この一戦、全部私がもらう</t>
+          <t xml:space="preserve">傷だらけで結構。最後まで残ったのはこっちだ。全部持っていく</t>
         </is>
       </c>
     </row>
     <row r="520" ht="40" customHeight="1">
       <c r="A520" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.bold[2]</t>
         </is>
       </c>
       <c r="B520" t="inlineStr" s="2">
@@ -17046,7 +17046,7 @@
       </c>
       <c r="D520" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.bold[1]</t>
+          <t xml:space="preserve">preFinal.standard.bold[2]</t>
         </is>
       </c>
       <c r="E520" t="inlineStr" s="2">
@@ -17056,14 +17056,14 @@
       </c>
       <c r="F520" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">何人並んでようが関係ない。真っ向から薙ぎ倒して、次に繋ぐ</t>
+          <t xml:space="preserve">ここまで抜いてきて、最後で退くわけないでしょ。獲りにいく</t>
         </is>
       </c>
     </row>
     <row r="521" ht="40" customHeight="1">
       <c r="A521" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.standard.bold[3]</t>
         </is>
       </c>
       <c r="B521" t="inlineStr" s="2">
@@ -17078,7 +17078,7 @@
       </c>
       <c r="D521" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.bold[2]</t>
+          <t xml:space="preserve">preFinal.standard.bold[3]</t>
         </is>
       </c>
       <c r="E521" t="inlineStr" s="2">
@@ -17088,14 +17088,14 @@
       </c>
       <c r="F521" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">来るなら来い。このリングを抜けさせると思ってんのか</t>
+          <t xml:space="preserve">身体は重いけど、心は決まってる。この一戦、全部私がもらう</t>
         </is>
       </c>
     </row>
     <row r="522" ht="40" customHeight="1">
       <c r="A522" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.bold[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.bold[1]</t>
         </is>
       </c>
       <c r="B522" t="inlineStr" s="2">
@@ -17110,7 +17110,7 @@
       </c>
       <c r="D522" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.bold[3]</t>
+          <t xml:space="preserve">preMatch.standard.bold[1]</t>
         </is>
       </c>
       <c r="E522" t="inlineStr" s="2">
@@ -17120,14 +17120,14 @@
       </c>
       <c r="F522" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手が誰だろうと、結果は変わらない。最後に立ってるのは私よ</t>
+          <t xml:space="preserve">何人並んでようが関係ない。真っ向から薙ぎ倒して、次に繋ぐ</t>
         </is>
       </c>
     </row>
     <row r="523" ht="40" customHeight="1">
       <c r="A523" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.bold[2]</t>
         </is>
       </c>
       <c r="B523" t="inlineStr" s="2">
@@ -17142,7 +17142,7 @@
       </c>
       <c r="D523" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.standard.bold[1]</t>
+          <t xml:space="preserve">preMatch.standard.bold[2]</t>
         </is>
       </c>
       <c r="E523" t="inlineStr" s="2">
@@ -17152,14 +17152,14 @@
       </c>
       <c r="F523" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人落とした。…息は上がってる。だから何だ? 次、まとめて来い</t>
+          <t xml:space="preserve">来るなら来い。このリングを抜けさせると思ってんのか</t>
         </is>
       </c>
     </row>
     <row r="524" ht="40" customHeight="1">
       <c r="A524" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.standard.bold[3]</t>
         </is>
       </c>
       <c r="B524" t="inlineStr" s="2">
@@ -17174,7 +17174,7 @@
       </c>
       <c r="D524" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.standard.bold[2]</t>
+          <t xml:space="preserve">preMatch.standard.bold[3]</t>
         </is>
       </c>
       <c r="E524" t="inlineStr" s="2">
@@ -17184,14 +17184,14 @@
       </c>
       <c r="F524" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだ立ってる。このリングを抜けたいなら、私を倒してからにしなさい。次</t>
+          <t xml:space="preserve">相手が誰だろうと、結果は変わらない。最後に立ってるのは私よ</t>
         </is>
       </c>
     </row>
     <row r="525" ht="40" customHeight="1">
       <c r="A525" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.bold[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.bold[1]</t>
         </is>
       </c>
       <c r="B525" t="inlineStr" s="2">
@@ -17206,7 +17206,7 @@
       </c>
       <c r="D525" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.standard.bold[3]</t>
+          <t xml:space="preserve">survivor.standard.bold[1]</t>
         </is>
       </c>
       <c r="E525" t="inlineStr" s="2">
@@ -17216,14 +17216,14 @@
       </c>
       <c r="F525" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一丁上がり。…息は切れてるけど、拳はまだ握れる。次、出てきな</t>
+          <t xml:space="preserve">一人落とした。…息は上がってる。だから何だ? 次、まとめて来い</t>
         </is>
       </c>
     </row>
     <row r="526" ht="40" customHeight="1">
       <c r="A526" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.bold[2]</t>
         </is>
       </c>
       <c r="B526" t="inlineStr" s="2">
@@ -17233,12 +17233,12 @@
       </c>
       <c r="C526" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D526" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.bold[1]</t>
+          <t xml:space="preserve">survivor.standard.bold[2]</t>
         </is>
       </c>
       <c r="E526" t="inlineStr" s="2">
@@ -17248,14 +17248,14 @@
       </c>
       <c r="F526" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体の三人が、一番強かった。今日の答えは、それで十分でしょ</t>
+          <t xml:space="preserve">まだ立ってる。このリングを抜けたいなら、私を倒してからにしなさい。次</t>
         </is>
       </c>
     </row>
     <row r="527" ht="40" customHeight="1">
       <c r="A527" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.standard.bold[3]</t>
         </is>
       </c>
       <c r="B527" t="inlineStr" s="2">
@@ -17265,12 +17265,12 @@
       </c>
       <c r="C527" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D527" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.bold[2]</t>
+          <t xml:space="preserve">survivor.standard.bold[3]</t>
         </is>
       </c>
       <c r="E527" t="inlineStr" s="2">
@@ -17280,14 +17280,14 @@
       </c>
       <c r="F527" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人で最強を証明した。これ以上の答えがあるなら聞いてみたいね</t>
+          <t xml:space="preserve">一丁上がり。…息は切れてるけど、拳はまだ握れる。次、出てきな</t>
         </is>
       </c>
     </row>
     <row r="528" ht="40" customHeight="1">
       <c r="A528" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.bold[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.bold[1]</t>
         </is>
       </c>
       <c r="B528" t="inlineStr" s="2">
@@ -17302,7 +17302,7 @@
       </c>
       <c r="D528" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.bold[3]</t>
+          <t xml:space="preserve">champion.standard.bold[1]</t>
         </is>
       </c>
       <c r="E528" t="inlineStr" s="2">
@@ -17312,14 +17312,14 @@
       </c>
       <c r="F528" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間が信じてくれたから、最後まで攻められた。この三人に勝てる奴はいない</t>
+          <t xml:space="preserve">この団体の三人が、一番強かった。今日の答えは、それで十分でしょ</t>
         </is>
       </c>
     </row>
     <row r="529" ht="40" customHeight="1">
       <c r="A529" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.bold[2]</t>
         </is>
       </c>
       <c r="B529" t="inlineStr" s="2">
@@ -17334,7 +17334,7 @@
       </c>
       <c r="D529" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.standard.bold[1]</t>
+          <t xml:space="preserve">champion.standard.bold[2]</t>
         </is>
       </c>
       <c r="E529" t="inlineStr" s="2">
@@ -17344,14 +17344,14 @@
       </c>
       <c r="F529" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">賞はもらう。でも優勝旗は向こうだ。次は、あれごと奪う</t>
+          <t xml:space="preserve">三人で最強を証明した。これ以上の答えがあるなら聞いてみたいね</t>
         </is>
       </c>
     </row>
     <row r="530" ht="40" customHeight="1">
       <c r="A530" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.standard.bold[3]</t>
         </is>
       </c>
       <c r="B530" t="inlineStr" s="2">
@@ -17366,7 +17366,7 @@
       </c>
       <c r="D530" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.standard.bold[2]</t>
+          <t xml:space="preserve">champion.standard.bold[3]</t>
         </is>
       </c>
       <c r="E530" t="inlineStr" s="2">
@@ -17376,14 +17376,14 @@
       </c>
       <c r="F530" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVP？ そんなもんで満足できるわけないでしょ。次は団体ごと叩き潰す</t>
+          <t xml:space="preserve">仲間が信じてくれたから、最後まで攻められた。この三人に勝てる奴はいない</t>
         </is>
       </c>
     </row>
     <row r="531" ht="40" customHeight="1">
       <c r="A531" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.bold[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.bold[1]</t>
         </is>
       </c>
       <c r="B531" t="inlineStr" s="2">
@@ -17398,7 +17398,7 @@
       </c>
       <c r="D531" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.standard.bold[3]</t>
+          <t xml:space="preserve">defiant.standard.bold[1]</t>
         </is>
       </c>
       <c r="E531" t="inlineStr" s="2">
@@ -17408,14 +17408,14 @@
       </c>
       <c r="F531" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">個人で勝っても、チームが負けたら意味がない。次は絶対に獲る</t>
+          <t xml:space="preserve">賞はもらう。でも優勝旗は向こうだ。次は、あれごと奪う</t>
         </is>
       </c>
     </row>
     <row r="532" ht="40" customHeight="1">
       <c r="A532" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.bold[2]</t>
         </is>
       </c>
       <c r="B532" t="inlineStr" s="2">
@@ -17430,7 +17430,7 @@
       </c>
       <c r="D532" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.standard.bold[1]</t>
+          <t xml:space="preserve">defiant.standard.bold[2]</t>
         </is>
       </c>
       <c r="E532" t="inlineStr" s="2">
@@ -17440,14 +17440,14 @@
       </c>
       <c r="F532" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">三人だろうが四人だろうが、立って来るなら倒す。今日はそれを証明しただけ</t>
+          <t xml:space="preserve">MVP？ そんなもんで満足できるわけないでしょ。次は団体ごと叩き潰す</t>
         </is>
       </c>
     </row>
     <row r="533" ht="40" customHeight="1">
       <c r="A533" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.standard.bold[3]</t>
         </is>
       </c>
       <c r="B533" t="inlineStr" s="2">
@@ -17462,7 +17462,7 @@
       </c>
       <c r="D533" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.standard.bold[2]</t>
+          <t xml:space="preserve">defiant.standard.bold[3]</t>
         </is>
       </c>
       <c r="E533" t="inlineStr" s="2">
@@ -17472,14 +17472,14 @@
       </c>
       <c r="F533" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次が来るなら、何人でもいい。この拳はまだ握れてる</t>
+          <t xml:space="preserve">個人で勝っても、チームが負けたら意味がない。次は絶対に獲る</t>
         </is>
       </c>
     </row>
     <row r="534" ht="40" customHeight="1">
       <c r="A534" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.bold[3]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.bold[1]</t>
         </is>
       </c>
       <c r="B534" t="inlineStr" s="2">
@@ -17494,7 +17494,7 @@
       </c>
       <c r="D534" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.standard.bold[3]</t>
+          <t xml:space="preserve">gauntlet.standard.bold[1]</t>
         </is>
       </c>
       <c r="E534" t="inlineStr" s="2">
@@ -17504,14 +17504,14 @@
       </c>
       <c r="F534" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全員まとめて相手にしてやった。文句あるなら、もう一回並べ</t>
+          <t xml:space="preserve">三人だろうが四人だろうが、立って来るなら倒す。今日はそれを証明しただけ</t>
         </is>
       </c>
     </row>
     <row r="535" ht="40" customHeight="1">
       <c r="A535" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.bold[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.bold[2]</t>
         </is>
       </c>
       <c r="B535" t="inlineStr" s="2">
@@ -17521,12 +17521,12 @@
       </c>
       <c r="C535" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D535" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.bold[1]</t>
+          <t xml:space="preserve">gauntlet.standard.bold[2]</t>
         </is>
       </c>
       <c r="E535" t="inlineStr" s="2">
@@ -17536,14 +17536,14 @@
       </c>
       <c r="F535" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">言ったでしょ？ 私が最強だって</t>
+          <t xml:space="preserve">次が来るなら、何人でもいい。この拳はまだ握れてる</t>
         </is>
       </c>
     </row>
     <row r="536" ht="40" customHeight="1">
       <c r="A536" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.bold[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.standard.bold[3]</t>
         </is>
       </c>
       <c r="B536" t="inlineStr" s="2">
@@ -17553,12 +17553,12 @@
       </c>
       <c r="C536" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D536" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.standard.bold[2]</t>
+          <t xml:space="preserve">gauntlet.standard.bold[3]</t>
         </is>
       </c>
       <c r="E536" t="inlineStr" s="2">
@@ -17568,14 +17568,14 @@
       </c>
       <c r="F536" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">はい優勝。当然の結果ね</t>
+          <t xml:space="preserve">全員まとめて相手にしてやった。文句あるなら、もう一回並べ</t>
         </is>
       </c>
     </row>
     <row r="537" ht="40" customHeight="1">
       <c r="A537" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.bold[1]</t>
         </is>
       </c>
       <c r="B537" t="inlineStr" s="2">
@@ -17590,7 +17590,7 @@
       </c>
       <c r="D537" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.standard.bold[1]</t>
+          <t xml:space="preserve">champion.standard.bold[1]</t>
         </is>
       </c>
       <c r="E537" t="inlineStr" s="2">
@@ -17600,14 +17600,14 @@
       </c>
       <c r="F537" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなはずじゃ…！ 次は絶対に見返す！</t>
+          <t xml:space="preserve">言ったでしょ？ 私が最強だって</t>
         </is>
       </c>
     </row>
     <row r="538" ht="40" customHeight="1">
       <c r="A538" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.champion.standard.bold[2]</t>
         </is>
       </c>
       <c r="B538" t="inlineStr" s="2">
@@ -17622,7 +17622,7 @@
       </c>
       <c r="D538" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postLose.standard.bold[2]</t>
+          <t xml:space="preserve">champion.standard.bold[2]</t>
         </is>
       </c>
       <c r="E538" t="inlineStr" s="2">
@@ -17632,14 +17632,14 @@
       </c>
       <c r="F538" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">認めない。次は絶対に勝つ</t>
+          <t xml:space="preserve">はい優勝。当然の結果ね</t>
         </is>
       </c>
     </row>
     <row r="539" ht="40" customHeight="1">
       <c r="A539" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.bold[1]</t>
         </is>
       </c>
       <c r="B539" t="inlineStr" s="2">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="D539" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.standard.bold[1]</t>
+          <t xml:space="preserve">postLose.standard.bold[1]</t>
         </is>
       </c>
       <c r="E539" t="inlineStr" s="2">
@@ -17664,14 +17664,14 @@
       </c>
       <c r="F539" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然の結果よ。次も同じ</t>
+          <t xml:space="preserve">こんなはずじゃ…！ 次は絶対に見返す！</t>
         </is>
       </c>
     </row>
     <row r="540" ht="40" customHeight="1">
       <c r="A540" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postLose.standard.bold[2]</t>
         </is>
       </c>
       <c r="B540" t="inlineStr" s="2">
@@ -17686,7 +17686,7 @@
       </c>
       <c r="D540" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postMatchWin.standard.bold[2]</t>
+          <t xml:space="preserve">postLose.standard.bold[2]</t>
         </is>
       </c>
       <c r="E540" t="inlineStr" s="2">
@@ -17696,14 +17696,14 @@
       </c>
       <c r="F540" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふん。この程度じゃ止まらないわよ</t>
+          <t xml:space="preserve">認めない。次は絶対に勝つ</t>
         </is>
       </c>
     </row>
     <row r="541" ht="40" customHeight="1">
       <c r="A541" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.bold[1]</t>
         </is>
       </c>
       <c r="B541" t="inlineStr" s="2">
@@ -17718,7 +17718,7 @@
       </c>
       <c r="D541" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.standard.bold[1]</t>
+          <t xml:space="preserve">postMatchWin.standard.bold[1]</t>
         </is>
       </c>
       <c r="E541" t="inlineStr" s="2">
@@ -17728,14 +17728,14 @@
       </c>
       <c r="F541" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然の結果ね。次は優勝よ</t>
+          <t xml:space="preserve">当然の結果よ。次も同じ</t>
         </is>
       </c>
     </row>
     <row r="542" ht="40" customHeight="1">
       <c r="A542" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postMatchWin.standard.bold[2]</t>
         </is>
       </c>
       <c r="B542" t="inlineStr" s="2">
@@ -17750,7 +17750,7 @@
       </c>
       <c r="D542" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">postWin.standard.bold[2]</t>
+          <t xml:space="preserve">postMatchWin.standard.bold[2]</t>
         </is>
       </c>
       <c r="E542" t="inlineStr" s="2">
@@ -17760,14 +17760,14 @@
       </c>
       <c r="F542" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この程度で満足するわけないでしょ</t>
+          <t xml:space="preserve">ふん。この程度じゃ止まらないわよ</t>
         </is>
       </c>
     </row>
     <row r="543" ht="40" customHeight="1">
       <c r="A543" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.bold[1]</t>
         </is>
       </c>
       <c r="B543" t="inlineStr" s="2">
@@ -17782,7 +17782,7 @@
       </c>
       <c r="D543" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.bold[1]</t>
+          <t xml:space="preserve">postWin.standard.bold[1]</t>
         </is>
       </c>
       <c r="E543" t="inlineStr" s="2">
@@ -17792,14 +17792,14 @@
       </c>
       <c r="F543" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来て負けるわけないでしょ。最後も私が獲る</t>
+          <t xml:space="preserve">当然の結果ね。次は優勝よ</t>
         </is>
       </c>
     </row>
     <row r="544" ht="40" customHeight="1">
       <c r="A544" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.postWin.standard.bold[2]</t>
         </is>
       </c>
       <c r="B544" t="inlineStr" s="2">
@@ -17814,7 +17814,7 @@
       </c>
       <c r="D544" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.standard.bold[2]</t>
+          <t xml:space="preserve">postWin.standard.bold[2]</t>
         </is>
       </c>
       <c r="E544" t="inlineStr" s="2">
@@ -17824,14 +17824,14 @@
       </c>
       <c r="F544" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">さあ、最後の獲物ね。楽しませてもらうわ</t>
+          <t xml:space="preserve">この程度で満足するわけないでしょ</t>
         </is>
       </c>
     </row>
     <row r="545" ht="40" customHeight="1">
       <c r="A545" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.bold[1]</t>
         </is>
       </c>
       <c r="B545" t="inlineStr" s="2">
@@ -17846,7 +17846,7 @@
       </c>
       <c r="D545" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.bold[1]</t>
+          <t xml:space="preserve">preFinal.standard.bold[1]</t>
         </is>
       </c>
       <c r="E545" t="inlineStr" s="2">
@@ -17856,14 +17856,14 @@
       </c>
       <c r="F545" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">目の前の相手を叩き潰す。それだけよ</t>
+          <t xml:space="preserve">ここまで来て負けるわけないでしょ。最後も私が獲る</t>
         </is>
       </c>
     </row>
     <row r="546" ht="40" customHeight="1">
       <c r="A546" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preFinal.standard.bold[2]</t>
         </is>
       </c>
       <c r="B546" t="inlineStr" s="2">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="D546" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.standard.bold[2]</t>
+          <t xml:space="preserve">preFinal.standard.bold[2]</t>
         </is>
       </c>
       <c r="E546" t="inlineStr" s="2">
@@ -17888,14 +17888,14 @@
       </c>
       <c r="F546" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝つのは私。最初から決まってることよ</t>
+          <t xml:space="preserve">さあ、最後の獲物ね。楽しませてもらうわ</t>
         </is>
       </c>
     </row>
     <row r="547" ht="40" customHeight="1">
       <c r="A547" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.bold[1]</t>
         </is>
       </c>
       <c r="B547" t="inlineStr" s="2">
@@ -17910,7 +17910,7 @@
       </c>
       <c r="D547" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.standard.bold[1]</t>
+          <t xml:space="preserve">preMatch.standard.bold[1]</t>
         </is>
       </c>
       <c r="E547" t="inlineStr" s="2">
@@ -17920,14 +17920,14 @@
       </c>
       <c r="F547" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然。呼ばれなかったら怒ってたわ</t>
+          <t xml:space="preserve">目の前の相手を叩き潰す。それだけよ</t>
         </is>
       </c>
     </row>
     <row r="548" ht="40" customHeight="1">
       <c r="A548" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.preMatch.standard.bold[2]</t>
         </is>
       </c>
       <c r="B548" t="inlineStr" s="2">
@@ -17942,7 +17942,7 @@
       </c>
       <c r="D548" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">summon.standard.bold[2]</t>
+          <t xml:space="preserve">preMatch.standard.bold[2]</t>
         </is>
       </c>
       <c r="E548" t="inlineStr" s="2">
@@ -17952,14 +17952,14 @@
       </c>
       <c r="F548" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふん、やっと正当な評価をしてくれたわけね</t>
+          <t xml:space="preserve">勝つのは私。最初から決まってることよ</t>
         </is>
       </c>
     </row>
     <row r="549" ht="40" customHeight="1">
       <c r="A549" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.bold[1]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.bold[1]</t>
         </is>
       </c>
       <c r="B549" t="inlineStr" s="2">
@@ -17969,12 +17969,12 @@
       </c>
       <c r="C549" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D549" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.bold[1]</t>
+          <t xml:space="preserve">summon.standard.bold[1]</t>
         </is>
       </c>
       <c r="E549" t="inlineStr" s="2">
@@ -17984,14 +17984,14 @@
       </c>
       <c r="F549" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ぶっ飛ばしてやる！</t>
+          <t xml:space="preserve">当然。呼ばれなかったら怒ってたわ</t>
         </is>
       </c>
     </row>
     <row r="550" ht="40" customHeight="1">
       <c r="A550" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.bold[2]</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES.summon.standard.bold[2]</t>
         </is>
       </c>
       <c r="B550" t="inlineStr" s="2">
@@ -18001,12 +18001,12 @@
       </c>
       <c r="C550" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">JUNIOR_TOURNAMENT_LINES</t>
         </is>
       </c>
       <c r="D550" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.bold[2]</t>
+          <t xml:space="preserve">summon.standard.bold[2]</t>
         </is>
       </c>
       <c r="E550" t="inlineStr" s="2">
@@ -18016,14 +18016,14 @@
       </c>
       <c r="F550" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私の実力、思い知らせてあげる</t>
+          <t xml:space="preserve">ふん、やっと正当な評価をしてくれたわけね</t>
         </is>
       </c>
     </row>
     <row r="551" ht="40" customHeight="1">
       <c r="A551" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.bold[3]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.bold[1]</t>
         </is>
       </c>
       <c r="B551" t="inlineStr" s="2">
@@ -18038,7 +18038,7 @@
       </c>
       <c r="D551" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.bold[3]</t>
+          <t xml:space="preserve">standard.bold[1]</t>
         </is>
       </c>
       <c r="E551" t="inlineStr" s="2">
@@ -18048,14 +18048,14 @@
       </c>
       <c r="F551" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">容赦しないわ。覚悟しなさい！</t>
+          <t xml:space="preserve">ぶっ飛ばしてやる！</t>
         </is>
       </c>
     </row>
     <row r="552" ht="40" customHeight="1">
       <c r="A552" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.bold[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.bold[2]</t>
         </is>
       </c>
       <c r="B552" t="inlineStr" s="2">
@@ -18065,12 +18065,12 @@
       </c>
       <c r="C552" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D552" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.bold[1]</t>
+          <t xml:space="preserve">standard.bold[2]</t>
         </is>
       </c>
       <c r="E552" t="inlineStr" s="2">
@@ -18080,14 +18080,14 @@
       </c>
       <c r="F552" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この瞬間をずっと待ってた……！ いい気分！</t>
+          <t xml:space="preserve">私の実力、思い知らせてあげる</t>
         </is>
       </c>
     </row>
     <row r="553" ht="40" customHeight="1">
       <c r="A553" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.bold[2]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.standard.bold[3]</t>
         </is>
       </c>
       <c r="B553" t="inlineStr" s="2">
@@ -18097,12 +18097,12 @@
       </c>
       <c r="C553" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D553" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.bold[2]</t>
+          <t xml:space="preserve">standard.bold[3]</t>
         </is>
       </c>
       <c r="E553" t="inlineStr" s="2">
@@ -18112,14 +18112,14 @@
       </c>
       <c r="F553" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">これが一番の景色か……！ 私のものね……！</t>
+          <t xml:space="preserve">容赦しないわ。覚悟しなさい！</t>
         </is>
       </c>
     </row>
     <row r="554" ht="40" customHeight="1">
       <c r="A554" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.bold[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.bold[1]</t>
         </is>
       </c>
       <c r="B554" t="inlineStr" s="2">
@@ -18129,7 +18129,7 @@
       </c>
       <c r="C554" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D554" t="inlineStr" s="12">
@@ -18144,14 +18144,14 @@
       </c>
       <c r="F554" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">聞いてあきれる。そんな団体に負けるわけないでしょ</t>
+          <t xml:space="preserve">この瞬間をずっと待ってた……！ いい気分！</t>
         </is>
       </c>
     </row>
     <row r="555" ht="40" customHeight="1">
       <c r="A555" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.bold[2]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.standard.bold[2]</t>
         </is>
       </c>
       <c r="B555" t="inlineStr" s="2">
@@ -18161,7 +18161,7 @@
       </c>
       <c r="C555" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D555" t="inlineStr" s="12">
@@ -18176,14 +18176,14 @@
       </c>
       <c r="F555" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あんたたちの看板選手？ 笑わせないで</t>
+          <t xml:space="preserve">これが一番の景色か……！ 私のものね……！</t>
         </is>
       </c>
     </row>
     <row r="556" ht="40" customHeight="1">
       <c r="A556" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.bold[1]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.bold[1]</t>
         </is>
       </c>
       <c r="B556" t="inlineStr" s="2">
@@ -18193,7 +18193,7 @@
       </c>
       <c r="C556" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D556" t="inlineStr" s="12">
@@ -18208,14 +18208,14 @@
       </c>
       <c r="F556" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">はっ、やっぱりね。戦う前から結果は見えてたわ</t>
+          <t xml:space="preserve">聞いてあきれる。そんな団体に負けるわけないでしょ</t>
         </is>
       </c>
     </row>
     <row r="557" ht="40" customHeight="1">
       <c r="A557" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.bold[2]</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE.standard.bold[2]</t>
         </is>
       </c>
       <c r="B557" t="inlineStr" s="2">
@@ -18225,7 +18225,7 @@
       </c>
       <c r="C557" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
+          <t xml:space="preserve">WAR_CHALLENGER_DIALOGUE</t>
         </is>
       </c>
       <c r="D557" t="inlineStr" s="12">
@@ -18240,14 +18240,14 @@
       </c>
       <c r="F557" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">逃げるの？ まあ、賢い判断よね</t>
+          <t xml:space="preserve">あんたたちの看板選手？ 笑わせないで</t>
         </is>
       </c>
     </row>
     <row r="558" ht="40" customHeight="1">
       <c r="A558" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.bold[1]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.bold[1]</t>
         </is>
       </c>
       <c r="B558" t="inlineStr" s="2">
@@ -18257,12 +18257,12 @@
       </c>
       <c r="C558" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D558" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.standard.bold[1]</t>
+          <t xml:space="preserve">standard.bold[1]</t>
         </is>
       </c>
       <c r="E558" t="inlineStr" s="2">
@@ -18272,14 +18272,14 @@
       </c>
       <c r="F558" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こんなの認めない…！ 絶対にリベンジしてやる</t>
+          <t xml:space="preserve">はっ、やっぱりね。戦う前から結果は見えてたわ</t>
         </is>
       </c>
     </row>
     <row r="559" ht="40" customHeight="1">
       <c r="A559" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.bold[2]</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE.standard.bold[2]</t>
         </is>
       </c>
       <c r="B559" t="inlineStr" s="2">
@@ -18289,12 +18289,12 @@
       </c>
       <c r="C559" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
+          <t xml:space="preserve">WAR_DECLINE_DIALOGUE</t>
         </is>
       </c>
       <c r="D559" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_lose.standard.bold[2]</t>
+          <t xml:space="preserve">standard.bold[2]</t>
         </is>
       </c>
       <c r="E559" t="inlineStr" s="2">
@@ -18304,14 +18304,14 @@
       </c>
       <c r="F559" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">たまたまよ、たまたま。次は潰す</t>
+          <t xml:space="preserve">逃げるの？ まあ、賢い判断よね</t>
         </is>
       </c>
     </row>
     <row r="560" ht="40" customHeight="1">
       <c r="A560" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.bold[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.bold[1]</t>
         </is>
       </c>
       <c r="B560" t="inlineStr" s="2">
@@ -18326,7 +18326,7 @@
       </c>
       <c r="D560" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.standard.bold[1]</t>
+          <t xml:space="preserve">result_lose.standard.bold[1]</t>
         </is>
       </c>
       <c r="E560" t="inlineStr" s="2">
@@ -18336,14 +18336,14 @@
       </c>
       <c r="F560" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然の結果でしょ。格が違うのよ</t>
+          <t xml:space="preserve">こんなの認めない…！ 絶対にリベンジしてやる</t>
         </is>
       </c>
     </row>
     <row r="561" ht="40" customHeight="1">
       <c r="A561" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.bold[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_lose.standard.bold[2]</t>
         </is>
       </c>
       <c r="B561" t="inlineStr" s="2">
@@ -18358,7 +18358,7 @@
       </c>
       <c r="D561" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">result_win.standard.bold[2]</t>
+          <t xml:space="preserve">result_lose.standard.bold[2]</t>
         </is>
       </c>
       <c r="E561" t="inlineStr" s="2">
@@ -18368,14 +18368,14 @@
       </c>
       <c r="F561" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう二度と歯向かわないことね</t>
+          <t xml:space="preserve">たまたまよ、たまたま。次は潰す</t>
         </is>
       </c>
     </row>
     <row r="562" ht="40" customHeight="1">
       <c r="A562" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.standard.bold[1]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.bold[1]</t>
         </is>
       </c>
       <c r="B562" t="inlineStr" s="2">
@@ -18385,12 +18385,12 @@
       </c>
       <c r="C562" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D562" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.bold[1]</t>
+          <t xml:space="preserve">result_win.standard.bold[1]</t>
         </is>
       </c>
       <c r="E562" t="inlineStr" s="2">
@@ -18400,14 +18400,14 @@
       </c>
       <c r="F562" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">当然でしょ！ うちの団体を甘く見ないでよね！</t>
+          <t xml:space="preserve">当然の結果でしょ。格が違うのよ</t>
         </is>
       </c>
     </row>
     <row r="563" ht="40" customHeight="1">
       <c r="A563" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.standard.bold[2]</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE.result_win.standard.bold[2]</t>
         </is>
       </c>
       <c r="B563" t="inlineStr" s="2">
@@ -18417,12 +18417,12 @@
       </c>
       <c r="C563" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">WAR_POST_DIALOGUE</t>
         </is>
       </c>
       <c r="D563" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.bold[2]</t>
+          <t xml:space="preserve">result_win.standard.bold[2]</t>
         </is>
       </c>
       <c r="E563" t="inlineStr" s="2">
@@ -18432,14 +18432,14 @@
       </c>
       <c r="F563" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この勝利は団体のみんなの勝利よ！</t>
+          <t xml:space="preserve">もう二度と歯向かわないことね</t>
         </is>
       </c>
     </row>
     <row r="564" ht="40" customHeight="1">
       <c r="A564" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.standard.bold[3]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.standard.bold[1]</t>
         </is>
       </c>
       <c r="B564" t="inlineStr" s="2">
@@ -18454,7 +18454,7 @@
       </c>
       <c r="D564" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.bold[3]</t>
+          <t xml:space="preserve">standard.bold[1]</t>
         </is>
       </c>
       <c r="E564" t="inlineStr" s="2">
@@ -18464,14 +18464,14 @@
       </c>
       <c r="F564" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">はっ、他所の団体なんてこんなもんよ！</t>
+          <t xml:space="preserve">当然でしょ！ うちの団体を甘く見ないでよね！</t>
         </is>
       </c>
     </row>
     <row r="565" ht="40" customHeight="1">
       <c r="A565" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.standard.bold[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.standard.bold[2]</t>
         </is>
       </c>
       <c r="B565" t="inlineStr" s="2">
@@ -18481,29 +18481,29 @@
       </c>
       <c r="C565" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D565" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.standard.bold[1]</t>
+          <t xml:space="preserve">standard.bold[2]</t>
         </is>
       </c>
       <c r="E565" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F565" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここが頂点？…でもまだ先がある気がする</t>
+          <t xml:space="preserve">この勝利は団体のみんなの勝利よ！</t>
         </is>
       </c>
     </row>
     <row r="566" ht="40" customHeight="1">
       <c r="A566" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.standard.bold[2]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.standard.bold[3]</t>
         </is>
       </c>
       <c r="B566" t="inlineStr" s="2">
@@ -18513,29 +18513,29 @@
       </c>
       <c r="C566" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D566" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.standard.bold[2]</t>
+          <t xml:space="preserve">standard.bold[3]</t>
         </is>
       </c>
       <c r="E566" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F566" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここで終わりじゃない。もっと強くなって、もっと上を目指す</t>
+          <t xml:space="preserve">はっ、他所の団体なんてこんなもんよ！</t>
         </is>
       </c>
     </row>
     <row r="567" ht="40" customHeight="1">
       <c r="A567" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.standard.bold[3]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter.standard.bold[1]</t>
         </is>
       </c>
       <c r="B567" t="inlineStr" s="2">
@@ -18550,7 +18550,7 @@
       </c>
       <c r="D567" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.standard.bold[3]</t>
+          <t xml:space="preserve">fighter.standard.bold[1]</t>
         </is>
       </c>
       <c r="E567" t="inlineStr" s="2">
@@ -18560,14 +18560,14 @@
       </c>
       <c r="F567" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">私たちの戦いが業界を変えたってことね。誇りに思うよ</t>
+          <t xml:space="preserve">ここが頂点？…でもまだ先がある気がする</t>
         </is>
       </c>
     </row>
     <row r="568" ht="40" customHeight="1">
       <c r="A568" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.standard.bold[1]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter.standard.bold[2]</t>
         </is>
       </c>
       <c r="B568" t="inlineStr" s="2">
@@ -18577,29 +18577,29 @@
       </c>
       <c r="C568" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
       <c r="D568" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.bold[1]</t>
+          <t xml:space="preserve">fighter.standard.bold[2]</t>
         </is>
       </c>
       <c r="E568" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
       <c r="F568" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">フリーのままで終わる女じゃないって、証明する</t>
+          <t xml:space="preserve">ここで終わりじゃない。もっと強くなって、もっと上を目指す</t>
         </is>
       </c>
     </row>
     <row r="569" ht="40" customHeight="1">
       <c r="A569" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.standard.bold[2]</t>
+          <t xml:space="preserve">ENDING_LINES.fighter.standard.bold[3]</t>
         </is>
       </c>
       <c r="B569" t="inlineStr" s="2">
@@ -18609,29 +18609,29 @@
       </c>
       <c r="C569" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
       <c r="D569" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">standard.bold[2]</t>
+          <t xml:space="preserve">fighter.standard.bold[3]</t>
         </is>
       </c>
       <c r="E569" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
       <c r="F569" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">払ってくれた分は、全部利子つけて返してやる</t>
+          <t xml:space="preserve">私たちの戦いが業界を変えたってことね。誇りに思うよ</t>
         </is>
       </c>
     </row>
     <row r="570" ht="40" customHeight="1">
       <c r="A570" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.standard.bold[1]</t>
+          <t xml:space="preserve">FA_GREETING_LINES.standard.bold[1]</t>
         </is>
       </c>
       <c r="B570" t="inlineStr" s="2">
@@ -18641,7 +18641,7 @@
       </c>
       <c r="C570" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
         </is>
       </c>
       <c r="D570" t="inlineStr" s="12">
@@ -18656,44 +18656,108 @@
       </c>
       <c r="F570" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">見る目あるじゃん。すぐ活躍してみせるよ</t>
+          <t xml:space="preserve">フリーのままで終わる女じゃないって、証明する</t>
         </is>
       </c>
     </row>
     <row r="571" ht="40" customHeight="1">
       <c r="A571" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">FA_GREETING_LINES.standard.bold[2]</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold[2]</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">払ってくれた分は、全部利子つけて返してやる</t>
+        </is>
+      </c>
+    </row>
+    <row r="572" ht="40" customHeight="1">
+      <c r="A572" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">standard.bold[1]</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">見る目あるじゃん。すぐ活躍してみせるよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="573" ht="40" customHeight="1">
+      <c r="A573" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.standard.bold[2]</t>
         </is>
       </c>
-      <c r="B571" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C571" t="inlineStr" s="2">
+      <c r="B573" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D571" t="inlineStr" s="12">
+      <c r="D573" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">standard.bold[2]</t>
         </is>
       </c>
-      <c r="E571" t="inlineStr" s="2">
+      <c r="E573" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F571" t="inlineStr" s="3">
+      <c r="F573" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">買われた実力、値段以上だったって言わせてみせるよ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H571"/>
+  <autoFilter ref="A1:H573"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/標準×強気.xlsx
+++ b/セリフ編集/キャラタイプ別/標準×強気.xlsx
@@ -3736,7 +3736,7 @@
       </c>
       <c r="F104" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、あの人とやらせてください。勝てます。</t>
+          <t xml:space="preserve">社長、三人であちらへ行かせてください。勝てます。</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="F105" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの人とやりたいんです。……今なら、いけると思ってます。</t>
+          <t xml:space="preserve">三人で乗り込みたいんです。……今なら、いけると思ってます。</t>
         </is>
       </c>
     </row>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="F106" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">待ってても回ってこないので、言いに来ました。組んでください。</t>
+          <t xml:space="preserve">待ってても回ってこないので、言いに来ました。三人で組ませてください。</t>
         </is>
       </c>
     </row>
